--- a/research/traditional_assets/database/data/indonesia/indonesia_diversified.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_diversified.xlsx
@@ -650,10 +650,10 @@
         <v>0.1821115796302303</v>
       </c>
       <c r="X2">
-        <v>0.1166541338677419</v>
+        <v>0.116638142686051</v>
       </c>
       <c r="Y2">
-        <v>0.06545744576248841</v>
+        <v>0.06547343694417929</v>
       </c>
       <c r="Z2">
         <v>1.484292883116158</v>
@@ -662,10 +662,10 @@
         <v>0.1709075714050555</v>
       </c>
       <c r="AB2">
-        <v>0.09651213260647325</v>
+        <v>0.09650169925221221</v>
       </c>
       <c r="AC2">
-        <v>0.07439543879858225</v>
+        <v>0.07440587215284329</v>
       </c>
       <c r="AD2">
         <v>6551.6</v>
@@ -787,10 +787,10 @@
         <v>0.1821115796302303</v>
       </c>
       <c r="X3">
-        <v>0.1166541338677419</v>
+        <v>0.116638142686051</v>
       </c>
       <c r="Y3">
-        <v>0.06545744576248841</v>
+        <v>0.06547343694417929</v>
       </c>
       <c r="Z3">
         <v>1.484292883116158</v>
@@ -799,10 +799,10 @@
         <v>0.1709075714050555</v>
       </c>
       <c r="AB3">
-        <v>0.09651213260647325</v>
+        <v>0.09650169925221221</v>
       </c>
       <c r="AC3">
-        <v>0.07439543879858225</v>
+        <v>0.07440587215284329</v>
       </c>
       <c r="AD3">
         <v>6551.6</v>
@@ -1139,7 +1139,7 @@
         <v>11.4427917620137</v>
       </c>
       <c r="F2">
-        <v>8.6761159607628</v>
+        <v>8.85175221733197</v>
       </c>
       <c r="G2">
         <v>1.6270799185417</v>
@@ -1157,13 +1157,13 @@
         <v>12298.9</v>
       </c>
       <c r="L2">
-        <v>14235.1468729929</v>
+        <v>14309.435435692</v>
       </c>
       <c r="M2">
         <v>15477.1</v>
       </c>
       <c r="N2">
-        <v>15762.8768729929</v>
+        <v>15837.165435692</v>
       </c>
       <c r="O2">
         <v>6551.6</v>
@@ -1172,16 +1172,16 @@
         <v>4901.13</v>
       </c>
       <c r="Q2">
-        <v>0.09651213260647321</v>
+        <v>0.09650169925221221</v>
       </c>
       <c r="R2">
-        <v>0.0953936168425697</v>
+        <v>0.0950990458793593</v>
       </c>
       <c r="S2">
         <v>0.0587008408132904</v>
       </c>
       <c r="T2">
-        <v>0.0550348408132904</v>
+        <v>0.0539428408132904</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.116654133867742</v>
+        <v>0.116638142686051</v>
       </c>
       <c r="X2">
-        <v>0.109573727339344</v>
+        <v>0.109559334145816</v>
       </c>
       <c r="Y2">
         <v>1.03078128973376</v>
@@ -1236,7 +1236,7 @@
         <v>12298.9</v>
       </c>
       <c r="AK2">
-        <v>0.06873828092673559</v>
+        <v>0.06872276727524602</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09585574695705792</v>
+        <v>0.09584444979624923</v>
       </c>
       <c r="C2">
-        <v>19016.93453621897</v>
+        <v>19017.15752614465</v>
       </c>
       <c r="D2">
-        <v>15643.53453621897</v>
+        <v>15643.75752614465</v>
       </c>
       <c r="E2">
         <v>-6551.6</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09585574695705792</v>
+        <v>0.09584444979624923</v>
       </c>
       <c r="T2">
         <v>0.7282077218429368</v>
       </c>
       <c r="U2">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V2">
         <v>0.22</v>
       </c>
       <c r="W2">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.0958379727218853</v>
+        <v>0.0958157804148304</v>
       </c>
       <c r="C3">
-        <v>18832.98620094316</v>
+        <v>18836.00390056454</v>
       </c>
       <c r="D3">
-        <v>15648.09120094316</v>
+        <v>15651.10890056454</v>
       </c>
       <c r="E3">
         <v>-6363.095</v>
@@ -1539,37 +1539,37 @@
         <v>3000.3</v>
       </c>
       <c r="M3">
-        <v>13.30043931731961</v>
+        <v>13.03653231731962</v>
       </c>
       <c r="N3">
-        <v>2986.999560682681</v>
+        <v>2987.263467682681</v>
       </c>
       <c r="O3">
-        <v>657.1399033501897</v>
+        <v>657.1979628901897</v>
       </c>
       <c r="P3">
-        <v>2329.859657332491</v>
+        <v>2330.065504792491</v>
       </c>
       <c r="Q3">
-        <v>3356.15965733249</v>
+        <v>3356.365504792491</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09625012556944686</v>
+        <v>0.09623873940070454</v>
       </c>
       <c r="T3">
         <v>0.7339451160150327</v>
       </c>
       <c r="U3">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>225.5790149798329</v>
+        <v>230.1455576506314</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09582019848671267</v>
+        <v>0.09578711103341155</v>
       </c>
       <c r="C4">
-        <v>18649.04052098071</v>
+        <v>18654.85718740476</v>
       </c>
       <c r="D4">
-        <v>15652.65052098071</v>
+        <v>15658.46718740476</v>
       </c>
       <c r="E4">
         <v>-6174.59</v>
@@ -1621,37 +1621,37 @@
         <v>3000.3</v>
       </c>
       <c r="M4">
-        <v>26.60087863463923</v>
+        <v>26.07306463463923</v>
       </c>
       <c r="N4">
-        <v>2973.699121365361</v>
+        <v>2974.226935365361</v>
       </c>
       <c r="O4">
-        <v>654.2138067003795</v>
+        <v>654.3299257803794</v>
       </c>
       <c r="P4">
-        <v>2319.485314664982</v>
+        <v>2319.897009584982</v>
       </c>
       <c r="Q4">
-        <v>3345.785314664981</v>
+        <v>3346.197009584982</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09665255272494577</v>
+        <v>0.09664107573178136</v>
       </c>
       <c r="T4">
         <v>0.73979959986411</v>
       </c>
       <c r="U4">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>112.7895074899165</v>
+        <v>115.0727788253157</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09580242425154005</v>
+        <v>0.0957584416519927</v>
       </c>
       <c r="C5">
-        <v>18465.0974986533</v>
+        <v>18473.71739641941</v>
       </c>
       <c r="D5">
-        <v>15657.21249865329</v>
+        <v>15665.83239641941</v>
       </c>
       <c r="E5">
         <v>-5986.085</v>
@@ -1703,37 +1703,37 @@
         <v>3000.3</v>
       </c>
       <c r="M5">
-        <v>39.90131795195884</v>
+        <v>39.10959695195885</v>
       </c>
       <c r="N5">
-        <v>2960.398682048041</v>
+        <v>2961.190403048041</v>
       </c>
       <c r="O5">
-        <v>651.2877100505691</v>
+        <v>651.4618886705691</v>
       </c>
       <c r="P5">
-        <v>2309.110971997472</v>
+        <v>2309.728514377472</v>
       </c>
       <c r="Q5">
-        <v>3335.410971997472</v>
+        <v>3336.028514377472</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09706327734756839</v>
+        <v>0.0970517076573134</v>
       </c>
       <c r="T5">
         <v>0.745774794720385</v>
       </c>
       <c r="U5">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.19300499327764</v>
+        <v>76.71518588354378</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09578465001636743</v>
+        <v>0.09572977227057386</v>
       </c>
       <c r="C6">
-        <v>18281.1571362853</v>
+        <v>18292.58453738094</v>
       </c>
       <c r="D6">
-        <v>15661.7771362853</v>
+        <v>15673.20453738094</v>
       </c>
       <c r="E6">
         <v>-5797.58</v>
@@ -1785,37 +1785,37 @@
         <v>3000.3</v>
       </c>
       <c r="M6">
-        <v>53.20175726927846</v>
+        <v>52.14612926927846</v>
       </c>
       <c r="N6">
-        <v>2947.098242730722</v>
+        <v>2948.153870730722</v>
       </c>
       <c r="O6">
-        <v>648.3616134007588</v>
+        <v>648.5938515607588</v>
       </c>
       <c r="P6">
-        <v>2298.736629329963</v>
+        <v>2299.560019169963</v>
       </c>
       <c r="Q6">
-        <v>3325.036629329963</v>
+        <v>3325.860019169963</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09748255873316231</v>
+        <v>0.09747089441462733</v>
       </c>
       <c r="T6">
         <v>0.7518744728028323</v>
       </c>
       <c r="U6">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.39475374495823</v>
+        <v>57.53638941265784</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09576687578119479</v>
+        <v>0.095701102889155</v>
       </c>
       <c r="C7">
-        <v>18097.21943620383</v>
+        <v>18111.45862008023</v>
       </c>
       <c r="D7">
-        <v>15666.34443620383</v>
+        <v>15680.58362008023</v>
       </c>
       <c r="E7">
         <v>-5609.075000000001</v>
@@ -1867,37 +1867,37 @@
         <v>3000.3</v>
       </c>
       <c r="M7">
-        <v>66.50219658659809</v>
+        <v>65.18266158659809</v>
       </c>
       <c r="N7">
-        <v>2933.797803413402</v>
+        <v>2935.117338413402</v>
       </c>
       <c r="O7">
-        <v>645.4355167509485</v>
+        <v>645.7258144509485</v>
       </c>
       <c r="P7">
-        <v>2288.362286662454</v>
+        <v>2289.391523962454</v>
       </c>
       <c r="Q7">
-        <v>3314.662286662453</v>
+        <v>3315.691523962454</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09791066709529503</v>
+        <v>0.09789890615630578</v>
       </c>
       <c r="T7">
         <v>0.7581025651606995</v>
       </c>
       <c r="U7">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.11580299596658</v>
+        <v>46.02911153012626</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09574910154602218</v>
+        <v>0.09567243350773617</v>
       </c>
       <c r="C8">
-        <v>17913.2844007387</v>
+        <v>17930.33965432657</v>
       </c>
       <c r="D8">
-        <v>15670.9144007387</v>
+        <v>15687.96965432657</v>
       </c>
       <c r="E8">
         <v>-5420.570000000001</v>
@@ -1949,37 +1949,37 @@
         <v>3000.3</v>
       </c>
       <c r="M8">
-        <v>79.80263590391769</v>
+        <v>78.2191939039177</v>
       </c>
       <c r="N8">
-        <v>2920.497364096082</v>
+        <v>2922.080806096083</v>
       </c>
       <c r="O8">
-        <v>642.5094201011382</v>
+        <v>642.8577773411382</v>
       </c>
       <c r="P8">
-        <v>2277.987943994945</v>
+        <v>2279.223028754945</v>
       </c>
       <c r="Q8">
-        <v>3304.287943994944</v>
+        <v>3305.523028754944</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09834788414598378</v>
+        <v>0.09833602453078591</v>
       </c>
       <c r="T8">
         <v>0.7644631701219256</v>
       </c>
       <c r="U8">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.59650249663882</v>
+        <v>38.35759294177189</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09573132731084956</v>
+        <v>0.09564376412631732</v>
       </c>
       <c r="C9">
-        <v>17729.35203222242</v>
+        <v>17749.2276499478</v>
       </c>
       <c r="D9">
-        <v>15675.48703222243</v>
+        <v>15695.3626499478</v>
       </c>
       <c r="E9">
         <v>-5232.065000000001</v>
@@ -2031,37 +2031,37 @@
         <v>3000.3</v>
       </c>
       <c r="M9">
-        <v>93.10307522123732</v>
+        <v>91.25572622123731</v>
       </c>
       <c r="N9">
-        <v>2907.196924778763</v>
+        <v>2909.044273778763</v>
       </c>
       <c r="O9">
-        <v>639.5833234513278</v>
+        <v>639.9897402313279</v>
       </c>
       <c r="P9">
-        <v>2267.613601327435</v>
+        <v>2269.054533547435</v>
       </c>
       <c r="Q9">
-        <v>3293.913601327435</v>
+        <v>3295.354533547435</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09879450371389165</v>
+        <v>0.09878254330041614</v>
       </c>
       <c r="T9">
         <v>0.770960562286619</v>
       </c>
       <c r="U9">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.22557356854756</v>
+        <v>32.87793680723305</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09571355307567693</v>
+        <v>0.09561509474489849</v>
       </c>
       <c r="C10">
-        <v>17545.42233299028</v>
+        <v>17568.12261679022</v>
       </c>
       <c r="D10">
-        <v>15680.06233299028</v>
+        <v>15702.76261679022</v>
       </c>
       <c r="E10">
         <v>-5043.56</v>
@@ -2113,37 +2113,37 @@
         <v>3000.3</v>
       </c>
       <c r="M10">
-        <v>106.4035145385569</v>
+        <v>104.2922585385569</v>
       </c>
       <c r="N10">
-        <v>2893.896485461443</v>
+        <v>2896.007741461443</v>
       </c>
       <c r="O10">
-        <v>636.6572268015175</v>
+        <v>637.1217031215175</v>
       </c>
       <c r="P10">
-        <v>2257.239258659926</v>
+        <v>2258.886038339926</v>
       </c>
       <c r="Q10">
-        <v>3283.539258659926</v>
+        <v>3285.186038339926</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09925083240284098</v>
+        <v>0.09923876899982093</v>
       </c>
       <c r="T10">
         <v>0.7775992021070665</v>
       </c>
       <c r="U10">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.19737687247911</v>
+        <v>28.76819470632892</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09569577884050431</v>
+        <v>0.09558642536347964</v>
       </c>
       <c r="C11">
-        <v>17361.49530538025</v>
+        <v>17387.02456471876</v>
       </c>
       <c r="D11">
-        <v>15684.64030538025</v>
+        <v>15710.16956471876</v>
       </c>
       <c r="E11">
         <v>-4855.055</v>
@@ -2195,37 +2195,37 @@
         <v>3000.3</v>
       </c>
       <c r="M11">
-        <v>119.7039538558765</v>
+        <v>117.3287908558765</v>
       </c>
       <c r="N11">
-        <v>2880.596046144124</v>
+        <v>2882.971209144124</v>
       </c>
       <c r="O11">
-        <v>633.7311301517072</v>
+        <v>634.2536660117072</v>
       </c>
       <c r="P11">
-        <v>2246.864915992416</v>
+        <v>2248.717543132417</v>
       </c>
       <c r="Q11">
-        <v>3273.164915992416</v>
+        <v>3275.017543132416</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09971719029374525</v>
+        <v>0.09970502163767418</v>
       </c>
       <c r="T11">
         <v>0.784383746099392</v>
       </c>
       <c r="U11">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.06433499775921</v>
+        <v>25.57172862784793</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09567800460533168</v>
+        <v>0.09555775598206079</v>
       </c>
       <c r="C12">
-        <v>17177.57095173304</v>
+        <v>17205.93350361697</v>
       </c>
       <c r="D12">
-        <v>15689.22095173303</v>
+        <v>15717.58350361696</v>
       </c>
       <c r="E12">
         <v>-4666.55</v>
@@ -2277,37 +2277,37 @@
         <v>3000.3</v>
       </c>
       <c r="M12">
-        <v>133.0043931731962</v>
+        <v>130.3653231731962</v>
       </c>
       <c r="N12">
-        <v>2867.295606826804</v>
+        <v>2869.934676826804</v>
       </c>
       <c r="O12">
-        <v>630.8050335018969</v>
+        <v>631.3856289018969</v>
       </c>
       <c r="P12">
-        <v>2236.490573324907</v>
+        <v>2238.549047924907</v>
       </c>
       <c r="Q12">
-        <v>3262.790573324907</v>
+        <v>3264.849047924907</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1001939116933363</v>
+        <v>0.1001816354452575</v>
       </c>
       <c r="T12">
         <v>0.7913190577359913</v>
       </c>
       <c r="U12">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.55790149798329</v>
+        <v>23.01455576506313</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09566023037015907</v>
+        <v>0.09552908660064195</v>
       </c>
       <c r="C13">
-        <v>16993.64927439209</v>
+        <v>17024.84944338703</v>
       </c>
       <c r="D13">
-        <v>15693.80427439209</v>
+        <v>15725.00444338703</v>
       </c>
       <c r="E13">
         <v>-4478.045</v>
@@ -2359,37 +2359,37 @@
         <v>3000.3</v>
       </c>
       <c r="M13">
-        <v>146.3048324905158</v>
+        <v>143.4018554905158</v>
       </c>
       <c r="N13">
-        <v>2853.995167509484</v>
+        <v>2856.898144509485</v>
       </c>
       <c r="O13">
-        <v>627.8789368520866</v>
+        <v>628.5175917920866</v>
       </c>
       <c r="P13">
-        <v>2226.116230657398</v>
+        <v>2228.380552717398</v>
       </c>
       <c r="Q13">
-        <v>3252.416230657398</v>
+        <v>3254.680552717398</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1006813459333676</v>
+        <v>0.1006689596754832</v>
       </c>
       <c r="T13">
         <v>0.7984102190722897</v>
       </c>
       <c r="U13">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.50718317998481</v>
+        <v>20.92232342278467</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.09564245613498645</v>
+        <v>0.09550041721922312</v>
       </c>
       <c r="C14">
-        <v>16809.73027570361</v>
+        <v>16843.77239394985</v>
       </c>
       <c r="D14">
-        <v>15698.39027570361</v>
+        <v>15732.43239394985</v>
       </c>
       <c r="E14">
         <v>-4289.540000000001</v>
@@ -2441,37 +2441,37 @@
         <v>3000.3</v>
       </c>
       <c r="M14">
-        <v>159.6052718078354</v>
+        <v>156.4383878078354</v>
       </c>
       <c r="N14">
-        <v>2840.694728192165</v>
+        <v>2843.861612192165</v>
       </c>
       <c r="O14">
-        <v>624.9528402022762</v>
+        <v>625.6495546822763</v>
       </c>
       <c r="P14">
-        <v>2215.741887989889</v>
+        <v>2218.212057509889</v>
       </c>
       <c r="Q14">
-        <v>3242.041887989888</v>
+        <v>3244.512057509889</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1011798582243086</v>
+        <v>0.1011673594563958</v>
       </c>
       <c r="T14">
         <v>0.8056625431662311</v>
       </c>
       <c r="U14">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.79825124831941</v>
+        <v>19.17879647088595</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.09562468189981381</v>
+        <v>0.09547174783780425</v>
       </c>
       <c r="C15">
-        <v>16625.81395801653</v>
+        <v>16662.70236524513</v>
       </c>
       <c r="D15">
-        <v>15702.97895801653</v>
+        <v>15739.86736524513</v>
       </c>
       <c r="E15">
         <v>-4101.035</v>
@@ -2523,37 +2523,37 @@
         <v>3000.3</v>
       </c>
       <c r="M15">
-        <v>172.905711125155</v>
+        <v>169.474920125155</v>
       </c>
       <c r="N15">
-        <v>2827.394288874845</v>
+        <v>2830.825079874845</v>
       </c>
       <c r="O15">
-        <v>622.026743552466</v>
+        <v>622.7815175724659</v>
       </c>
       <c r="P15">
-        <v>2205.367545322379</v>
+        <v>2208.043562302379</v>
       </c>
       <c r="Q15">
-        <v>3231.667545322379</v>
+        <v>3234.343562302379</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.101689830567915</v>
+        <v>0.1016772167035362</v>
       </c>
       <c r="T15">
         <v>0.813081587354286</v>
       </c>
       <c r="U15">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.35223192152561</v>
+        <v>17.70350443466395</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09560690766464118</v>
+        <v>0.09544307845638542</v>
       </c>
       <c r="C16">
-        <v>16441.90032368252</v>
+        <v>16481.6393672313</v>
       </c>
       <c r="D16">
-        <v>15707.57032368252</v>
+        <v>15747.3093672313</v>
       </c>
       <c r="E16">
         <v>-3912.53</v>
@@ -2605,37 +2605,37 @@
         <v>3000.3</v>
       </c>
       <c r="M16">
-        <v>186.2061504424746</v>
+        <v>182.5114524424746</v>
       </c>
       <c r="N16">
-        <v>2814.093849557526</v>
+        <v>2817.788547557525</v>
       </c>
       <c r="O16">
-        <v>619.1006469026556</v>
+        <v>619.9134804626556</v>
       </c>
       <c r="P16">
-        <v>2194.99320265487</v>
+        <v>2197.87506709487</v>
       </c>
       <c r="Q16">
-        <v>3221.29320265487</v>
+        <v>3224.17506709487</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1022116627334657</v>
+        <v>0.102198931095959</v>
       </c>
       <c r="T16">
         <v>0.8206731674536911</v>
       </c>
       <c r="U16">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.11278678427378</v>
+        <v>16.43896840361652</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.09558913342946856</v>
+        <v>0.09541440907496657</v>
       </c>
       <c r="C17">
-        <v>16257.98937505601</v>
+        <v>16300.58340988569</v>
       </c>
       <c r="D17">
-        <v>15712.16437505601</v>
+        <v>15754.75840988569</v>
       </c>
       <c r="E17">
         <v>-3724.025000000001</v>
@@ -2687,37 +2687,37 @@
         <v>3000.3</v>
       </c>
       <c r="M17">
-        <v>199.5065897597942</v>
+        <v>195.5479847597942</v>
       </c>
       <c r="N17">
-        <v>2800.793410240206</v>
+        <v>2804.752015240206</v>
       </c>
       <c r="O17">
-        <v>616.1745502528453</v>
+        <v>617.0454433528453</v>
       </c>
       <c r="P17">
-        <v>2184.618859987361</v>
+        <v>2187.70657188736</v>
       </c>
       <c r="Q17">
-        <v>3210.918859987361</v>
+        <v>3214.00657188736</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1027457733029118</v>
+        <v>0.1027329211211447</v>
       </c>
       <c r="T17">
         <v>0.8284433729671999</v>
       </c>
       <c r="U17">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.03860099865553</v>
+        <v>15.34303717670876</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.09557135919429594</v>
+        <v>0.09538573969354772</v>
       </c>
       <c r="C18">
-        <v>16074.08111449419</v>
+        <v>16119.53450320447</v>
       </c>
       <c r="D18">
-        <v>15716.76111449419</v>
+        <v>15762.21450320447</v>
       </c>
       <c r="E18">
         <v>-3535.52</v>
@@ -2769,37 +2769,37 @@
         <v>3000.3</v>
       </c>
       <c r="M18">
-        <v>212.8070290771138</v>
+        <v>208.5845170771138</v>
       </c>
       <c r="N18">
-        <v>2787.492970922886</v>
+        <v>2791.715482922886</v>
       </c>
       <c r="O18">
-        <v>613.248453603035</v>
+        <v>614.177406243035</v>
       </c>
       <c r="P18">
-        <v>2174.244517319851</v>
+        <v>2177.538076679851</v>
       </c>
       <c r="Q18">
-        <v>3200.544517319851</v>
+        <v>3203.838076679851</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.103292600790678</v>
+        <v>0.1032796251945491</v>
       </c>
       <c r="T18">
         <v>0.8363985833738874</v>
       </c>
       <c r="U18">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.09868843623956</v>
+        <v>14.38409735316446</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09555358495912332</v>
+        <v>0.09535707031212887</v>
       </c>
       <c r="C19">
-        <v>15890.17554435701</v>
+        <v>15938.4926572028</v>
       </c>
       <c r="D19">
-        <v>15721.36054435701</v>
+        <v>15769.6776572028</v>
       </c>
       <c r="E19">
         <v>-3347.015</v>
@@ -2851,37 +2851,37 @@
         <v>3000.3</v>
       </c>
       <c r="M19">
-        <v>226.1074683944335</v>
+        <v>221.6210493944335</v>
       </c>
       <c r="N19">
-        <v>2774.192531605567</v>
+        <v>2778.678950605567</v>
       </c>
       <c r="O19">
-        <v>610.3223569532247</v>
+        <v>611.3093691332247</v>
       </c>
       <c r="P19">
-        <v>2163.870174652342</v>
+        <v>2167.369581472342</v>
       </c>
       <c r="Q19">
-        <v>3190.170174652342</v>
+        <v>3193.669581472342</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1038526048444144</v>
+        <v>0.1038395028600838</v>
       </c>
       <c r="T19">
         <v>0.8445454855976037</v>
       </c>
       <c r="U19">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.26935382234311</v>
+        <v>13.5379739794489</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.09553581072395069</v>
+        <v>0.09532840093071004</v>
       </c>
       <c r="C20">
-        <v>15706.27266700717</v>
+        <v>15757.45788191475</v>
       </c>
       <c r="D20">
-        <v>15725.96266700717</v>
+        <v>15777.14788191475</v>
       </c>
       <c r="E20">
         <v>-3158.510000000001</v>
@@ -2933,37 +2933,37 @@
         <v>3000.3</v>
       </c>
       <c r="M20">
-        <v>239.4079077117531</v>
+        <v>234.6575817117531</v>
       </c>
       <c r="N20">
-        <v>2760.892092288247</v>
+        <v>2765.642418288247</v>
       </c>
       <c r="O20">
-        <v>607.3962603034144</v>
+        <v>608.4413320234144</v>
       </c>
       <c r="P20">
-        <v>2153.495831984833</v>
+        <v>2157.201086264833</v>
       </c>
       <c r="Q20">
-        <v>3179.795831984833</v>
+        <v>3183.501086264832</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1044262675336078</v>
+        <v>0.1044130360784363</v>
       </c>
       <c r="T20">
         <v>0.8528910927536054</v>
       </c>
       <c r="U20">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.53216749887961</v>
+        <v>12.78586431392396</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09551803648877807</v>
+        <v>0.09529973154929119</v>
       </c>
       <c r="C21">
-        <v>15522.37248481014</v>
+        <v>15576.43018739347</v>
       </c>
       <c r="D21">
-        <v>15730.56748481015</v>
+        <v>15784.62518739347</v>
       </c>
       <c r="E21">
         <v>-2970.005</v>
@@ -3015,37 +3015,37 @@
         <v>3000.3</v>
       </c>
       <c r="M21">
-        <v>252.7083470290727</v>
+        <v>247.6941140290727</v>
       </c>
       <c r="N21">
-        <v>2747.591652970927</v>
+        <v>2752.605885970927</v>
       </c>
       <c r="O21">
-        <v>604.470163653604</v>
+        <v>605.5732949136041</v>
       </c>
       <c r="P21">
-        <v>2143.121489317324</v>
+        <v>2147.032591057323</v>
       </c>
       <c r="Q21">
-        <v>3169.421489317323</v>
+        <v>3173.332591057323</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1050140947336456</v>
+        <v>0.1050007306108222</v>
       </c>
       <c r="T21">
         <v>0.8614427642838297</v>
       </c>
       <c r="U21">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.87257973578068</v>
+        <v>12.11292408687533</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09550026225360544</v>
+        <v>0.09527106216787237</v>
       </c>
       <c r="C22">
-        <v>15338.47500013419</v>
+        <v>15395.40958371114</v>
       </c>
       <c r="D22">
-        <v>15735.17500013419</v>
+        <v>15792.10958371114</v>
       </c>
       <c r="E22">
         <v>-2781.5</v>
@@ -3097,37 +3097,37 @@
         <v>3000.3</v>
       </c>
       <c r="M22">
-        <v>266.0087863463924</v>
+        <v>260.7306463463923</v>
       </c>
       <c r="N22">
-        <v>2734.291213653608</v>
+        <v>2739.569353653608</v>
       </c>
       <c r="O22">
-        <v>601.5440670037938</v>
+        <v>602.7052578037938</v>
       </c>
       <c r="P22">
-        <v>2132.747146649814</v>
+        <v>2136.864095849814</v>
       </c>
       <c r="Q22">
-        <v>3159.047146649814</v>
+        <v>3163.164095849814</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1056166176136842</v>
+        <v>0.1056031175065179</v>
       </c>
       <c r="T22">
         <v>0.8702082276023095</v>
       </c>
       <c r="U22">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.27895074899164</v>
+        <v>11.50727788253156</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09548248801843283</v>
+        <v>0.09524239278645349</v>
       </c>
       <c r="C23">
-        <v>15154.58021535033</v>
+        <v>15214.39608095908</v>
       </c>
       <c r="D23">
-        <v>15739.78521535033</v>
+        <v>15799.60108095908</v>
       </c>
       <c r="E23">
         <v>-2592.995</v>
@@ -3179,37 +3179,37 @@
         <v>3000.3</v>
       </c>
       <c r="M23">
-        <v>279.3092256637119</v>
+        <v>273.7671786637119</v>
       </c>
       <c r="N23">
-        <v>2720.990774336288</v>
+        <v>2726.532821336288</v>
       </c>
       <c r="O23">
-        <v>598.6179703539834</v>
+        <v>599.8372206939835</v>
       </c>
       <c r="P23">
-        <v>2122.372803982305</v>
+        <v>2126.695600642305</v>
       </c>
       <c r="Q23">
-        <v>3148.672803982305</v>
+        <v>3152.995600642304</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1062343942375213</v>
+        <v>0.1062207547033703</v>
       </c>
       <c r="T23">
         <v>0.8791956013845482</v>
       </c>
       <c r="U23">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.74185785618252</v>
+        <v>10.95931226907768</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.0954647137832602</v>
+        <v>0.09521372340503467</v>
       </c>
       <c r="C24">
-        <v>14970.68813283236</v>
+        <v>15033.38968924774</v>
       </c>
       <c r="D24">
-        <v>15744.39813283236</v>
+        <v>15807.09968924774</v>
       </c>
       <c r="E24">
         <v>-2404.490000000001</v>
@@ -3261,37 +3261,37 @@
         <v>3000.3</v>
       </c>
       <c r="M24">
-        <v>292.6096649810315</v>
+        <v>286.8037109810315</v>
       </c>
       <c r="N24">
-        <v>2707.690335018969</v>
+        <v>2713.496289018969</v>
       </c>
       <c r="O24">
-        <v>595.6918737041731</v>
+        <v>596.969183584173</v>
       </c>
       <c r="P24">
-        <v>2111.998461314795</v>
+        <v>2116.527105434795</v>
       </c>
       <c r="Q24">
-        <v>3138.298461314795</v>
+        <v>3142.827105434795</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1068680112876107</v>
+        <v>0.1068542287514241</v>
       </c>
       <c r="T24">
         <v>0.8884134206483829</v>
       </c>
       <c r="U24">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.25359158999241</v>
+        <v>10.46116171139233</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09544693954808757</v>
+        <v>0.09518505402361582</v>
       </c>
       <c r="C25">
-        <v>14786.79875495687</v>
+        <v>14852.39041870679</v>
       </c>
       <c r="D25">
-        <v>15749.01375495687</v>
+        <v>15814.60541870679</v>
       </c>
       <c r="E25">
         <v>-2215.985000000001</v>
@@ -3343,37 +3343,37 @@
         <v>3000.3</v>
       </c>
       <c r="M25">
-        <v>305.9101042983511</v>
+        <v>299.8402432983511</v>
       </c>
       <c r="N25">
-        <v>2694.389895701649</v>
+        <v>2700.459756701649</v>
       </c>
       <c r="O25">
-        <v>592.7657770543628</v>
+        <v>594.1011464743627</v>
       </c>
       <c r="P25">
-        <v>2101.624118647286</v>
+        <v>2106.358610227286</v>
       </c>
       <c r="Q25">
-        <v>3127.924118647286</v>
+        <v>3132.658610227286</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1075180859234166</v>
+        <v>0.1075041566708559</v>
       </c>
       <c r="T25">
         <v>0.8978706637892003</v>
       </c>
       <c r="U25">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.807783259992735</v>
+        <v>10.00632859350571</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09542916531291495</v>
+        <v>0.09515638464219697</v>
       </c>
       <c r="C26">
-        <v>14602.91208410323</v>
+        <v>14671.39827948515</v>
       </c>
       <c r="D26">
-        <v>15753.63208410322</v>
+        <v>15822.11827948515</v>
       </c>
       <c r="E26">
         <v>-2027.48</v>
@@ -3425,37 +3425,37 @@
         <v>3000.3</v>
       </c>
       <c r="M26">
-        <v>319.2105436156708</v>
+        <v>312.8767756156708</v>
       </c>
       <c r="N26">
-        <v>2681.089456384329</v>
+        <v>2687.423224384329</v>
       </c>
       <c r="O26">
-        <v>589.8396804045525</v>
+        <v>591.2331093645524</v>
       </c>
       <c r="P26">
-        <v>2091.249775979777</v>
+        <v>2096.190115019777</v>
       </c>
       <c r="Q26">
-        <v>3117.549775979777</v>
+        <v>3122.490115019777</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1081852677864806</v>
+        <v>0.1081711879565885</v>
       </c>
       <c r="T26">
         <v>0.9075767817495128</v>
       </c>
       <c r="U26">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.399125624159705</v>
+        <v>9.589398235442973</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09541139107774232</v>
+        <v>0.09512771526077812</v>
       </c>
       <c r="C27">
-        <v>14419.0281226536</v>
+        <v>14490.41328175103</v>
       </c>
       <c r="D27">
-        <v>15758.2531226536</v>
+        <v>15829.63828175103</v>
       </c>
       <c r="E27">
         <v>-1838.975</v>
@@ -3507,37 +3507,37 @@
         <v>3000.3</v>
       </c>
       <c r="M27">
-        <v>332.5109829329904</v>
+        <v>325.9133079329904</v>
       </c>
       <c r="N27">
-        <v>2667.78901706701</v>
+        <v>2674.38669206701</v>
       </c>
       <c r="O27">
-        <v>586.9135837547421</v>
+        <v>588.3650722547421</v>
       </c>
       <c r="P27">
-        <v>2080.875433312268</v>
+        <v>2086.021619812268</v>
       </c>
       <c r="Q27">
-        <v>3107.175433312268</v>
+        <v>3112.321619812267</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.108870241165893</v>
+        <v>0.108856006743274</v>
       </c>
       <c r="T27">
         <v>0.9175417295221003</v>
       </c>
       <c r="U27">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.023160599193316</v>
+        <v>9.205822306025254</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.09539361684256971</v>
+        <v>0.09509904587935927</v>
       </c>
       <c r="C28">
-        <v>14235.14687299295</v>
+        <v>14309.43543569196</v>
       </c>
       <c r="D28">
-        <v>15762.87687299295</v>
+        <v>15837.16543569196</v>
       </c>
       <c r="E28">
         <v>-1650.47</v>
@@ -3589,37 +3589,37 @@
         <v>3000.3</v>
       </c>
       <c r="M28">
-        <v>345.81142225031</v>
+        <v>338.94984025031</v>
       </c>
       <c r="N28">
-        <v>2654.48857774969</v>
+        <v>2661.35015974969</v>
       </c>
       <c r="O28">
-        <v>583.9874871049318</v>
+        <v>585.4970351449318</v>
       </c>
       <c r="P28">
-        <v>2070.501090644758</v>
+        <v>2075.853124604758</v>
       </c>
       <c r="Q28">
-        <v>3096.801090644758</v>
+        <v>3102.153124604758</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1095737273393435</v>
+        <v>0.1095593341458159</v>
       </c>
       <c r="T28">
         <v>0.9277760002074606</v>
       </c>
       <c r="U28">
-        <v>0.07055748822216713</v>
+        <v>0.06915748822216713</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.05503484081329037</v>
+        <v>0.05394284081329036</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.676115960762804</v>
+        <v>8.851752217331974</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09560750260739709</v>
+        <v>0.09538627649794043</v>
       </c>
       <c r="C29">
-        <v>13991.1815971417</v>
+        <v>14045.83983076756</v>
       </c>
       <c r="D29">
-        <v>15707.4165971417</v>
+        <v>15762.07483076756</v>
       </c>
       <c r="E29">
         <v>-1461.965</v>
@@ -3671,37 +3671,37 @@
         <v>3000.3</v>
       </c>
       <c r="M29">
-        <v>364.7104600676296</v>
+        <v>359.6208250676297</v>
       </c>
       <c r="N29">
-        <v>2635.58953993237</v>
+        <v>2640.679174932371</v>
       </c>
       <c r="O29">
-        <v>579.8296987851215</v>
+        <v>580.9494184851216</v>
       </c>
       <c r="P29">
-        <v>2055.759841147249</v>
+        <v>2059.729756447249</v>
       </c>
       <c r="Q29">
-        <v>3082.059841147249</v>
+        <v>3086.029756447249</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1102964871065872</v>
+        <v>0.1102819307922631</v>
       </c>
       <c r="T29">
         <v>0.9382906618705019</v>
       </c>
       <c r="U29">
-        <v>0.07165748822216714</v>
+        <v>0.07065748822216714</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.05589284081329037</v>
+        <v>0.05511284081329037</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.226525774565509</v>
+        <v>8.342953997271346</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09559830837222447</v>
+        <v>0.0953693071165216</v>
       </c>
       <c r="C30">
-        <v>13805.05262058459</v>
+        <v>13861.75133330042</v>
       </c>
       <c r="D30">
-        <v>15709.79262058459</v>
+        <v>15766.49133330042</v>
       </c>
       <c r="E30">
         <v>-1273.46</v>
@@ -3753,37 +3753,37 @@
         <v>3000.3</v>
       </c>
       <c r="M30">
-        <v>378.2182548849493</v>
+        <v>372.9401148849493</v>
       </c>
       <c r="N30">
-        <v>2622.081745115051</v>
+        <v>2627.359885115051</v>
       </c>
       <c r="O30">
-        <v>576.8579839253113</v>
+        <v>578.0191747253112</v>
       </c>
       <c r="P30">
-        <v>2045.22376118974</v>
+        <v>2049.34071038974</v>
       </c>
       <c r="Q30">
-        <v>3071.52376118974</v>
+        <v>3075.64071038974</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1110393235340322</v>
+        <v>0.1110245995677782</v>
       </c>
       <c r="T30">
         <v>0.9490973974686278</v>
       </c>
       <c r="U30">
-        <v>0.07165748822216714</v>
+        <v>0.07065748822216714</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.05589284081329037</v>
+        <v>0.05511284081329037</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.932721282616741</v>
+        <v>8.044991354511655</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09558911413705182</v>
+        <v>0.09535233773510274</v>
       </c>
       <c r="C31">
-        <v>13618.92436296705</v>
+        <v>13677.6653115177</v>
       </c>
       <c r="D31">
-        <v>15712.16936296705</v>
+        <v>15770.9103115177</v>
       </c>
       <c r="E31">
         <v>-1084.955000000001</v>
@@ -3835,37 +3835,37 @@
         <v>3000.3</v>
       </c>
       <c r="M31">
-        <v>391.7260497022688</v>
+        <v>386.2594047022689</v>
       </c>
       <c r="N31">
-        <v>2608.573950297731</v>
+        <v>2614.040595297731</v>
       </c>
       <c r="O31">
-        <v>573.8862690655009</v>
+        <v>575.0889309655008</v>
       </c>
       <c r="P31">
-        <v>2034.68768123223</v>
+        <v>2038.95166433223</v>
       </c>
       <c r="Q31">
-        <v>3060.98768123223</v>
+        <v>3065.25166433223</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1118030849312643</v>
+        <v>0.1117881885904909</v>
       </c>
       <c r="T31">
         <v>0.9602085481540246</v>
       </c>
       <c r="U31">
-        <v>0.07165748822216714</v>
+        <v>0.07065748822216714</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.05589284081329037</v>
+        <v>0.05511284081329037</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.659179169423061</v>
+        <v>7.767577859528495</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.0955799199018792</v>
+        <v>0.09533536835368389</v>
       </c>
       <c r="C32">
-        <v>13432.7968246154</v>
+        <v>13493.58176750162</v>
       </c>
       <c r="D32">
-        <v>15714.5468246154</v>
+        <v>15775.33176750162</v>
       </c>
       <c r="E32">
         <v>-896.4500000000007</v>
@@ -3917,37 +3917,37 @@
         <v>3000.3</v>
       </c>
       <c r="M32">
-        <v>405.2338445195884</v>
+        <v>399.5786945195885</v>
       </c>
       <c r="N32">
-        <v>2595.066155480412</v>
+        <v>2600.721305480412</v>
       </c>
       <c r="O32">
-        <v>570.9145542056906</v>
+        <v>572.1586872056905</v>
       </c>
       <c r="P32">
-        <v>2024.151601274721</v>
+        <v>2028.562618274721</v>
       </c>
       <c r="Q32">
-        <v>3050.451601274721</v>
+        <v>3054.862618274721</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.112588668082703</v>
+        <v>0.112573594442424</v>
       </c>
       <c r="T32">
         <v>0.9716371602875757</v>
       </c>
       <c r="U32">
-        <v>0.07165748822216714</v>
+        <v>0.07065748822216714</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.05589284081329037</v>
+        <v>0.05511284081329037</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.403873197108959</v>
+        <v>7.508658597544212</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09557072566670657</v>
+        <v>0.09531839897226504</v>
       </c>
       <c r="C33">
-        <v>13246.67000585621</v>
+        <v>13309.50070333672</v>
       </c>
       <c r="D33">
-        <v>15716.92500585621</v>
+        <v>15779.75570333672</v>
       </c>
       <c r="E33">
         <v>-707.9450000000006</v>
@@ -3999,37 +3999,37 @@
         <v>3000.3</v>
       </c>
       <c r="M33">
-        <v>418.7416393369081</v>
+        <v>412.8979843369081</v>
       </c>
       <c r="N33">
-        <v>2581.558360663092</v>
+        <v>2587.402015663092</v>
       </c>
       <c r="O33">
-        <v>567.9428393458803</v>
+        <v>569.2284434458803</v>
       </c>
       <c r="P33">
-        <v>2013.615521317212</v>
+        <v>2018.173572217212</v>
       </c>
       <c r="Q33">
-        <v>3039.915521317212</v>
+        <v>3044.473572217212</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1133970217602704</v>
+        <v>0.1133817656813696</v>
       </c>
       <c r="T33">
         <v>0.9833970365409399</v>
       </c>
       <c r="U33">
-        <v>0.07165748822216714</v>
+        <v>0.07065748822216714</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.05589284081329037</v>
+        <v>0.05511284081329037</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.16503857784738</v>
+        <v>7.266443804075045</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09556153143153398</v>
+        <v>0.0953014295908462</v>
       </c>
       <c r="C34">
-        <v>13060.54390701622</v>
+        <v>13125.42212110988</v>
       </c>
       <c r="D34">
-        <v>15719.30390701622</v>
+        <v>15784.18212110988</v>
       </c>
       <c r="E34">
         <v>-519.4400000000005</v>
@@ -4081,37 +4081,37 @@
         <v>3000.3</v>
       </c>
       <c r="M34">
-        <v>432.2494341542277</v>
+        <v>426.2172741542277</v>
       </c>
       <c r="N34">
-        <v>2568.050565845772</v>
+        <v>2574.082725845773</v>
       </c>
       <c r="O34">
-        <v>564.9711244860699</v>
+        <v>566.29819968607</v>
       </c>
       <c r="P34">
-        <v>2003.079441359702</v>
+        <v>2007.784526159703</v>
       </c>
       <c r="Q34">
-        <v>3029.379441359702</v>
+        <v>3034.084526159702</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1142291505460016</v>
+        <v>0.1142137066626372</v>
       </c>
       <c r="T34">
         <v>0.9955027915076384</v>
       </c>
       <c r="U34">
-        <v>0.07165748822216714</v>
+        <v>0.07065748822216714</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.05589284081329037</v>
+        <v>0.05511284081329037</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.941131122289649</v>
+        <v>7.039367435197699</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09555233719636133</v>
+        <v>0.09528446020942737</v>
       </c>
       <c r="C35">
-        <v>12874.41852842241</v>
+        <v>12941.34602291035</v>
       </c>
       <c r="D35">
-        <v>15721.68352842241</v>
+        <v>15788.61102291035</v>
       </c>
       <c r="E35">
         <v>-330.9350000000004</v>
@@ -4163,37 +4163,37 @@
         <v>3000.3</v>
       </c>
       <c r="M35">
-        <v>445.7572289715473</v>
+        <v>439.5365639715473</v>
       </c>
       <c r="N35">
-        <v>2554.542771028453</v>
+        <v>2560.763436028453</v>
       </c>
       <c r="O35">
-        <v>561.9994096262596</v>
+        <v>563.3679559262596</v>
       </c>
       <c r="P35">
-        <v>1992.543361402193</v>
+        <v>1997.395480102193</v>
       </c>
       <c r="Q35">
-        <v>3018.843361402193</v>
+        <v>3023.695480102193</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1150861189969784</v>
+        <v>0.1150704817030471</v>
       </c>
       <c r="T35">
         <v>1.007969912294238</v>
       </c>
       <c r="U35">
-        <v>0.07165748822216714</v>
+        <v>0.07065748822216714</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.05589284081329037</v>
+        <v>0.05511284081329037</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.730793815553599</v>
+        <v>6.826053270494738</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.0961265829611887</v>
+        <v>0.0957183308280085</v>
       </c>
       <c r="C36">
-        <v>12538.6589249534</v>
+        <v>12640.37856573124</v>
       </c>
       <c r="D36">
-        <v>15574.4289249534</v>
+        <v>15676.14856573124</v>
       </c>
       <c r="E36">
         <v>-142.4300000000003</v>
@@ -4245,37 +4245,37 @@
         <v>3000.3</v>
       </c>
       <c r="M36">
-        <v>473.3651977888669</v>
+        <v>463.7514427888669</v>
       </c>
       <c r="N36">
-        <v>2526.934802211134</v>
+        <v>2536.548557211133</v>
       </c>
       <c r="O36">
-        <v>555.9256564864494</v>
+        <v>558.0406825864493</v>
       </c>
       <c r="P36">
-        <v>1971.009145724684</v>
+        <v>1978.507874624684</v>
       </c>
       <c r="Q36">
-        <v>2997.309145724684</v>
+        <v>3004.807874624684</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1159690561888939</v>
+        <v>0.1159532196234694</v>
       </c>
       <c r="T36">
         <v>1.020814824619826</v>
       </c>
       <c r="U36">
-        <v>0.07385748822216713</v>
+        <v>0.07235748822216713</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.05760884081329037</v>
+        <v>0.05643884081329036</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.338235286444129</v>
+        <v>6.469629467796509</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09613454872601609</v>
+        <v>0.09571462144658968</v>
       </c>
       <c r="C37">
-        <v>12348.13064854011</v>
+        <v>12452.8282740642</v>
       </c>
       <c r="D37">
-        <v>15572.40564854011</v>
+        <v>15677.1032740642</v>
       </c>
       <c r="E37">
         <v>46.07499999999982</v>
@@ -4327,37 +4327,37 @@
         <v>3000.3</v>
       </c>
       <c r="M37">
-        <v>487.2877036061865</v>
+        <v>477.3911911061865</v>
       </c>
       <c r="N37">
-        <v>2513.012296393814</v>
+        <v>2522.908808893814</v>
       </c>
       <c r="O37">
-        <v>552.862705206639</v>
+        <v>555.0399379566391</v>
       </c>
       <c r="P37">
-        <v>1960.149591187175</v>
+        <v>1967.868870937175</v>
       </c>
       <c r="Q37">
-        <v>2986.449591187175</v>
+        <v>2994.168870937175</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1168791606790223</v>
+        <v>0.1168631187106739</v>
       </c>
       <c r="T37">
         <v>1.03405496501697</v>
       </c>
       <c r="U37">
-        <v>0.07385748822216713</v>
+        <v>0.07235748822216713</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.05760884081329037</v>
+        <v>0.05643884081329036</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.157142849688582</v>
+        <v>6.284782911573752</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09614251449084346</v>
+        <v>0.09571091206517082</v>
       </c>
       <c r="C38">
-        <v>12157.60289774683</v>
+        <v>12265.2780986915</v>
       </c>
       <c r="D38">
-        <v>15570.38289774683</v>
+        <v>15678.0580986915</v>
       </c>
       <c r="E38">
         <v>234.579999999999</v>
@@ -4409,37 +4409,37 @@
         <v>3000.3</v>
       </c>
       <c r="M38">
-        <v>501.2102094235061</v>
+        <v>491.0309394235061</v>
       </c>
       <c r="N38">
-        <v>2499.089790576494</v>
+        <v>2509.269060576494</v>
       </c>
       <c r="O38">
-        <v>549.7997539268287</v>
+        <v>552.0391933268287</v>
       </c>
       <c r="P38">
-        <v>1949.290036649666</v>
+        <v>1957.229867249665</v>
       </c>
       <c r="Q38">
-        <v>2975.590036649665</v>
+        <v>2983.529867249665</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1178177059344671</v>
+        <v>0.1178014521443536</v>
       </c>
       <c r="T38">
         <v>1.047708859801525</v>
       </c>
       <c r="U38">
-        <v>0.07385748822216713</v>
+        <v>0.07235748822216713</v>
       </c>
       <c r="V38">
         <v>0.22</v>
       </c>
       <c r="W38">
-        <v>0.05760884081329037</v>
+        <v>0.05643884081329036</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.986111103863899</v>
+        <v>6.110205608474482</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09615048025567086</v>
+        <v>0.09570720268375199</v>
       </c>
       <c r="C39">
-        <v>11967.07567236876</v>
+        <v>12077.72803963436</v>
       </c>
       <c r="D39">
-        <v>15568.36067236876</v>
+        <v>15679.01303963436</v>
       </c>
       <c r="E39">
         <v>423.0849999999991</v>
@@ -4491,37 +4491,37 @@
         <v>3000.3</v>
       </c>
       <c r="M39">
-        <v>515.1327152408257</v>
+        <v>504.6706877408257</v>
       </c>
       <c r="N39">
-        <v>2485.167284759174</v>
+        <v>2495.629312259175</v>
       </c>
       <c r="O39">
-        <v>546.7368026470184</v>
+        <v>549.0384486970185</v>
       </c>
       <c r="P39">
-        <v>1938.430482112156</v>
+        <v>1946.590863562156</v>
       </c>
       <c r="Q39">
-        <v>2964.730482112156</v>
+        <v>2972.890863562156</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1187860462773864</v>
+        <v>0.1187695739410072</v>
       </c>
       <c r="T39">
         <v>1.061796211563368</v>
       </c>
       <c r="U39">
-        <v>0.07385748822216713</v>
+        <v>0.07235748822216713</v>
       </c>
       <c r="V39">
         <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.05760884081329037</v>
+        <v>0.05643884081329036</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.824324317272983</v>
+        <v>5.94506491635355</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09615844602049822</v>
+        <v>0.09570349330233315</v>
       </c>
       <c r="C40">
-        <v>11776.5489722012</v>
+        <v>11890.17809691405</v>
       </c>
       <c r="D40">
-        <v>15566.3389722012</v>
+        <v>15679.96809691405</v>
       </c>
       <c r="E40">
         <v>611.5900000000001</v>
@@ -4573,37 +4573,37 @@
         <v>3000.3</v>
       </c>
       <c r="M40">
-        <v>529.0552210581454</v>
+        <v>518.3104360581453</v>
       </c>
       <c r="N40">
-        <v>2471.244778941855</v>
+        <v>2481.989563941855</v>
       </c>
       <c r="O40">
-        <v>543.673851367208</v>
+        <v>546.037704067208</v>
       </c>
       <c r="P40">
-        <v>1927.570927574647</v>
+        <v>1935.951859874647</v>
       </c>
       <c r="Q40">
-        <v>2953.870927574646</v>
+        <v>2962.251859874646</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1197856234055611</v>
+        <v>0.1197689254730368</v>
       </c>
       <c r="T40">
         <v>1.076337994027205</v>
       </c>
       <c r="U40">
-        <v>0.07385748822216713</v>
+        <v>0.07235748822216713</v>
       </c>
       <c r="V40">
         <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.05760884081329037</v>
+        <v>0.05643884081329036</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.671052624713166</v>
+        <v>5.788615839607402</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09662271178532558</v>
+        <v>0.09569978392091429</v>
       </c>
       <c r="C41">
-        <v>11471.11424956059</v>
+        <v>11702.62827055182</v>
       </c>
       <c r="D41">
-        <v>15449.40924956058</v>
+        <v>15680.92327055182</v>
       </c>
       <c r="E41">
         <v>800.0950000000003</v>
@@ -4655,45 +4655,45 @@
         <v>3000.3</v>
       </c>
       <c r="M41">
-        <v>554.005269375465</v>
+        <v>531.950184375465</v>
       </c>
       <c r="N41">
-        <v>2446.294730624535</v>
+        <v>2468.349815624535</v>
       </c>
       <c r="O41">
-        <v>538.1848407373977</v>
+        <v>543.0369594373977</v>
       </c>
       <c r="P41">
-        <v>1908.109889887137</v>
+        <v>1925.312856187137</v>
       </c>
       <c r="Q41">
-        <v>2934.409889887137</v>
+        <v>2951.612856187137</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1208179735543317</v>
+        <v>0.1208010426290673</v>
       </c>
       <c r="T41">
         <v>1.091356556243956</v>
       </c>
       <c r="U41">
-        <v>0.07535748822216713</v>
+        <v>0.07235748822216713</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.05877884081329036</v>
+        <v>0.05643884081329036</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>5.415652460097112</v>
+        <v>5.640189792437981</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09664237755015295</v>
+        <v>0.09594567453949544</v>
       </c>
       <c r="C42">
-        <v>11277.69500992465</v>
+        <v>11451.05672335466</v>
       </c>
       <c r="D42">
-        <v>15444.49500992465</v>
+        <v>15617.85672335466</v>
       </c>
       <c r="E42">
         <v>988.6000000000004</v>
@@ -4737,37 +4737,37 @@
         <v>3000.3</v>
       </c>
       <c r="M42">
-        <v>568.2105326927847</v>
+        <v>551.6220926927847</v>
       </c>
       <c r="N42">
-        <v>2432.089467307215</v>
+        <v>2448.677907307216</v>
       </c>
       <c r="O42">
-        <v>535.0596828075874</v>
+        <v>538.7091396075874</v>
       </c>
       <c r="P42">
-        <v>1897.029784499628</v>
+        <v>1909.968767699628</v>
       </c>
       <c r="Q42">
-        <v>2923.329784499628</v>
+        <v>2936.268767699628</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.121884735374728</v>
+        <v>0.1218675636902988</v>
       </c>
       <c r="T42">
         <v>1.106875737201264</v>
       </c>
       <c r="U42">
-        <v>0.07535748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V42">
         <v>0.22</v>
       </c>
       <c r="W42">
-        <v>0.05877884081329036</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.280261148594683</v>
+        <v>5.439049740291964</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09666204331498032</v>
+        <v>0.0959482051580766</v>
       </c>
       <c r="C43">
-        <v>11084.27889559552</v>
+        <v>11261.90530211684</v>
       </c>
       <c r="D43">
-        <v>15439.58389559552</v>
+        <v>15617.21030211685</v>
       </c>
       <c r="E43">
         <v>1177.105</v>
@@ -4819,37 +4819,37 @@
         <v>3000.3</v>
       </c>
       <c r="M43">
-        <v>582.4157960101043</v>
+        <v>565.4126450101044</v>
       </c>
       <c r="N43">
-        <v>2417.884203989896</v>
+        <v>2434.887354989896</v>
       </c>
       <c r="O43">
-        <v>531.9345248777771</v>
+        <v>535.6752180977771</v>
       </c>
       <c r="P43">
-        <v>1885.949679112119</v>
+        <v>1899.212136892119</v>
       </c>
       <c r="Q43">
-        <v>2912.249679112118</v>
+        <v>2925.512136892118</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1229876586127649</v>
+        <v>0.1229702380078433</v>
       </c>
       <c r="T43">
         <v>1.122920992089329</v>
       </c>
       <c r="U43">
-        <v>0.07535748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V43">
         <v>0.22</v>
       </c>
       <c r="W43">
-        <v>0.05877884081329036</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.151474291311887</v>
+        <v>5.306389990528745</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09668170907980772</v>
+        <v>0.09595073577665778</v>
       </c>
       <c r="C44">
-        <v>10890.86590359275</v>
+        <v>11072.75393438741</v>
       </c>
       <c r="D44">
-        <v>15434.67590359275</v>
+        <v>15616.56393438741</v>
       </c>
       <c r="E44">
         <v>1365.61</v>
@@ -4901,37 +4901,37 @@
         <v>3000.3</v>
       </c>
       <c r="M44">
-        <v>596.6210593274238</v>
+        <v>579.2031973274239</v>
       </c>
       <c r="N44">
-        <v>2403.678940672577</v>
+        <v>2421.096802672576</v>
       </c>
       <c r="O44">
-        <v>528.8093669479669</v>
+        <v>532.6412965879668</v>
       </c>
       <c r="P44">
-        <v>1874.86957372461</v>
+        <v>1888.45550608461</v>
       </c>
       <c r="Q44">
-        <v>2901.16957372461</v>
+        <v>2914.755506084609</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1241286136865961</v>
+        <v>0.1241109355777169</v>
       </c>
       <c r="T44">
         <v>1.139519531628706</v>
       </c>
       <c r="U44">
-        <v>0.07535748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.05877884081329036</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.028820141518747</v>
+        <v>5.180047371706633</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.0967013748446351</v>
+        <v>0.09595326639523892</v>
       </c>
       <c r="C45">
-        <v>10697.45603093966</v>
+        <v>10883.60262015972</v>
       </c>
       <c r="D45">
-        <v>15429.77103093966</v>
+        <v>15615.91762015971</v>
       </c>
       <c r="E45">
         <v>1554.115</v>
@@ -4983,37 +4983,37 @@
         <v>3000.3</v>
       </c>
       <c r="M45">
-        <v>610.8263226447434</v>
+        <v>592.9937496447435</v>
       </c>
       <c r="N45">
-        <v>2389.473677355257</v>
+        <v>2407.306250355256</v>
       </c>
       <c r="O45">
-        <v>525.6842090181565</v>
+        <v>529.6073750781565</v>
       </c>
       <c r="P45">
-        <v>1863.7894683371</v>
+        <v>1877.6988752771</v>
       </c>
       <c r="Q45">
-        <v>2890.0894683371</v>
+        <v>2903.9988752771</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1253096022717899</v>
+        <v>0.1252916576237264</v>
       </c>
       <c r="T45">
         <v>1.156700476064202</v>
       </c>
       <c r="U45">
-        <v>0.07535748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.05877884081329036</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.911870835902032</v>
+        <v>5.059581153759966</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09672104060946249</v>
+        <v>0.09595579701382009</v>
       </c>
       <c r="C46">
-        <v>10504.04927466339</v>
+        <v>10694.45135942711</v>
       </c>
       <c r="D46">
-        <v>15424.86927466339</v>
+        <v>15615.27135942711</v>
       </c>
       <c r="E46">
         <v>1742.619999999999</v>
@@ -5065,37 +5065,37 @@
         <v>3000.3</v>
       </c>
       <c r="M46">
-        <v>625.031585962063</v>
+        <v>606.7843019620631</v>
       </c>
       <c r="N46">
-        <v>2375.268414037937</v>
+        <v>2393.515698037937</v>
       </c>
       <c r="O46">
-        <v>522.5590510883461</v>
+        <v>526.5734535683462</v>
       </c>
       <c r="P46">
-        <v>1852.709362949591</v>
+        <v>1866.942244469591</v>
       </c>
       <c r="Q46">
-        <v>2879.00936294959</v>
+        <v>2893.24224446959</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1265327690207406</v>
+        <v>0.1265145483142363</v>
       </c>
       <c r="T46">
         <v>1.174495025658108</v>
       </c>
       <c r="U46">
-        <v>0.07535748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V46">
         <v>0.22</v>
       </c>
       <c r="W46">
-        <v>0.05877884081329036</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.800237407813349</v>
+        <v>4.944590672992695</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09674070637428986</v>
+        <v>0.09595832763240125</v>
       </c>
       <c r="C47">
-        <v>10310.64563179483</v>
+        <v>10505.30015218297</v>
       </c>
       <c r="D47">
-        <v>15419.97063179483</v>
+        <v>15614.62515218297</v>
       </c>
       <c r="E47">
         <v>1931.125</v>
@@ -5147,37 +5147,37 @@
         <v>3000.3</v>
       </c>
       <c r="M47">
-        <v>639.2368492793827</v>
+        <v>620.5748542793827</v>
       </c>
       <c r="N47">
-        <v>2361.063150720618</v>
+        <v>2379.725145720618</v>
       </c>
       <c r="O47">
-        <v>519.4338931585359</v>
+        <v>523.5395320585359</v>
       </c>
       <c r="P47">
-        <v>1841.629257562082</v>
+        <v>1856.185613662082</v>
       </c>
       <c r="Q47">
-        <v>2867.929257562082</v>
+        <v>2882.485613662082</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1278004145605622</v>
+        <v>0.1277819077571283</v>
       </c>
       <c r="T47">
         <v>1.192936649782702</v>
       </c>
       <c r="U47">
-        <v>0.07535748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V47">
         <v>0.22</v>
       </c>
       <c r="W47">
-        <v>0.05877884081329036</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.693565465417498</v>
+        <v>4.834710880259523</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09676037213911723</v>
+        <v>0.09596085825098238</v>
       </c>
       <c r="C48">
-        <v>10117.24509936863</v>
+        <v>10316.14899842065</v>
       </c>
       <c r="D48">
-        <v>15415.07509936863</v>
+        <v>15613.97899842065</v>
       </c>
       <c r="E48">
         <v>2119.629999999999</v>
@@ -5229,37 +5229,37 @@
         <v>3000.3</v>
       </c>
       <c r="M48">
-        <v>653.4421125967023</v>
+        <v>634.3654065967023</v>
       </c>
       <c r="N48">
-        <v>2346.857887403298</v>
+        <v>2365.934593403298</v>
       </c>
       <c r="O48">
-        <v>516.3087352287255</v>
+        <v>520.5056105487256</v>
       </c>
       <c r="P48">
-        <v>1830.549152174572</v>
+        <v>1845.428982854572</v>
       </c>
       <c r="Q48">
-        <v>2856.849152174572</v>
+        <v>2871.728982854572</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.129115009935192</v>
+        <v>0.1290962064386459</v>
       </c>
       <c r="T48">
         <v>1.212061297023021</v>
       </c>
       <c r="U48">
-        <v>0.07535748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V48">
         <v>0.22</v>
       </c>
       <c r="W48">
-        <v>0.05877884081329036</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.591531433560595</v>
+        <v>4.7296084698191</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.0967800379039446</v>
+        <v>0.09596338886956354</v>
       </c>
       <c r="C49">
-        <v>9923.847674423239</v>
+        <v>10126.99789813349</v>
       </c>
       <c r="D49">
-        <v>15410.18267442324</v>
+        <v>15613.33289813349</v>
       </c>
       <c r="E49">
         <v>2308.135</v>
@@ -5311,37 +5311,37 @@
         <v>3000.3</v>
       </c>
       <c r="M49">
-        <v>667.6473759140219</v>
+        <v>648.155958914022</v>
       </c>
       <c r="N49">
-        <v>2332.652624085978</v>
+        <v>2352.144041085978</v>
       </c>
       <c r="O49">
-        <v>513.1835772989152</v>
+        <v>517.4716890389152</v>
       </c>
       <c r="P49">
-        <v>1819.469046787063</v>
+        <v>1834.672352047063</v>
       </c>
       <c r="Q49">
-        <v>2845.769046787063</v>
+        <v>2860.972352047062</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1304792126824493</v>
+        <v>0.1304601012968246</v>
       </c>
       <c r="T49">
         <v>1.231907629064863</v>
       </c>
       <c r="U49">
-        <v>0.07535748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V49">
         <v>0.22</v>
       </c>
       <c r="W49">
-        <v>0.05877884081329036</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.493839275399731</v>
+        <v>4.628978502376139</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09679970366877197</v>
+        <v>0.0959659194881447</v>
       </c>
       <c r="C50">
-        <v>9730.45335400084</v>
+        <v>9937.846851314875</v>
       </c>
       <c r="D50">
-        <v>15405.29335400084</v>
+        <v>15612.68685131487</v>
       </c>
       <c r="E50">
         <v>2496.639999999999</v>
@@ -5393,37 +5393,37 @@
         <v>3000.3</v>
       </c>
       <c r="M50">
-        <v>681.8526392313415</v>
+        <v>661.9465112313416</v>
       </c>
       <c r="N50">
-        <v>2318.447360768659</v>
+        <v>2338.353488768659</v>
       </c>
       <c r="O50">
-        <v>510.0584193691049</v>
+        <v>514.4377675291049</v>
       </c>
       <c r="P50">
-        <v>1808.388941399554</v>
+        <v>1823.915721239554</v>
       </c>
       <c r="Q50">
-        <v>2834.688941399553</v>
+        <v>2850.215721239554</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1318958847661396</v>
+        <v>0.1318764536495487</v>
       </c>
       <c r="T50">
         <v>1.252517281569851</v>
       </c>
       <c r="U50">
-        <v>0.07535748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.05877884081329036</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.400217623828904</v>
+        <v>4.532541450243304</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09681936943359937</v>
+        <v>0.09596845010672586</v>
       </c>
       <c r="C51">
-        <v>9537.062135147364</v>
+        <v>9748.695857958159</v>
       </c>
       <c r="D51">
-        <v>15400.40713514736</v>
+        <v>15612.04085795816</v>
       </c>
       <c r="E51">
         <v>2685.144999999999</v>
@@ -5475,37 +5475,37 @@
         <v>3000.3</v>
       </c>
       <c r="M51">
-        <v>696.0579025486611</v>
+        <v>675.7370635486611</v>
       </c>
       <c r="N51">
-        <v>2304.242097451339</v>
+        <v>2324.562936451339</v>
       </c>
       <c r="O51">
-        <v>506.9332614392945</v>
+        <v>511.4038460192945</v>
       </c>
       <c r="P51">
-        <v>1797.308836012044</v>
+        <v>1813.159090432044</v>
       </c>
       <c r="Q51">
-        <v>2823.608836012044</v>
+        <v>2839.459090432044</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1333681126178178</v>
+        <v>0.1333483492317913</v>
       </c>
       <c r="T51">
         <v>1.273935155741702</v>
       </c>
       <c r="U51">
-        <v>0.07535748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V51">
         <v>0.22</v>
       </c>
       <c r="W51">
-        <v>0.05877884081329036</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.310417264158925</v>
+        <v>4.440040604319972</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09738503519842673</v>
+        <v>0.09597098072530699</v>
       </c>
       <c r="C52">
-        <v>9209.324845768173</v>
+        <v>9559.544918056708</v>
       </c>
       <c r="D52">
-        <v>15261.17484576817</v>
+        <v>15611.39491805671</v>
       </c>
       <c r="E52">
         <v>2873.65</v>
@@ -5557,45 +5557,45 @@
         <v>3000.3</v>
       </c>
       <c r="M52">
-        <v>723.4585158659808</v>
+        <v>689.5276158659808</v>
       </c>
       <c r="N52">
-        <v>2276.84148413402</v>
+        <v>2310.772384134019</v>
       </c>
       <c r="O52">
-        <v>500.9051265094843</v>
+        <v>508.3699245094843</v>
       </c>
       <c r="P52">
-        <v>1775.936357624535</v>
+        <v>1802.402459624535</v>
       </c>
       <c r="Q52">
-        <v>2802.236357624535</v>
+        <v>2828.702459624535</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1348992295835631</v>
+        <v>0.1348791206373236</v>
       </c>
       <c r="T52">
         <v>1.296209744880428</v>
       </c>
       <c r="U52">
-        <v>0.07675748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V52">
         <v>0.22</v>
       </c>
       <c r="W52">
-        <v>0.05987084081329037</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.147162462257615</v>
+        <v>4.351239792233571</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09741562096325411</v>
+        <v>0.09597351134388817</v>
       </c>
       <c r="C53">
-        <v>9013.363209981049</v>
+        <v>9370.394031603882</v>
       </c>
       <c r="D53">
-        <v>15253.71820998105</v>
+        <v>15610.74903160388</v>
       </c>
       <c r="E53">
         <v>3062.155000000001</v>
@@ -5639,45 +5639,45 @@
         <v>3000.3</v>
       </c>
       <c r="M53">
-        <v>737.9276861833005</v>
+        <v>703.3181681833005</v>
       </c>
       <c r="N53">
-        <v>2262.3723138167</v>
+        <v>2296.9818318167</v>
       </c>
       <c r="O53">
-        <v>497.721909039674</v>
+        <v>505.336002999674</v>
       </c>
       <c r="P53">
-        <v>1764.650404777026</v>
+        <v>1791.645828817026</v>
       </c>
       <c r="Q53">
-        <v>2790.950404777026</v>
+        <v>2817.945828817025</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1364928411193388</v>
+        <v>0.1364723725083879</v>
       </c>
       <c r="T53">
         <v>1.319393500922774</v>
       </c>
       <c r="U53">
-        <v>0.07675748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.05987084081329037</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.065845551232955</v>
+        <v>4.265921364934874</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09744620672808149</v>
+        <v>0.09638164196246933</v>
       </c>
       <c r="C54">
-        <v>8817.408857285058</v>
+        <v>9078.417113933237</v>
       </c>
       <c r="D54">
-        <v>15246.26885728506</v>
+        <v>15507.27711393324</v>
       </c>
       <c r="E54">
         <v>3250.66</v>
@@ -5721,37 +5721,37 @@
         <v>3000.3</v>
       </c>
       <c r="M54">
-        <v>752.3968565006199</v>
+        <v>726.9109805006201</v>
       </c>
       <c r="N54">
-        <v>2247.90314349938</v>
+        <v>2273.38901949938</v>
       </c>
       <c r="O54">
-        <v>494.5386915698637</v>
+        <v>500.1455842898636</v>
       </c>
       <c r="P54">
-        <v>1753.364451929517</v>
+        <v>1773.243435209517</v>
       </c>
       <c r="Q54">
-        <v>2779.664451929516</v>
+        <v>2799.543435209516</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1381528531357719</v>
+        <v>0.1381320098740799</v>
       </c>
       <c r="T54">
         <v>1.343543246800219</v>
       </c>
       <c r="U54">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V54">
         <v>0.22</v>
       </c>
       <c r="W54">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.987656213709245</v>
+        <v>4.1274655088216</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09747679249290886</v>
+        <v>0.09639197258105048</v>
       </c>
       <c r="C55">
-        <v>8621.461777015031</v>
+        <v>8887.310824981812</v>
       </c>
       <c r="D55">
-        <v>15238.82677701503</v>
+        <v>15504.67582498181</v>
       </c>
       <c r="E55">
         <v>3439.165000000001</v>
@@ -5803,37 +5803,37 @@
         <v>3000.3</v>
       </c>
       <c r="M55">
-        <v>766.8660268179397</v>
+        <v>740.8900378179397</v>
       </c>
       <c r="N55">
-        <v>2233.433973182061</v>
+        <v>2259.409962182061</v>
       </c>
       <c r="O55">
-        <v>491.3554741000533</v>
+        <v>497.0701916800533</v>
       </c>
       <c r="P55">
-        <v>1742.078499082007</v>
+        <v>1762.339770502007</v>
       </c>
       <c r="Q55">
-        <v>2768.378499082007</v>
+        <v>2788.639770502007</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1398835039614148</v>
+        <v>0.139862270106397</v>
       </c>
       <c r="T55">
         <v>1.368720641438405</v>
       </c>
       <c r="U55">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V55">
         <v>0.22</v>
       </c>
       <c r="W55">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.912417417224164</v>
+        <v>4.049588801107985</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09750737825773623</v>
+        <v>0.09640230319963163</v>
       </c>
       <c r="C56">
-        <v>8425.521958526606</v>
+        <v>8696.205408597416</v>
       </c>
       <c r="D56">
-        <v>15231.39195852661</v>
+        <v>15502.07540859741</v>
       </c>
       <c r="E56">
         <v>3627.67</v>
@@ -5885,37 +5885,37 @@
         <v>3000.3</v>
       </c>
       <c r="M56">
-        <v>781.3351971352592</v>
+        <v>754.8690951352594</v>
       </c>
       <c r="N56">
-        <v>2218.964802864741</v>
+        <v>2245.430904864741</v>
       </c>
       <c r="O56">
-        <v>488.1722566302429</v>
+        <v>493.994799070243</v>
       </c>
       <c r="P56">
-        <v>1730.792546234498</v>
+        <v>1751.436105794498</v>
       </c>
       <c r="Q56">
-        <v>2757.092546234498</v>
+        <v>2777.736105794498</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1416894004751292</v>
+        <v>0.141667759044467</v>
       </c>
       <c r="T56">
         <v>1.394992705408687</v>
       </c>
       <c r="U56">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V56">
         <v>0.22</v>
       </c>
       <c r="W56">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.839965242831124</v>
+        <v>3.974596415902282</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.09753796402256362</v>
+        <v>0.09641263381821279</v>
       </c>
       <c r="C57">
-        <v>8229.58939119619</v>
+        <v>8505.100864341075</v>
       </c>
       <c r="D57">
-        <v>15223.96439119619</v>
+        <v>15499.47586434108</v>
       </c>
       <c r="E57">
         <v>3816.175000000001</v>
@@ -5967,37 +5967,37 @@
         <v>3000.3</v>
       </c>
       <c r="M57">
-        <v>795.804367452579</v>
+        <v>768.848152452579</v>
       </c>
       <c r="N57">
-        <v>2204.495632547421</v>
+        <v>2231.451847547421</v>
       </c>
       <c r="O57">
-        <v>484.9890391604327</v>
+        <v>490.9194064604326</v>
       </c>
       <c r="P57">
-        <v>1719.506593386989</v>
+        <v>1740.532441086988</v>
       </c>
       <c r="Q57">
-        <v>2745.806593386988</v>
+        <v>2766.832441086988</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1435755590561198</v>
+        <v>0.1435534919353402</v>
       </c>
       <c r="T57">
         <v>1.422432416666537</v>
       </c>
       <c r="U57">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V57">
         <v>0.22</v>
       </c>
       <c r="W57">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.770147692961467</v>
+        <v>3.90233102652224</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09756854978739099</v>
+        <v>0.09642296443679393</v>
       </c>
       <c r="C58">
-        <v>8033.664064420909</v>
+        <v>8313.99719177413</v>
       </c>
       <c r="D58">
-        <v>15216.54406442091</v>
+        <v>15496.87719177413</v>
       </c>
       <c r="E58">
         <v>4004.68</v>
@@ -6049,37 +6049,37 @@
         <v>3000.3</v>
       </c>
       <c r="M58">
-        <v>810.2735377698984</v>
+        <v>782.8272097698986</v>
       </c>
       <c r="N58">
-        <v>2190.026462230102</v>
+        <v>2217.472790230102</v>
       </c>
       <c r="O58">
-        <v>481.8058216906225</v>
+        <v>487.8440138506223</v>
       </c>
       <c r="P58">
-        <v>1708.22064053948</v>
+        <v>1729.628776379479</v>
       </c>
       <c r="Q58">
-        <v>2734.520640539479</v>
+        <v>2755.928776379479</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1455474521180645</v>
+        <v>0.1455249399576167</v>
       </c>
       <c r="T58">
         <v>1.451119387527016</v>
       </c>
       <c r="U58">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V58">
         <v>0.22</v>
       </c>
       <c r="W58">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.702823627015727</v>
+        <v>3.832646543905772</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09759913555221836</v>
+        <v>0.0964332950553751</v>
       </c>
       <c r="C59">
-        <v>7837.745967618537</v>
+        <v>8122.894390458192</v>
       </c>
       <c r="D59">
-        <v>15209.13096761854</v>
+        <v>15494.27939045819</v>
       </c>
       <c r="E59">
         <v>4193.185000000001</v>
@@ -6131,37 +6131,37 @@
         <v>3000.3</v>
       </c>
       <c r="M59">
-        <v>824.7427080872181</v>
+        <v>796.8062670872183</v>
       </c>
       <c r="N59">
-        <v>2175.557291912782</v>
+        <v>2203.493732912782</v>
       </c>
       <c r="O59">
-        <v>478.6226042208121</v>
+        <v>484.768621240812</v>
       </c>
       <c r="P59">
-        <v>1696.93468769197</v>
+        <v>1718.72511167197</v>
       </c>
       <c r="Q59">
-        <v>2723.23468769197</v>
+        <v>2745.02511167197</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1476110611363788</v>
+        <v>0.1475880832367432</v>
       </c>
       <c r="T59">
         <v>1.481140636101936</v>
       </c>
       <c r="U59">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V59">
         <v>0.22</v>
       </c>
       <c r="W59">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.637861808997907</v>
+        <v>3.765407130854793</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.09762972131704574</v>
+        <v>0.09644362567395626</v>
       </c>
       <c r="C60">
-        <v>7641.835090227471</v>
+        <v>7931.792459955204</v>
       </c>
       <c r="D60">
-        <v>15201.72509022747</v>
+        <v>15491.6824599552</v>
       </c>
       <c r="E60">
         <v>4381.689999999999</v>
@@ -6213,37 +6213,37 @@
         <v>3000.3</v>
       </c>
       <c r="M60">
-        <v>839.2118784045376</v>
+        <v>810.7853244045377</v>
       </c>
       <c r="N60">
-        <v>2161.088121595462</v>
+        <v>2189.514675595462</v>
       </c>
       <c r="O60">
-        <v>475.4393867510017</v>
+        <v>481.6932286310017</v>
       </c>
       <c r="P60">
-        <v>1685.648734844461</v>
+        <v>1707.821446964461</v>
       </c>
       <c r="Q60">
-        <v>2711.94873484446</v>
+        <v>2734.121446964461</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1497729372508032</v>
+        <v>0.1497494714339234</v>
       </c>
       <c r="T60">
         <v>1.512591467942329</v>
       </c>
       <c r="U60">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V60">
         <v>0.22</v>
       </c>
       <c r="W60">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.575140053670357</v>
+        <v>3.700486318253849</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.09766030708187312</v>
+        <v>0.09645395629253742</v>
       </c>
       <c r="C61">
-        <v>7445.931421706651</v>
+        <v>7740.691399827361</v>
       </c>
       <c r="D61">
-        <v>15194.32642170665</v>
+        <v>15489.08639982736</v>
       </c>
       <c r="E61">
         <v>4570.195</v>
@@ -6295,37 +6295,37 @@
         <v>3000.3</v>
       </c>
       <c r="M61">
-        <v>853.6810487218573</v>
+        <v>824.7643817218574</v>
       </c>
       <c r="N61">
-        <v>2146.618951278143</v>
+        <v>2175.535618278143</v>
       </c>
       <c r="O61">
-        <v>472.2561692811914</v>
+        <v>478.6178360211915</v>
       </c>
       <c r="P61">
-        <v>1674.362781996952</v>
+        <v>1696.917782256951</v>
       </c>
       <c r="Q61">
-        <v>2700.662781996951</v>
+        <v>2723.217782256951</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1520402707366629</v>
+        <v>0.1520162932016978</v>
       </c>
       <c r="T61">
         <v>1.545576486701765</v>
       </c>
       <c r="U61">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V61">
         <v>0.22</v>
       </c>
       <c r="W61">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.514544459540351</v>
+        <v>3.6377662111648</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.09769089284670049</v>
+        <v>0.09646428691111855</v>
       </c>
       <c r="C62">
-        <v>7250.034951535563</v>
+        <v>7549.591209637183</v>
       </c>
       <c r="D62">
-        <v>15186.93495153556</v>
+        <v>15486.49120963718</v>
       </c>
       <c r="E62">
         <v>4758.699999999999</v>
@@ -6377,37 +6377,37 @@
         <v>3000.3</v>
       </c>
       <c r="M62">
-        <v>868.1502190391768</v>
+        <v>838.7434390391769</v>
       </c>
       <c r="N62">
-        <v>2132.149780960824</v>
+        <v>2161.556560960823</v>
       </c>
       <c r="O62">
-        <v>469.0729518113812</v>
+        <v>475.5424434113812</v>
       </c>
       <c r="P62">
-        <v>1663.076829149442</v>
+        <v>1686.014117549442</v>
       </c>
       <c r="Q62">
-        <v>2689.376829149442</v>
+        <v>2712.314117549442</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1544209708968157</v>
+        <v>0.1543964560578608</v>
       </c>
       <c r="T62">
         <v>1.580210756399173</v>
       </c>
       <c r="U62">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V62">
         <v>0.22</v>
       </c>
       <c r="W62">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.455968718548013</v>
+        <v>3.577136774312054</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.09772147861152786</v>
+        <v>0.09647461752969971</v>
       </c>
       <c r="C63">
-        <v>7054.145669214118</v>
+        <v>7358.491888947457</v>
       </c>
       <c r="D63">
-        <v>15179.55066921412</v>
+        <v>15483.89688894746</v>
       </c>
       <c r="E63">
         <v>4947.205</v>
@@ -6459,37 +6459,37 @@
         <v>3000.3</v>
       </c>
       <c r="M63">
-        <v>882.6193893564965</v>
+        <v>852.7224963564967</v>
       </c>
       <c r="N63">
-        <v>2117.680610643504</v>
+        <v>2147.577503643503</v>
       </c>
       <c r="O63">
-        <v>465.8897343415708</v>
+        <v>472.4670508015707</v>
       </c>
       <c r="P63">
-        <v>1651.790876301933</v>
+        <v>1675.110452841933</v>
       </c>
       <c r="Q63">
-        <v>2678.090876301932</v>
+        <v>2701.410452841933</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1569237582446686</v>
+        <v>0.1568986785476733</v>
       </c>
       <c r="T63">
         <v>1.616621142491319</v>
       </c>
       <c r="U63">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V63">
         <v>0.22</v>
       </c>
       <c r="W63">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.399313493653783</v>
+        <v>3.518495187847921</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.09775206437635525</v>
+        <v>0.09648494814828087</v>
       </c>
       <c r="C64">
-        <v>6858.263564262654</v>
+        <v>7167.393437321281</v>
       </c>
       <c r="D64">
-        <v>15172.17356426265</v>
+        <v>15481.30343732128</v>
       </c>
       <c r="E64">
         <v>5135.709999999999</v>
@@ -6541,37 +6541,37 @@
         <v>3000.3</v>
       </c>
       <c r="M64">
-        <v>897.0885596738161</v>
+        <v>866.7015536738162</v>
       </c>
       <c r="N64">
-        <v>2103.211440326184</v>
+        <v>2133.598446326184</v>
       </c>
       <c r="O64">
-        <v>462.7065168717605</v>
+        <v>469.3916581917604</v>
       </c>
       <c r="P64">
-        <v>1640.504923454424</v>
+        <v>1664.206788134424</v>
       </c>
       <c r="Q64">
-        <v>2666.804923454423</v>
+        <v>2690.506788134423</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1595582712424085</v>
+        <v>0.1595325969580022</v>
       </c>
       <c r="T64">
         <v>1.65494786469358</v>
       </c>
       <c r="U64">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V64">
         <v>0.22</v>
       </c>
       <c r="W64">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.344485856659366</v>
+        <v>3.461745265463278</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.09778265014118262</v>
+        <v>0.09649527876686202</v>
       </c>
       <c r="C65">
-        <v>6662.388626221878</v>
+        <v>6976.295854322047</v>
       </c>
       <c r="D65">
-        <v>15164.80362622188</v>
+        <v>15478.71085432205</v>
       </c>
       <c r="E65">
         <v>5324.215</v>
@@ -6623,37 +6623,37 @@
         <v>3000.3</v>
       </c>
       <c r="M65">
-        <v>911.5577299911358</v>
+        <v>880.6806109911358</v>
       </c>
       <c r="N65">
-        <v>2088.742270008865</v>
+        <v>2119.619389008864</v>
       </c>
       <c r="O65">
-        <v>459.5232994019502</v>
+        <v>466.3162655819502</v>
       </c>
       <c r="P65">
-        <v>1629.218970606914</v>
+        <v>1653.303123426914</v>
       </c>
       <c r="Q65">
-        <v>2655.518970606914</v>
+        <v>2679.603123426914</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1623351903481343</v>
+        <v>0.162308889336457</v>
       </c>
       <c r="T65">
         <v>1.695346301609475</v>
       </c>
       <c r="U65">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V65">
         <v>0.22</v>
       </c>
       <c r="W65">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.291398779569535</v>
+        <v>3.406796927916242</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.09781323590600999</v>
+        <v>0.09650560938544318</v>
       </c>
       <c r="C66">
-        <v>6466.520844652801</v>
+        <v>6785.199139513428</v>
       </c>
       <c r="D66">
-        <v>15157.4408446528</v>
+        <v>15476.11913951343</v>
       </c>
       <c r="E66">
         <v>5512.719999999999</v>
@@ -6705,37 +6705,37 @@
         <v>3000.3</v>
       </c>
       <c r="M66">
-        <v>926.0269003084553</v>
+        <v>894.6596683084555</v>
       </c>
       <c r="N66">
-        <v>2074.273099691545</v>
+        <v>2105.640331691545</v>
       </c>
       <c r="O66">
-        <v>456.3400819321399</v>
+        <v>463.2408729721399</v>
       </c>
       <c r="P66">
-        <v>1617.933017759405</v>
+        <v>1642.399458719405</v>
       </c>
       <c r="Q66">
-        <v>2644.233017759405</v>
+        <v>2668.699458719405</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1652663827375116</v>
+        <v>0.1652394201803815</v>
       </c>
       <c r="T66">
         <v>1.737989096131809</v>
       </c>
       <c r="U66">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V66">
         <v>0.22</v>
       </c>
       <c r="W66">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.239970673638761</v>
+        <v>3.35356572591755</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.09784382167083737</v>
+        <v>0.09651594000402433</v>
       </c>
       <c r="C67">
-        <v>6270.660209136691</v>
+        <v>6594.103292459396</v>
       </c>
       <c r="D67">
-        <v>15150.08520913669</v>
+        <v>15473.5282924594</v>
       </c>
       <c r="E67">
         <v>5701.225</v>
@@ -6787,37 +6787,37 @@
         <v>3000.3</v>
       </c>
       <c r="M67">
-        <v>940.496070625775</v>
+        <v>908.6387256257751</v>
       </c>
       <c r="N67">
-        <v>2059.803929374225</v>
+        <v>2091.661274374225</v>
       </c>
       <c r="O67">
-        <v>453.1568644623295</v>
+        <v>460.1654803623296</v>
       </c>
       <c r="P67">
-        <v>1606.647064911896</v>
+        <v>1631.495794011896</v>
       </c>
       <c r="Q67">
-        <v>2632.947064911895</v>
+        <v>2657.795794011895</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1683650718348532</v>
+        <v>0.1683374099296731</v>
       </c>
       <c r="T67">
         <v>1.783068621769705</v>
       </c>
       <c r="U67">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V67">
         <v>0.22</v>
       </c>
       <c r="W67">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.190124970967395</v>
+        <v>3.30197240705728</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.09787440743566475</v>
+        <v>0.09652627062260549</v>
       </c>
       <c r="C68">
-        <v>6074.806709275048</v>
+        <v>6403.008312724209</v>
       </c>
       <c r="D68">
-        <v>15142.73670927505</v>
+        <v>15470.93831272421</v>
       </c>
       <c r="E68">
         <v>5889.73</v>
@@ -6869,37 +6869,37 @@
         <v>3000.3</v>
       </c>
       <c r="M68">
-        <v>954.9652409430946</v>
+        <v>922.6177829430947</v>
       </c>
       <c r="N68">
-        <v>2045.334759056906</v>
+        <v>2077.682217056906</v>
       </c>
       <c r="O68">
-        <v>449.9736469925192</v>
+        <v>457.0900877525193</v>
       </c>
       <c r="P68">
-        <v>1595.361112064386</v>
+        <v>1620.592129304387</v>
       </c>
       <c r="Q68">
-        <v>2621.661112064386</v>
+        <v>2646.892129304386</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1716460367614503</v>
+        <v>0.1716176343700996</v>
       </c>
       <c r="T68">
         <v>1.830799884209831</v>
       </c>
       <c r="U68">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V68">
         <v>0.22</v>
       </c>
       <c r="W68">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.141789744134556</v>
+        <v>3.251942522101867</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.09790499320049215</v>
+        <v>0.09653660124118665</v>
       </c>
       <c r="C69">
-        <v>5878.960334689518</v>
+        <v>6211.914199872424</v>
       </c>
       <c r="D69">
-        <v>15135.39533468952</v>
+        <v>15468.34919987242</v>
       </c>
       <c r="E69">
         <v>6078.235000000001</v>
@@ -6951,37 +6951,37 @@
         <v>3000.3</v>
       </c>
       <c r="M69">
-        <v>969.4344112604143</v>
+        <v>936.5968402604144</v>
       </c>
       <c r="N69">
-        <v>2030.865588739586</v>
+        <v>2063.703159739586</v>
       </c>
       <c r="O69">
-        <v>446.7904295227088</v>
+        <v>454.0146951427089</v>
       </c>
       <c r="P69">
-        <v>1584.075159216877</v>
+        <v>1609.688464596877</v>
       </c>
       <c r="Q69">
-        <v>2610.375159216876</v>
+        <v>2635.988464596877</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1751258480472351</v>
+        <v>0.175096660291764</v>
       </c>
       <c r="T69">
         <v>1.881423950434206</v>
       </c>
       <c r="U69">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V69">
         <v>0.22</v>
       </c>
       <c r="W69">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.094897359893741</v>
+        <v>3.203406066548107</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09793557896531951</v>
+        <v>0.09654693185976781</v>
       </c>
       <c r="C70">
-        <v>5683.121075021889</v>
+        <v>6020.820953468887</v>
       </c>
       <c r="D70">
-        <v>15128.06107502189</v>
+        <v>15465.76095346889</v>
       </c>
       <c r="E70">
         <v>6266.74</v>
@@ -7033,37 +7033,37 @@
         <v>3000.3</v>
       </c>
       <c r="M70">
-        <v>983.9035815777338</v>
+        <v>950.5758975777339</v>
       </c>
       <c r="N70">
-        <v>2016.396418422266</v>
+        <v>2049.724102422266</v>
       </c>
       <c r="O70">
-        <v>443.6072120528986</v>
+        <v>450.9393025328986</v>
       </c>
       <c r="P70">
-        <v>1572.789206369368</v>
+        <v>1598.784799889368</v>
       </c>
       <c r="Q70">
-        <v>2599.089206369367</v>
+        <v>2625.084799889367</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1788231475383815</v>
+        <v>0.1787931253335324</v>
       </c>
       <c r="T70">
         <v>1.935212020797605</v>
       </c>
       <c r="U70">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V70">
         <v>0.22</v>
       </c>
       <c r="W70">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.049384163424717</v>
+        <v>3.156297153804753</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09796616473014688</v>
+        <v>0.09655726247834896</v>
       </c>
       <c r="C71">
-        <v>5487.288919933988</v>
+        <v>5829.728573078733</v>
       </c>
       <c r="D71">
-        <v>15120.73391993399</v>
+        <v>15463.17357307873</v>
       </c>
       <c r="E71">
         <v>6455.245000000001</v>
@@ -7115,37 +7115,37 @@
         <v>3000.3</v>
       </c>
       <c r="M71">
-        <v>998.3727518950535</v>
+        <v>964.5549548950536</v>
       </c>
       <c r="N71">
-        <v>2001.927248104947</v>
+        <v>2035.745045104947</v>
       </c>
       <c r="O71">
-        <v>440.4239945830882</v>
+        <v>447.8639099230883</v>
       </c>
       <c r="P71">
-        <v>1561.503253521858</v>
+        <v>1587.881135181859</v>
       </c>
       <c r="Q71">
-        <v>2587.803253521858</v>
+        <v>2614.181135181858</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1827589824805695</v>
+        <v>0.1827280719908987</v>
       </c>
       <c r="T71">
         <v>1.992470289248965</v>
       </c>
       <c r="U71">
-        <v>0.07675748822216713</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V71">
         <v>0.22</v>
       </c>
       <c r="W71">
-        <v>0.05987084081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.005190190041749</v>
+        <v>3.11055371679309</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09941635049497424</v>
+        <v>0.09656759309693011</v>
       </c>
       <c r="C72">
-        <v>4959.339456585958</v>
+        <v>5638.637058267397</v>
       </c>
       <c r="D72">
-        <v>14781.28945658596</v>
+        <v>15460.5870582674</v>
       </c>
       <c r="E72">
         <v>6643.75</v>
@@ -7197,45 +7197,45 @@
         <v>3000.3</v>
       </c>
       <c r="M72">
-        <v>1047.149832212373</v>
+        <v>978.5340122123732</v>
       </c>
       <c r="N72">
-        <v>1953.150167787627</v>
+        <v>2021.765987787627</v>
       </c>
       <c r="O72">
-        <v>429.693036913278</v>
+        <v>444.7885173132779</v>
       </c>
       <c r="P72">
-        <v>1523.457130874349</v>
+        <v>1576.977470474349</v>
       </c>
       <c r="Q72">
-        <v>2549.757130874349</v>
+        <v>2603.277470474349</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1869572064189033</v>
+        <v>0.1869253484254229</v>
       </c>
       <c r="T72">
         <v>2.053545775597082</v>
       </c>
       <c r="U72">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V72">
         <v>0.22</v>
       </c>
       <c r="W72">
-        <v>0.06189884081329036</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.865206017042562</v>
+        <v>3.066117235124617</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.09946721625980162</v>
+        <v>0.09657792371551127</v>
       </c>
       <c r="C73">
-        <v>4759.204762515958</v>
+        <v>5447.546408600585</v>
       </c>
       <c r="D73">
-        <v>14769.65976251596</v>
+        <v>15458.00140860058</v>
       </c>
       <c r="E73">
         <v>6832.254999999999</v>
@@ -7279,45 +7279,45 @@
         <v>3000.3</v>
       </c>
       <c r="M73">
-        <v>1062.109115529692</v>
+        <v>992.5130695296928</v>
       </c>
       <c r="N73">
-        <v>1938.190884470308</v>
+        <v>2007.786930470307</v>
       </c>
       <c r="O73">
-        <v>426.4019945834677</v>
+        <v>441.7131247034677</v>
       </c>
       <c r="P73">
-        <v>1511.78888988684</v>
+        <v>1566.07380576684</v>
       </c>
       <c r="Q73">
-        <v>2538.08888988684</v>
+        <v>2592.37380576684</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1914449630426396</v>
+        <v>0.191412092200259</v>
       </c>
       <c r="T73">
         <v>2.118833364451965</v>
       </c>
       <c r="U73">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V73">
         <v>0.22</v>
       </c>
       <c r="W73">
-        <v>0.06189884081329036</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.824851002718019</v>
+        <v>3.02293248533413</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.099518082024629</v>
+        <v>0.09799225433409242</v>
       </c>
       <c r="C74">
-        <v>4559.088354192367</v>
+        <v>4913.030345754951</v>
       </c>
       <c r="D74">
-        <v>14758.04835419237</v>
+        <v>15111.99034575495</v>
       </c>
       <c r="E74">
         <v>7020.759999999998</v>
@@ -7361,37 +7361,37 @@
         <v>3000.3</v>
       </c>
       <c r="M74">
-        <v>1077.068398847012</v>
+        <v>1040.423026847012</v>
       </c>
       <c r="N74">
-        <v>1923.231601152988</v>
+        <v>1959.876973152988</v>
       </c>
       <c r="O74">
-        <v>423.1109522536574</v>
+        <v>431.1729340936574</v>
       </c>
       <c r="P74">
-        <v>1500.120648899331</v>
+        <v>1528.704039059331</v>
       </c>
       <c r="Q74">
-        <v>2526.42064889933</v>
+        <v>2555.00403905933</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1962532737109284</v>
+        <v>0.1962193176732977</v>
       </c>
       <c r="T74">
         <v>2.18878435251077</v>
       </c>
       <c r="U74">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V74">
         <v>0.22</v>
       </c>
       <c r="W74">
-        <v>0.06189884081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.785616961013602</v>
+        <v>2.883730869637102</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.09956894778945638</v>
+        <v>0.09802208495267357</v>
       </c>
       <c r="C75">
-        <v>4358.990188522161</v>
+        <v>4717.39411258924</v>
       </c>
       <c r="D75">
-        <v>14746.45518852216</v>
+        <v>15104.85911258924</v>
       </c>
       <c r="E75">
         <v>7209.264999999999</v>
@@ -7443,37 +7443,37 @@
         <v>3000.3</v>
       </c>
       <c r="M75">
-        <v>1092.027682164332</v>
+        <v>1054.873346664332</v>
       </c>
       <c r="N75">
-        <v>1908.272317835668</v>
+        <v>1945.426653335668</v>
       </c>
       <c r="O75">
-        <v>419.819909923847</v>
+        <v>427.993863733847</v>
       </c>
       <c r="P75">
-        <v>1488.452407911821</v>
+        <v>1517.432789601821</v>
       </c>
       <c r="Q75">
-        <v>2514.752407911821</v>
+        <v>2543.732789601821</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2014177555398312</v>
+        <v>0.2013826339221171</v>
       </c>
       <c r="T75">
         <v>2.263916895240597</v>
       </c>
       <c r="U75">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V75">
         <v>0.22</v>
       </c>
       <c r="W75">
-        <v>0.06189884081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.747457824561361</v>
+        <v>2.844227707039333</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09961981355428376</v>
+        <v>0.09805191557125473</v>
       </c>
       <c r="C76">
-        <v>4158.910222547605</v>
+        <v>4521.764606598284</v>
       </c>
       <c r="D76">
-        <v>14734.8802225476</v>
+        <v>15097.73460659828</v>
       </c>
       <c r="E76">
         <v>7397.769999999999</v>
@@ -7525,37 +7525,37 @@
         <v>3000.3</v>
       </c>
       <c r="M76">
-        <v>1106.986965481651</v>
+        <v>1069.323666481651</v>
       </c>
       <c r="N76">
-        <v>1893.313034518349</v>
+        <v>1930.976333518349</v>
       </c>
       <c r="O76">
-        <v>416.5288675940367</v>
+        <v>424.8147933740368</v>
       </c>
       <c r="P76">
-        <v>1476.784166924312</v>
+        <v>1506.161540144312</v>
       </c>
       <c r="Q76">
-        <v>2503.084166924312</v>
+        <v>2532.461540144312</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2069795052017265</v>
+        <v>0.2069431283439225</v>
       </c>
       <c r="T76">
         <v>2.344828864334256</v>
       </c>
       <c r="U76">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V76">
         <v>0.22</v>
       </c>
       <c r="W76">
-        <v>0.06189884081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.710330016121342</v>
+        <v>2.805792197484748</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.09967067931911112</v>
+        <v>0.09808174618983588</v>
       </c>
       <c r="C77">
-        <v>3958.848413445736</v>
+        <v>4326.141818267548</v>
       </c>
       <c r="D77">
-        <v>14723.32341344573</v>
+        <v>15090.61681826755</v>
       </c>
       <c r="E77">
         <v>7586.275</v>
@@ -7607,37 +7607,37 @@
         <v>3000.3</v>
       </c>
       <c r="M77">
-        <v>1121.946248798971</v>
+        <v>1083.773986298971</v>
       </c>
       <c r="N77">
-        <v>1878.353751201029</v>
+        <v>1916.526013701029</v>
       </c>
       <c r="O77">
-        <v>413.2378252642264</v>
+        <v>421.6357230142264</v>
       </c>
       <c r="P77">
-        <v>1465.115925936803</v>
+        <v>1494.890290686803</v>
       </c>
       <c r="Q77">
-        <v>2491.415925936803</v>
+        <v>2521.190290686803</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2129861948365734</v>
+        <v>0.2129484623194725</v>
       </c>
       <c r="T77">
         <v>2.432213790955409</v>
       </c>
       <c r="U77">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V77">
         <v>0.22</v>
       </c>
       <c r="W77">
-        <v>0.06189884081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.674192282573058</v>
+        <v>2.768381634851618</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.0997215450839385</v>
+        <v>0.09811157680841703</v>
       </c>
       <c r="C78">
-        <v>3758.804718527826</v>
+        <v>4130.525738100438</v>
       </c>
       <c r="D78">
-        <v>14711.78471852783</v>
+        <v>15083.50573810044</v>
       </c>
       <c r="E78">
         <v>7774.780000000001</v>
@@ -7689,37 +7689,37 @@
         <v>3000.3</v>
       </c>
       <c r="M78">
-        <v>1136.905532116291</v>
+        <v>1098.224306116291</v>
       </c>
       <c r="N78">
-        <v>1863.394467883709</v>
+        <v>1902.075693883709</v>
       </c>
       <c r="O78">
-        <v>409.9467829344161</v>
+        <v>418.4566526544161</v>
       </c>
       <c r="P78">
-        <v>1453.447684949293</v>
+        <v>1483.619041229293</v>
       </c>
       <c r="Q78">
-        <v>2479.747684949293</v>
+        <v>2509.919041229293</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.219493441940991</v>
+        <v>0.2194542407929849</v>
       </c>
       <c r="T78">
         <v>2.526880794794991</v>
       </c>
       <c r="U78">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V78">
         <v>0.22</v>
       </c>
       <c r="W78">
-        <v>0.06189884081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.639005542012886</v>
+        <v>2.731955560708833</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.09977241084876588</v>
+        <v>0.0981414074269982</v>
       </c>
       <c r="C79">
-        <v>3558.779095238884</v>
+        <v>3934.916356618252</v>
       </c>
       <c r="D79">
-        <v>14700.26409523888</v>
+        <v>15076.40135661825</v>
       </c>
       <c r="E79">
         <v>7963.285</v>
@@ -7771,37 +7771,37 @@
         <v>3000.3</v>
       </c>
       <c r="M79">
-        <v>1151.86481543361</v>
+        <v>1112.67462593361</v>
       </c>
       <c r="N79">
-        <v>1848.43518456639</v>
+        <v>1887.62537406639</v>
       </c>
       <c r="O79">
-        <v>406.6557406046058</v>
+        <v>415.2775822946058</v>
       </c>
       <c r="P79">
-        <v>1441.779443961784</v>
+        <v>1472.347791771784</v>
       </c>
       <c r="Q79">
-        <v>2468.079443961784</v>
+        <v>2498.647791771784</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2265665366197057</v>
+        <v>0.2265257391337592</v>
       </c>
       <c r="T79">
         <v>2.629779712011928</v>
       </c>
       <c r="U79">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V79">
         <v>0.22</v>
       </c>
       <c r="W79">
-        <v>0.06189884081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.604732742765965</v>
+        <v>2.696475618361966</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.09982327661359328</v>
+        <v>0.09817123804557935</v>
       </c>
       <c r="C80">
-        <v>3358.771501157085</v>
+        <v>3739.313664360145</v>
       </c>
       <c r="D80">
-        <v>14688.76150115709</v>
+        <v>15069.30366436014</v>
       </c>
       <c r="E80">
         <v>8151.790000000001</v>
@@ -7853,37 +7853,37 @@
         <v>3000.3</v>
       </c>
       <c r="M80">
-        <v>1166.82409875093</v>
+        <v>1127.12494575093</v>
       </c>
       <c r="N80">
-        <v>1833.47590124907</v>
+        <v>1873.17505424907</v>
       </c>
       <c r="O80">
-        <v>403.3646982747954</v>
+        <v>412.0985119347955</v>
       </c>
       <c r="P80">
-        <v>1430.111202974275</v>
+        <v>1461.076542314275</v>
       </c>
       <c r="Q80">
-        <v>2456.411202974275</v>
+        <v>2487.376542314275</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2342826399055763</v>
+        <v>0.2342401009600585</v>
       </c>
       <c r="T80">
         <v>2.742033076248586</v>
       </c>
       <c r="U80">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V80">
         <v>0.22</v>
       </c>
       <c r="W80">
-        <v>0.06189884081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.571338733243325</v>
+        <v>2.661905418126555</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.09987414237842064</v>
+        <v>0.09820106866416051</v>
       </c>
       <c r="C81">
-        <v>3158.781893993306</v>
+        <v>3543.717651883064</v>
       </c>
       <c r="D81">
-        <v>14677.27689399331</v>
+        <v>15062.21265188306</v>
       </c>
       <c r="E81">
         <v>8340.295</v>
@@ -7935,37 +7935,37 @@
         <v>3000.3</v>
       </c>
       <c r="M81">
-        <v>1181.783382068249</v>
+        <v>1141.57526556825</v>
       </c>
       <c r="N81">
-        <v>1818.516617931751</v>
+        <v>1858.724734431751</v>
       </c>
       <c r="O81">
-        <v>400.0736559449851</v>
+        <v>408.9194415749852</v>
       </c>
       <c r="P81">
-        <v>1418.442961986766</v>
+        <v>1449.805292856765</v>
       </c>
       <c r="Q81">
-        <v>2444.742961986765</v>
+        <v>2476.105292856765</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2427336101710536</v>
+        <v>0.242689163912672</v>
       </c>
       <c r="T81">
         <v>2.864977237079212</v>
       </c>
       <c r="U81">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V81">
         <v>0.22</v>
       </c>
       <c r="W81">
-        <v>0.06189884081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.538790141683283</v>
+        <v>2.628210412833814</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.09992500814324801</v>
+        <v>0.09823089928274167</v>
       </c>
       <c r="C82">
-        <v>2958.810231590549</v>
+        <v>3348.128309761727</v>
       </c>
       <c r="D82">
-        <v>14665.81023159055</v>
+        <v>15055.12830976173</v>
       </c>
       <c r="E82">
         <v>8528.800000000001</v>
@@ -8017,37 +8017,37 @@
         <v>3000.3</v>
       </c>
       <c r="M82">
-        <v>1196.742665385569</v>
+        <v>1156.025585385569</v>
       </c>
       <c r="N82">
-        <v>1803.557334614431</v>
+        <v>1844.274414614431</v>
       </c>
       <c r="O82">
-        <v>396.7826136151749</v>
+        <v>405.7403712151748</v>
       </c>
       <c r="P82">
-        <v>1406.774720999256</v>
+        <v>1438.534043399256</v>
       </c>
       <c r="Q82">
-        <v>2433.074720999256</v>
+        <v>2464.834043399256</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2520296774630787</v>
+        <v>0.2519831331605469</v>
       </c>
       <c r="T82">
         <v>3.0002158139929</v>
       </c>
       <c r="U82">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V82">
         <v>0.22</v>
       </c>
       <c r="W82">
-        <v>0.06189884081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.507055264912242</v>
+        <v>2.595357782673391</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1016817339080754</v>
+        <v>0.09826072990132281</v>
       </c>
       <c r="C83">
-        <v>2384.992578651998</v>
+        <v>3152.54562858859</v>
       </c>
       <c r="D83">
-        <v>14280.497578652</v>
+        <v>15048.05062858859</v>
       </c>
       <c r="E83">
         <v>8717.305</v>
@@ -8099,45 +8099,45 @@
         <v>3000.3</v>
       </c>
       <c r="M83">
-        <v>1252.927992202889</v>
+        <v>1170.475905202889</v>
       </c>
       <c r="N83">
-        <v>1747.372007797111</v>
+        <v>1829.824094797111</v>
       </c>
       <c r="O83">
-        <v>384.4218417153645</v>
+        <v>402.5613008553645</v>
       </c>
       <c r="P83">
-        <v>1362.950166081747</v>
+        <v>1427.262793941747</v>
       </c>
       <c r="Q83">
-        <v>2389.250166081747</v>
+        <v>2453.562793941746</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2623042781542642</v>
+        <v>0.2622554149608297</v>
       </c>
       <c r="T83">
         <v>3.149690030581714</v>
       </c>
       <c r="U83">
-        <v>0.08205748822216713</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V83">
         <v>0.22</v>
       </c>
       <c r="W83">
-        <v>0.06400484081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.394630831676842</v>
+        <v>2.563316328566313</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1017536596729028</v>
+        <v>0.09829056051990395</v>
       </c>
       <c r="C84">
-        <v>2181.142675510588</v>
+        <v>2956.969598973772</v>
       </c>
       <c r="D84">
-        <v>14265.15267551059</v>
+        <v>15040.97959897377</v>
       </c>
       <c r="E84">
         <v>8905.810000000001</v>
@@ -8181,45 +8181,45 @@
         <v>3000.3</v>
       </c>
       <c r="M84">
-        <v>1268.396239020208</v>
+        <v>1184.926225020208</v>
       </c>
       <c r="N84">
-        <v>1731.903760979792</v>
+        <v>1815.373774979792</v>
       </c>
       <c r="O84">
-        <v>381.0188274155542</v>
+        <v>399.3822304955542</v>
       </c>
       <c r="P84">
-        <v>1350.884933564238</v>
+        <v>1415.991544484237</v>
       </c>
       <c r="Q84">
-        <v>2377.184933564237</v>
+        <v>2442.291544484237</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2737205011444704</v>
+        <v>0.2736690614055882</v>
       </c>
       <c r="T84">
         <v>3.315772493458173</v>
       </c>
       <c r="U84">
-        <v>0.08205748822216713</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V84">
         <v>0.22</v>
       </c>
       <c r="W84">
-        <v>0.06400484081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.365428016656393</v>
+        <v>2.532056373339894</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1018255854377301</v>
+        <v>0.09832039113848512</v>
       </c>
       <c r="C85">
-        <v>1977.325714261577</v>
+        <v>2761.400211545042</v>
       </c>
       <c r="D85">
-        <v>14249.84071426158</v>
+        <v>15033.91521154504</v>
       </c>
       <c r="E85">
         <v>9094.315000000001</v>
@@ -8263,45 +8263,45 @@
         <v>3000.3</v>
       </c>
       <c r="M85">
-        <v>1283.864485837528</v>
+        <v>1199.376544837528</v>
       </c>
       <c r="N85">
-        <v>1716.435514162472</v>
+        <v>1800.923455162472</v>
       </c>
       <c r="O85">
-        <v>377.6158131157439</v>
+        <v>396.2031601357439</v>
       </c>
       <c r="P85">
-        <v>1338.819701046728</v>
+        <v>1404.720295026728</v>
       </c>
       <c r="Q85">
-        <v>2365.119701046728</v>
+        <v>2431.020295026728</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.286479809192348</v>
+        <v>0.2864254897850244</v>
       </c>
       <c r="T85">
         <v>3.501394069614217</v>
       </c>
       <c r="U85">
-        <v>0.08205748822216713</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V85">
         <v>0.22</v>
       </c>
       <c r="W85">
-        <v>0.06400484081329036</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y85">
-        <v>2.336928883925594</v>
+        <v>2.501549670046642</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1018975112025575</v>
+        <v>0.1006434217570663</v>
       </c>
       <c r="C86">
-        <v>1773.541588940983</v>
+        <v>2042.423547280507</v>
       </c>
       <c r="D86">
-        <v>14234.56158894098</v>
+        <v>14503.44354728051</v>
       </c>
       <c r="E86">
         <v>9282.82</v>
@@ -8345,37 +8345,37 @@
         <v>3000.3</v>
       </c>
       <c r="M86">
-        <v>1299.332732654848</v>
+        <v>1269.247334654848</v>
       </c>
       <c r="N86">
-        <v>1700.967267345153</v>
+        <v>1731.052665345152</v>
       </c>
       <c r="O86">
-        <v>374.2127988159336</v>
+        <v>380.8315863759336</v>
       </c>
       <c r="P86">
-        <v>1326.754468529219</v>
+        <v>1350.221078969219</v>
       </c>
       <c r="Q86">
-        <v>2353.054468529219</v>
+        <v>2376.521078969219</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3008340307462101</v>
+        <v>0.3007764717118899</v>
       </c>
       <c r="T86">
         <v>3.710218342789763</v>
       </c>
       <c r="U86">
-        <v>0.08205748822216713</v>
+        <v>0.08015748822216713</v>
       </c>
       <c r="V86">
         <v>0.22</v>
       </c>
       <c r="W86">
-        <v>0.06400484081329036</v>
+        <v>0.06252284081329036</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.309108301974098</v>
+        <v>2.363841875481177</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1019694369673849</v>
+        <v>0.1007005523756474</v>
       </c>
       <c r="C87">
-        <v>1569.790194038811</v>
+        <v>1841.343821839622</v>
       </c>
       <c r="D87">
-        <v>14219.31519403881</v>
+        <v>14490.86882183962</v>
       </c>
       <c r="E87">
         <v>9471.324999999999</v>
@@ -8427,37 +8427,37 @@
         <v>3000.3</v>
       </c>
       <c r="M87">
-        <v>1314.800979472167</v>
+        <v>1284.357421972167</v>
       </c>
       <c r="N87">
-        <v>1685.499020527833</v>
+        <v>1715.942578027833</v>
       </c>
       <c r="O87">
-        <v>370.8097845161233</v>
+        <v>377.5073671661232</v>
       </c>
       <c r="P87">
-        <v>1314.68923601171</v>
+        <v>1338.43521086171</v>
       </c>
       <c r="Q87">
-        <v>2340.989236011709</v>
+        <v>2364.73521086171</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3171021485072539</v>
+        <v>0.3170409178956708</v>
       </c>
       <c r="T87">
         <v>3.946885852388717</v>
       </c>
       <c r="U87">
-        <v>0.08205748822216713</v>
+        <v>0.08015748822216713</v>
       </c>
       <c r="V87">
         <v>0.22</v>
       </c>
       <c r="W87">
-        <v>0.06400484081329036</v>
+        <v>0.06252284081329036</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.281942321950874</v>
+        <v>2.336031971063751</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1020413627322123</v>
+        <v>0.1007576829942286</v>
       </c>
       <c r="C88">
-        <v>1366.071424496608</v>
+        <v>1640.285882499702</v>
       </c>
       <c r="D88">
-        <v>14204.10142449661</v>
+        <v>14478.3158824997</v>
       </c>
       <c r="E88">
         <v>9659.83</v>
@@ -8509,37 +8509,37 @@
         <v>3000.3</v>
       </c>
       <c r="M88">
-        <v>1330.269226289487</v>
+        <v>1299.467509289487</v>
       </c>
       <c r="N88">
-        <v>1670.030773710513</v>
+        <v>1700.832490710513</v>
       </c>
       <c r="O88">
-        <v>367.406770216313</v>
+        <v>374.1831479563129</v>
       </c>
       <c r="P88">
-        <v>1302.6240034942</v>
+        <v>1326.6493427542</v>
       </c>
       <c r="Q88">
-        <v>2328.9240034942</v>
+        <v>2352.9493427542</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.335694283091304</v>
+        <v>0.3356288563914206</v>
       </c>
       <c r="T88">
         <v>4.217363006216094</v>
       </c>
       <c r="U88">
-        <v>0.08205748822216713</v>
+        <v>0.08015748822216713</v>
       </c>
       <c r="V88">
         <v>0.22</v>
       </c>
       <c r="W88">
-        <v>0.06400484081329036</v>
+        <v>0.06252284081329036</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.255408108904933</v>
+        <v>2.308868808609521</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1053027084970397</v>
+        <v>0.1008148136128098</v>
       </c>
       <c r="C89">
-        <v>520.347771709552</v>
+        <v>1439.249672692124</v>
       </c>
       <c r="D89">
-        <v>13546.88277170955</v>
+        <v>14465.78467269212</v>
       </c>
       <c r="E89">
         <v>9848.335000000001</v>
@@ -8591,45 +8591,45 @@
         <v>3000.3</v>
       </c>
       <c r="M89">
-        <v>1422.817167606807</v>
+        <v>1314.577596606807</v>
       </c>
       <c r="N89">
-        <v>1577.482832393193</v>
+        <v>1685.722403393194</v>
       </c>
       <c r="O89">
-        <v>347.0462231265025</v>
+        <v>370.8589287465026</v>
       </c>
       <c r="P89">
-        <v>1230.436609266691</v>
+        <v>1314.863474646691</v>
       </c>
       <c r="Q89">
-        <v>2256.736609266691</v>
+        <v>2341.163474646691</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3571467460729003</v>
+        <v>0.3570764777326703</v>
       </c>
       <c r="T89">
         <v>4.529452029863067</v>
       </c>
       <c r="U89">
-        <v>0.08675748822216714</v>
+        <v>0.08015748822216713</v>
       </c>
       <c r="V89">
         <v>0.22</v>
       </c>
       <c r="W89">
-        <v>0.06767084081329038</v>
+        <v>0.06252284081329036</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.108703822464088</v>
+        <v>2.282330086671481</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.105411294261867</v>
+        <v>0.1008719442313909</v>
       </c>
       <c r="C90">
-        <v>311.0053967512795</v>
+        <v>1238.235136043921</v>
       </c>
       <c r="D90">
-        <v>13526.04539675128</v>
+        <v>14453.27513604392</v>
       </c>
       <c r="E90">
         <v>10036.84</v>
@@ -8673,45 +8673,45 @@
         <v>3000.3</v>
       </c>
       <c r="M90">
-        <v>1439.171387924126</v>
+        <v>1329.687683924126</v>
       </c>
       <c r="N90">
-        <v>1561.128612075874</v>
+        <v>1670.612316075874</v>
       </c>
       <c r="O90">
-        <v>343.4482946566923</v>
+        <v>367.5347095366923</v>
       </c>
       <c r="P90">
-        <v>1217.680317419182</v>
+        <v>1303.077606539182</v>
       </c>
       <c r="Q90">
-        <v>2243.980317419182</v>
+        <v>2329.377606539181</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3821746195514293</v>
+        <v>0.3820987026307949</v>
       </c>
       <c r="T90">
         <v>4.893555890784536</v>
       </c>
       <c r="U90">
-        <v>0.08675748822216714</v>
+        <v>0.08015748822216713</v>
       </c>
       <c r="V90">
         <v>0.22</v>
       </c>
       <c r="W90">
-        <v>0.06767084081329038</v>
+        <v>0.06252284081329036</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.084741279026996</v>
+        <v>2.25639451750476</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1055198800266944</v>
+        <v>0.1028728348499721</v>
       </c>
       <c r="C91">
-        <v>101.7270260900441</v>
+        <v>624.8545507013769</v>
       </c>
       <c r="D91">
-        <v>13505.27202609004</v>
+        <v>14028.39955070138</v>
       </c>
       <c r="E91">
         <v>10225.345</v>
@@ -8755,37 +8755,37 @@
         <v>3000.3</v>
       </c>
       <c r="M91">
-        <v>1455.525608241446</v>
+        <v>1391.773217241446</v>
       </c>
       <c r="N91">
-        <v>1544.774391758554</v>
+        <v>1608.526782758554</v>
       </c>
       <c r="O91">
-        <v>339.850366186882</v>
+        <v>353.8758922068819</v>
       </c>
       <c r="P91">
-        <v>1204.924025571672</v>
+        <v>1254.650890551672</v>
       </c>
       <c r="Q91">
-        <v>2231.224025571672</v>
+        <v>2280.950890551672</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4117530154805998</v>
+        <v>0.4116704229649422</v>
       </c>
       <c r="T91">
         <v>5.323860453691726</v>
       </c>
       <c r="U91">
-        <v>0.08675748822216714</v>
+        <v>0.08295748822216714</v>
       </c>
       <c r="V91">
         <v>0.22</v>
       </c>
       <c r="W91">
-        <v>0.06767084081329038</v>
+        <v>0.06470684081329037</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.061317219712086</v>
+        <v>2.155739141141631</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1056284657915218</v>
+        <v>0.1029518054685532</v>
       </c>
       <c r="C92">
-        <v>-107.4876347163517</v>
+        <v>420.0924819457105</v>
       </c>
       <c r="D92">
-        <v>13484.56236528365</v>
+        <v>14012.14248194571</v>
       </c>
       <c r="E92">
         <v>10413.85</v>
@@ -8837,37 +8837,37 @@
         <v>3000.3</v>
       </c>
       <c r="M92">
-        <v>1471.879828558766</v>
+        <v>1407.411118558766</v>
       </c>
       <c r="N92">
-        <v>1528.420171441235</v>
+        <v>1592.888881441235</v>
       </c>
       <c r="O92">
-        <v>336.2524377170716</v>
+        <v>350.4355539170716</v>
       </c>
       <c r="P92">
-        <v>1192.167733724163</v>
+        <v>1242.453327524163</v>
       </c>
       <c r="Q92">
-        <v>2218.467733724163</v>
+        <v>2268.753327524163</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4472470905956046</v>
+        <v>0.447156487365919</v>
       </c>
       <c r="T92">
         <v>5.840225929180354</v>
       </c>
       <c r="U92">
-        <v>0.08675748822216714</v>
+        <v>0.08295748822216714</v>
       </c>
       <c r="V92">
         <v>0.22</v>
       </c>
       <c r="W92">
-        <v>0.06767084081329038</v>
+        <v>0.06470684081329037</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.038413695048618</v>
+        <v>2.131786484017836</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1057370515563492</v>
+        <v>0.1030307760871344</v>
       </c>
       <c r="C93">
-        <v>-316.6388783068069</v>
+        <v>215.368049180961</v>
       </c>
       <c r="D93">
-        <v>13463.91612169319</v>
+        <v>13995.92304918096</v>
       </c>
       <c r="E93">
         <v>10602.355</v>
@@ -8919,37 +8919,37 @@
         <v>3000.3</v>
       </c>
       <c r="M93">
-        <v>1488.234048876085</v>
+        <v>1423.049019876085</v>
       </c>
       <c r="N93">
-        <v>1512.065951123915</v>
+        <v>1577.250980123915</v>
       </c>
       <c r="O93">
-        <v>332.6545092472613</v>
+        <v>346.9952156272612</v>
       </c>
       <c r="P93">
-        <v>1179.411441876653</v>
+        <v>1230.255764496654</v>
       </c>
       <c r="Q93">
-        <v>2205.711441876653</v>
+        <v>2256.555764496653</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4906287379583882</v>
+        <v>0.4905283438560017</v>
       </c>
       <c r="T93">
         <v>6.471339288110901</v>
       </c>
       <c r="U93">
-        <v>0.08675748822216714</v>
+        <v>0.08295748822216714</v>
       </c>
       <c r="V93">
         <v>0.22</v>
       </c>
       <c r="W93">
-        <v>0.06767084081329038</v>
+        <v>0.06470684081329037</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.016013544553578</v>
+        <v>2.108360258918738</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1125193173211765</v>
+        <v>0.1031097467057155</v>
       </c>
       <c r="C94">
-        <v>-1680.345925416761</v>
+        <v>10.68112186422877</v>
       </c>
       <c r="D94">
-        <v>12288.71407458324</v>
+        <v>13979.74112186423</v>
       </c>
       <c r="E94">
         <v>10790.86</v>
@@ -9001,45 +9001,45 @@
         <v>3000.3</v>
       </c>
       <c r="M94">
-        <v>1665.873147193405</v>
+        <v>1438.686921193405</v>
       </c>
       <c r="N94">
-        <v>1334.426852806596</v>
+        <v>1561.613078806595</v>
       </c>
       <c r="O94">
-        <v>293.573907617451</v>
+        <v>343.554877337451</v>
       </c>
       <c r="P94">
-        <v>1040.852945189145</v>
+        <v>1218.058201469144</v>
       </c>
       <c r="Q94">
-        <v>2067.152945189144</v>
+        <v>2244.358201469144</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5448557971618677</v>
+        <v>0.5447431644686052</v>
       </c>
       <c r="T94">
         <v>7.260230986774085</v>
       </c>
       <c r="U94">
-        <v>0.09605748822216713</v>
+        <v>0.08295748822216714</v>
       </c>
       <c r="V94">
         <v>0.22</v>
       </c>
       <c r="W94">
-        <v>0.07492484081329036</v>
+        <v>0.06470684081329037</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y94">
-        <v>1.801037494994612</v>
+        <v>2.085443299582665</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1127004430860039</v>
+        <v>0.1031887173242967</v>
       </c>
       <c r="C95">
-        <v>-1897.429583834892</v>
+        <v>-193.968429944387</v>
       </c>
       <c r="D95">
-        <v>12260.13541616511</v>
+        <v>13963.59657005561</v>
       </c>
       <c r="E95">
         <v>10979.365</v>
@@ -9083,45 +9083,45 @@
         <v>3000.3</v>
       </c>
       <c r="M95">
-        <v>1683.980464010724</v>
+        <v>1454.324822510724</v>
       </c>
       <c r="N95">
-        <v>1316.319535989276</v>
+        <v>1545.975177489276</v>
       </c>
       <c r="O95">
-        <v>289.5902979176407</v>
+        <v>340.1145390476407</v>
       </c>
       <c r="P95">
-        <v>1026.729238071635</v>
+        <v>1205.860638441635</v>
       </c>
       <c r="Q95">
-        <v>2053.029238071635</v>
+        <v>2232.160638441635</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6145763018520556</v>
+        <v>0.6144479338276666</v>
       </c>
       <c r="T95">
         <v>8.274520313626747</v>
       </c>
       <c r="U95">
-        <v>0.09605748822216713</v>
+        <v>0.08295748822216714</v>
       </c>
       <c r="V95">
         <v>0.22</v>
       </c>
       <c r="W95">
-        <v>0.07492484081329036</v>
+        <v>0.06470684081329037</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y95">
-        <v>1.781671500424778</v>
+        <v>2.063019178081777</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1128815688508313</v>
+        <v>0.1032676879428778</v>
       </c>
       <c r="C96">
-        <v>-2114.380625494663</v>
+        <v>-398.5807355852085</v>
       </c>
       <c r="D96">
-        <v>12231.68937450534</v>
+        <v>13947.48926441479</v>
       </c>
       <c r="E96">
         <v>11167.87</v>
@@ -9165,45 +9165,45 @@
         <v>3000.3</v>
       </c>
       <c r="M96">
-        <v>1702.087780828044</v>
+        <v>1469.962723828044</v>
       </c>
       <c r="N96">
-        <v>1298.212219171956</v>
+        <v>1530.337276171956</v>
       </c>
       <c r="O96">
-        <v>285.6066882178304</v>
+        <v>336.6742007578304</v>
       </c>
       <c r="P96">
-        <v>1012.605530954126</v>
+        <v>1193.663075414126</v>
       </c>
       <c r="Q96">
-        <v>2038.905530954126</v>
+        <v>2219.963075414125</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7075369747723063</v>
+        <v>0.7073876263064155</v>
       </c>
       <c r="T96">
         <v>9.626906082763634</v>
       </c>
       <c r="U96">
-        <v>0.09605748822216713</v>
+        <v>0.08295748822216714</v>
       </c>
       <c r="V96">
         <v>0.22</v>
       </c>
       <c r="W96">
-        <v>0.07492484081329036</v>
+        <v>0.06470684081329037</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y96">
-        <v>1.762717548292599</v>
+        <v>2.041072165548992</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1165453946156587</v>
+        <v>0.103346658561459</v>
       </c>
       <c r="C97">
-        <v>-2851.223926041544</v>
+        <v>-603.1559238024747</v>
       </c>
       <c r="D97">
-        <v>11683.35107395846</v>
+        <v>13931.41907619753</v>
       </c>
       <c r="E97">
         <v>11356.375</v>
@@ -9247,45 +9247,45 @@
         <v>3000.3</v>
       </c>
       <c r="M97">
-        <v>1804.362580145364</v>
+        <v>1485.600625145364</v>
       </c>
       <c r="N97">
-        <v>1195.937419854637</v>
+        <v>1514.699374854636</v>
       </c>
       <c r="O97">
-        <v>263.1062323680201</v>
+        <v>333.23386246802</v>
       </c>
       <c r="P97">
-        <v>932.8311874866165</v>
+        <v>1181.465512386616</v>
       </c>
       <c r="Q97">
-        <v>1959.131187486616</v>
+        <v>2207.765512386616</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8376819168606574</v>
+        <v>0.8375031957766641</v>
       </c>
       <c r="T97">
         <v>11.52024615955528</v>
       </c>
       <c r="U97">
-        <v>0.1007574882221671</v>
+        <v>0.08295748822216714</v>
       </c>
       <c r="V97">
         <v>0.22</v>
       </c>
       <c r="W97">
-        <v>0.07859084081329036</v>
+        <v>0.06470684081329037</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y97">
-        <v>1.662803270813945</v>
+        <v>2.019587195385318</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.116763180380486</v>
+        <v>0.1092662691800401</v>
       </c>
       <c r="C98">
-        <v>-3070.779418635426</v>
+        <v>-1899.230319504442</v>
       </c>
       <c r="D98">
-        <v>11652.30058136457</v>
+        <v>12823.84968049556</v>
       </c>
       <c r="E98">
         <v>11544.88</v>
@@ -9329,45 +9329,45 @@
         <v>3000.3</v>
       </c>
       <c r="M98">
-        <v>1823.355870462683</v>
+        <v>1642.391070462683</v>
       </c>
       <c r="N98">
-        <v>1176.944129537317</v>
+        <v>1357.908929537317</v>
       </c>
       <c r="O98">
-        <v>258.9277084982098</v>
+        <v>298.7399644982097</v>
       </c>
       <c r="P98">
-        <v>918.0164210391076</v>
+        <v>1059.168965039107</v>
       </c>
       <c r="Q98">
-        <v>1944.316421039107</v>
+        <v>2085.468965039107</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.032899329993181</v>
+        <v>1.032676549982034</v>
       </c>
       <c r="T98">
         <v>14.3602562747427</v>
       </c>
       <c r="U98">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216714</v>
       </c>
       <c r="V98">
         <v>0.22</v>
       </c>
       <c r="W98">
-        <v>0.07859084081329036</v>
+        <v>0.07079084081329037</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y98">
-        <v>1.645482403409634</v>
+        <v>1.826787818052844</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1169809661453134</v>
+        <v>0.1094060797986213</v>
       </c>
       <c r="C99">
-        <v>-3290.17030476865</v>
+        <v>-2111.769334189537</v>
       </c>
       <c r="D99">
-        <v>11621.41469523135</v>
+        <v>12799.81566581046</v>
       </c>
       <c r="E99">
         <v>11733.385</v>
@@ -9411,45 +9411,45 @@
         <v>3000.3</v>
       </c>
       <c r="M99">
-        <v>1842.349160780003</v>
+        <v>1659.499310780003</v>
       </c>
       <c r="N99">
-        <v>1157.950839219998</v>
+        <v>1340.800689219997</v>
       </c>
       <c r="O99">
-        <v>254.7491846283995</v>
+        <v>294.9761516283994</v>
       </c>
       <c r="P99">
-        <v>903.2016545915981</v>
+        <v>1045.824537591598</v>
       </c>
       <c r="Q99">
-        <v>1929.501654591598</v>
+        <v>2072.124537591598</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.358261685214058</v>
+        <v>1.357965473657654</v>
       </c>
       <c r="T99">
         <v>19.09360646672179</v>
       </c>
       <c r="U99">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216714</v>
       </c>
       <c r="V99">
         <v>0.22</v>
       </c>
       <c r="W99">
-        <v>0.07859084081329036</v>
+        <v>0.07079084081329037</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y99">
-        <v>1.628518667292008</v>
+        <v>1.807954953949206</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1171987519101408</v>
+        <v>0.1095458904172025</v>
       </c>
       <c r="C100">
-        <v>-3509.397889911186</v>
+        <v>-2324.218429962593</v>
       </c>
       <c r="D100">
-        <v>11590.69211008881</v>
+        <v>12775.87157003741</v>
       </c>
       <c r="E100">
         <v>11921.89</v>
@@ -9493,45 +9493,45 @@
         <v>3000.3</v>
       </c>
       <c r="M100">
-        <v>1861.342451097322</v>
+        <v>1676.607551097322</v>
       </c>
       <c r="N100">
-        <v>1138.957548902678</v>
+        <v>1323.692448902678</v>
       </c>
       <c r="O100">
-        <v>250.5706607585892</v>
+        <v>291.2123387585891</v>
       </c>
       <c r="P100">
-        <v>888.386888144089</v>
+        <v>1032.480110144089</v>
       </c>
       <c r="Q100">
-        <v>1914.686888144089</v>
+        <v>2058.780110144088</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.00898639565581</v>
+        <v>2.008543321008894</v>
       </c>
       <c r="T100">
         <v>28.56030685067996</v>
       </c>
       <c r="U100">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216714</v>
       </c>
       <c r="V100">
         <v>0.22</v>
       </c>
       <c r="W100">
-        <v>0.07859084081329036</v>
+        <v>0.07079084081329037</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.611901129870662</v>
+        <v>1.78950643401095</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1174165376749682</v>
+        <v>0.1096857010357836</v>
       </c>
       <c r="C101">
-        <v>-3728.463465764764</v>
+        <v>-2536.578110504388</v>
       </c>
       <c r="D101">
-        <v>11560.13153423524</v>
+        <v>12752.01688949561</v>
       </c>
       <c r="E101">
         <v>12110.395</v>
@@ -9575,45 +9575,45 @@
         <v>3000.3</v>
       </c>
       <c r="M101">
-        <v>1880.335741414642</v>
+        <v>1693.715791414642</v>
       </c>
       <c r="N101">
-        <v>1119.964258585358</v>
+        <v>1306.584208585358</v>
       </c>
       <c r="O101">
-        <v>246.3921368887789</v>
+        <v>287.4485258887788</v>
       </c>
       <c r="P101">
-        <v>873.5721216965796</v>
+        <v>1019.135682696579</v>
       </c>
       <c r="Q101">
-        <v>1899.872121696579</v>
+        <v>2045.435682696579</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.961160526981067</v>
+        <v>3.960276863062612</v>
       </c>
       <c r="T101">
         <v>56.96040800255447</v>
       </c>
       <c r="U101">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216714</v>
       </c>
       <c r="V101">
         <v>0.22</v>
       </c>
       <c r="W101">
-        <v>0.07859084081329036</v>
+        <v>0.07079084081329037</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y101">
-        <v>1.595619300276009</v>
+        <v>1.771430611445182</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/indonesia/indonesia_diversified.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_diversified.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09584444979624923</v>
+        <v>0.0958157804148304</v>
       </c>
       <c r="C2">
-        <v>19017.15752614465</v>
+        <v>18836.00390056454</v>
       </c>
       <c r="D2">
-        <v>15643.75752614465</v>
+        <v>15651.10890056454</v>
       </c>
       <c r="E2">
-        <v>-6551.6</v>
+        <v>-6363.095</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>188.505</v>
       </c>
       <c r="G2">
         <v>3373.4</v>
@@ -1457,28 +1457,28 @@
         <v>3000.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>13.03653231731962</v>
       </c>
       <c r="N2">
-        <v>3000.3</v>
+        <v>2987.263467682681</v>
       </c>
       <c r="O2">
-        <v>660.066</v>
+        <v>657.1979628901897</v>
       </c>
       <c r="P2">
-        <v>2340.234</v>
+        <v>2330.065504792491</v>
       </c>
       <c r="Q2">
-        <v>3366.534</v>
+        <v>3356.365504792491</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09584444979624923</v>
+        <v>0.09623873940070454</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7339451160150327</v>
       </c>
       <c r="U2">
         <v>0.06915748822216713</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>230.1455576506314</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0958157804148304</v>
+        <v>0.09578711103341155</v>
       </c>
       <c r="C3">
-        <v>18836.00390056454</v>
+        <v>18654.85718740476</v>
       </c>
       <c r="D3">
-        <v>15651.10890056454</v>
+        <v>15658.46718740476</v>
       </c>
       <c r="E3">
-        <v>-6363.095</v>
+        <v>-6174.59</v>
       </c>
       <c r="F3">
-        <v>188.505</v>
+        <v>377.01</v>
       </c>
       <c r="G3">
         <v>3373.4</v>
@@ -1539,28 +1539,28 @@
         <v>3000.3</v>
       </c>
       <c r="M3">
-        <v>13.03653231731962</v>
+        <v>26.07306463463923</v>
       </c>
       <c r="N3">
-        <v>2987.263467682681</v>
+        <v>2974.226935365361</v>
       </c>
       <c r="O3">
-        <v>657.1979628901897</v>
+        <v>654.3299257803794</v>
       </c>
       <c r="P3">
-        <v>2330.065504792491</v>
+        <v>2319.897009584982</v>
       </c>
       <c r="Q3">
-        <v>3356.365504792491</v>
+        <v>3346.197009584982</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09623873940070454</v>
+        <v>0.09664107573178136</v>
       </c>
       <c r="T3">
-        <v>0.7339451160150327</v>
+        <v>0.73979959986411</v>
       </c>
       <c r="U3">
         <v>0.06915748822216713</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>230.1455576506314</v>
+        <v>115.0727788253157</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09578711103341155</v>
+        <v>0.0957584416519927</v>
       </c>
       <c r="C4">
-        <v>18654.85718740476</v>
+        <v>18473.71739641941</v>
       </c>
       <c r="D4">
-        <v>15658.46718740476</v>
+        <v>15665.83239641941</v>
       </c>
       <c r="E4">
-        <v>-6174.59</v>
+        <v>-5986.085</v>
       </c>
       <c r="F4">
-        <v>377.01</v>
+        <v>565.515</v>
       </c>
       <c r="G4">
         <v>3373.4</v>
@@ -1621,28 +1621,28 @@
         <v>3000.3</v>
       </c>
       <c r="M4">
-        <v>26.07306463463923</v>
+        <v>39.10959695195885</v>
       </c>
       <c r="N4">
-        <v>2974.226935365361</v>
+        <v>2961.190403048041</v>
       </c>
       <c r="O4">
-        <v>654.3299257803794</v>
+        <v>651.4618886705691</v>
       </c>
       <c r="P4">
-        <v>2319.897009584982</v>
+        <v>2309.728514377472</v>
       </c>
       <c r="Q4">
-        <v>3346.197009584982</v>
+        <v>3336.028514377472</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09664107573178136</v>
+        <v>0.0970517076573134</v>
       </c>
       <c r="T4">
-        <v>0.73979959986411</v>
+        <v>0.745774794720385</v>
       </c>
       <c r="U4">
         <v>0.06915748822216713</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>115.0727788253157</v>
+        <v>76.71518588354378</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0957584416519927</v>
+        <v>0.09572977227057386</v>
       </c>
       <c r="C5">
-        <v>18473.71739641941</v>
+        <v>18292.58453738094</v>
       </c>
       <c r="D5">
-        <v>15665.83239641941</v>
+        <v>15673.20453738094</v>
       </c>
       <c r="E5">
-        <v>-5986.085</v>
+        <v>-5797.58</v>
       </c>
       <c r="F5">
-        <v>565.515</v>
+        <v>754.02</v>
       </c>
       <c r="G5">
         <v>3373.4</v>
@@ -1703,28 +1703,28 @@
         <v>3000.3</v>
       </c>
       <c r="M5">
-        <v>39.10959695195885</v>
+        <v>52.14612926927846</v>
       </c>
       <c r="N5">
-        <v>2961.190403048041</v>
+        <v>2948.153870730722</v>
       </c>
       <c r="O5">
-        <v>651.4618886705691</v>
+        <v>648.5938515607588</v>
       </c>
       <c r="P5">
-        <v>2309.728514377472</v>
+        <v>2299.560019169963</v>
       </c>
       <c r="Q5">
-        <v>3336.028514377472</v>
+        <v>3325.860019169963</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0970517076573134</v>
+        <v>0.09747089441462733</v>
       </c>
       <c r="T5">
-        <v>0.745774794720385</v>
+        <v>0.7518744728028323</v>
       </c>
       <c r="U5">
         <v>0.06915748822216713</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>76.71518588354378</v>
+        <v>57.53638941265784</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09572977227057386</v>
+        <v>0.095701102889155</v>
       </c>
       <c r="C6">
-        <v>18292.58453738094</v>
+        <v>18111.45862008023</v>
       </c>
       <c r="D6">
-        <v>15673.20453738094</v>
+        <v>15680.58362008023</v>
       </c>
       <c r="E6">
-        <v>-5797.58</v>
+        <v>-5609.075000000001</v>
       </c>
       <c r="F6">
-        <v>754.02</v>
+        <v>942.5250000000001</v>
       </c>
       <c r="G6">
         <v>3373.4</v>
@@ -1785,28 +1785,28 @@
         <v>3000.3</v>
       </c>
       <c r="M6">
-        <v>52.14612926927846</v>
+        <v>65.18266158659809</v>
       </c>
       <c r="N6">
-        <v>2948.153870730722</v>
+        <v>2935.117338413402</v>
       </c>
       <c r="O6">
-        <v>648.5938515607588</v>
+        <v>645.7258144509485</v>
       </c>
       <c r="P6">
-        <v>2299.560019169963</v>
+        <v>2289.391523962454</v>
       </c>
       <c r="Q6">
-        <v>3325.860019169963</v>
+        <v>3315.691523962454</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09747089441462733</v>
+        <v>0.09789890615630578</v>
       </c>
       <c r="T6">
-        <v>0.7518744728028323</v>
+        <v>0.7581025651606995</v>
       </c>
       <c r="U6">
         <v>0.06915748822216713</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>57.53638941265784</v>
+        <v>46.02911153012626</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.095701102889155</v>
+        <v>0.09567243350773617</v>
       </c>
       <c r="C7">
-        <v>18111.45862008023</v>
+        <v>17930.33965432657</v>
       </c>
       <c r="D7">
-        <v>15680.58362008023</v>
+        <v>15687.96965432657</v>
       </c>
       <c r="E7">
-        <v>-5609.075000000001</v>
+        <v>-5420.57</v>
       </c>
       <c r="F7">
-        <v>942.5250000000001</v>
+        <v>1131.03</v>
       </c>
       <c r="G7">
         <v>3373.4</v>
@@ -1867,28 +1867,28 @@
         <v>3000.3</v>
       </c>
       <c r="M7">
-        <v>65.18266158659809</v>
+        <v>78.21919390391771</v>
       </c>
       <c r="N7">
-        <v>2935.117338413402</v>
+        <v>2922.080806096083</v>
       </c>
       <c r="O7">
-        <v>645.7258144509485</v>
+        <v>642.8577773411382</v>
       </c>
       <c r="P7">
-        <v>2289.391523962454</v>
+        <v>2279.223028754945</v>
       </c>
       <c r="Q7">
-        <v>3315.691523962454</v>
+        <v>3305.523028754944</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09789890615630578</v>
+        <v>0.09833602453078591</v>
       </c>
       <c r="T7">
-        <v>0.7581025651606995</v>
+        <v>0.7644631701219256</v>
       </c>
       <c r="U7">
         <v>0.06915748822216713</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.02911153012626</v>
+        <v>38.35759294177188</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09567243350773617</v>
+        <v>0.09564376412631732</v>
       </c>
       <c r="C8">
-        <v>17930.33965432657</v>
+        <v>17749.2276499478</v>
       </c>
       <c r="D8">
-        <v>15687.96965432657</v>
+        <v>15695.3626499478</v>
       </c>
       <c r="E8">
-        <v>-5420.570000000001</v>
+        <v>-5232.065000000001</v>
       </c>
       <c r="F8">
-        <v>1131.03</v>
+        <v>1319.535</v>
       </c>
       <c r="G8">
         <v>3373.4</v>
@@ -1949,28 +1949,28 @@
         <v>3000.3</v>
       </c>
       <c r="M8">
-        <v>78.2191939039177</v>
+        <v>91.2557262212373</v>
       </c>
       <c r="N8">
-        <v>2922.080806096083</v>
+        <v>2909.044273778763</v>
       </c>
       <c r="O8">
-        <v>642.8577773411382</v>
+        <v>639.9897402313279</v>
       </c>
       <c r="P8">
-        <v>2279.223028754945</v>
+        <v>2269.054533547435</v>
       </c>
       <c r="Q8">
-        <v>3305.523028754944</v>
+        <v>3295.354533547435</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09833602453078591</v>
+        <v>0.09878254330041612</v>
       </c>
       <c r="T8">
-        <v>0.7644631701219256</v>
+        <v>0.7709605622866188</v>
       </c>
       <c r="U8">
         <v>0.06915748822216713</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.35759294177189</v>
+        <v>32.87793680723306</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09564376412631732</v>
+        <v>0.09561509474489849</v>
       </c>
       <c r="C9">
-        <v>17749.2276499478</v>
+        <v>17568.12261679022</v>
       </c>
       <c r="D9">
-        <v>15695.3626499478</v>
+        <v>15702.76261679022</v>
       </c>
       <c r="E9">
-        <v>-5232.065000000001</v>
+        <v>-5043.56</v>
       </c>
       <c r="F9">
-        <v>1319.535</v>
+        <v>1508.04</v>
       </c>
       <c r="G9">
         <v>3373.4</v>
@@ -2031,28 +2031,28 @@
         <v>3000.3</v>
       </c>
       <c r="M9">
-        <v>91.25572622123731</v>
+        <v>104.2922585385569</v>
       </c>
       <c r="N9">
-        <v>2909.044273778763</v>
+        <v>2896.007741461443</v>
       </c>
       <c r="O9">
-        <v>639.9897402313279</v>
+        <v>637.1217031215175</v>
       </c>
       <c r="P9">
-        <v>2269.054533547435</v>
+        <v>2258.886038339926</v>
       </c>
       <c r="Q9">
-        <v>3295.354533547435</v>
+        <v>3285.186038339926</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09878254330041614</v>
+        <v>0.09923876899982093</v>
       </c>
       <c r="T9">
-        <v>0.770960562286619</v>
+        <v>0.7775992021070665</v>
       </c>
       <c r="U9">
         <v>0.06915748822216713</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.87793680723305</v>
+        <v>28.76819470632892</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09561509474489849</v>
+        <v>0.09558642536347964</v>
       </c>
       <c r="C10">
-        <v>17568.12261679022</v>
+        <v>17387.02456471876</v>
       </c>
       <c r="D10">
-        <v>15702.76261679022</v>
+        <v>15710.16956471876</v>
       </c>
       <c r="E10">
-        <v>-5043.56</v>
+        <v>-4855.055</v>
       </c>
       <c r="F10">
-        <v>1508.04</v>
+        <v>1696.545</v>
       </c>
       <c r="G10">
         <v>3373.4</v>
@@ -2113,28 +2113,28 @@
         <v>3000.3</v>
       </c>
       <c r="M10">
-        <v>104.2922585385569</v>
+        <v>117.3287908558765</v>
       </c>
       <c r="N10">
-        <v>2896.007741461443</v>
+        <v>2882.971209144124</v>
       </c>
       <c r="O10">
-        <v>637.1217031215175</v>
+        <v>634.2536660117072</v>
       </c>
       <c r="P10">
-        <v>2258.886038339926</v>
+        <v>2248.717543132417</v>
       </c>
       <c r="Q10">
-        <v>3285.186038339926</v>
+        <v>3275.017543132416</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09923876899982093</v>
+        <v>0.09970502163767418</v>
       </c>
       <c r="T10">
-        <v>0.7775992021070665</v>
+        <v>0.784383746099392</v>
       </c>
       <c r="U10">
         <v>0.06915748822216713</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.76819470632892</v>
+        <v>25.57172862784793</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09558642536347964</v>
+        <v>0.09555775598206079</v>
       </c>
       <c r="C11">
-        <v>17387.02456471876</v>
+        <v>17205.93350361697</v>
       </c>
       <c r="D11">
-        <v>15710.16956471876</v>
+        <v>15717.58350361696</v>
       </c>
       <c r="E11">
-        <v>-4855.055</v>
+        <v>-4666.55</v>
       </c>
       <c r="F11">
-        <v>1696.545</v>
+        <v>1885.05</v>
       </c>
       <c r="G11">
         <v>3373.4</v>
@@ -2195,28 +2195,28 @@
         <v>3000.3</v>
       </c>
       <c r="M11">
-        <v>117.3287908558765</v>
+        <v>130.3653231731961</v>
       </c>
       <c r="N11">
-        <v>2882.971209144124</v>
+        <v>2869.934676826804</v>
       </c>
       <c r="O11">
-        <v>634.2536660117072</v>
+        <v>631.3856289018969</v>
       </c>
       <c r="P11">
-        <v>2248.717543132417</v>
+        <v>2238.549047924907</v>
       </c>
       <c r="Q11">
-        <v>3275.017543132416</v>
+        <v>3264.849047924907</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09970502163767418</v>
+        <v>0.1001816354452575</v>
       </c>
       <c r="T11">
-        <v>0.784383746099392</v>
+        <v>0.7913190577359913</v>
       </c>
       <c r="U11">
         <v>0.06915748822216713</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.57172862784793</v>
+        <v>23.01455576506314</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09555775598206079</v>
+        <v>0.09552908660064195</v>
       </c>
       <c r="C12">
-        <v>17205.93350361697</v>
+        <v>17024.84944338703</v>
       </c>
       <c r="D12">
-        <v>15717.58350361696</v>
+        <v>15725.00444338703</v>
       </c>
       <c r="E12">
-        <v>-4666.55</v>
+        <v>-4478.045</v>
       </c>
       <c r="F12">
-        <v>1885.05</v>
+        <v>2073.555</v>
       </c>
       <c r="G12">
         <v>3373.4</v>
@@ -2277,28 +2277,28 @@
         <v>3000.3</v>
       </c>
       <c r="M12">
-        <v>130.3653231731962</v>
+        <v>143.4018554905158</v>
       </c>
       <c r="N12">
-        <v>2869.934676826804</v>
+        <v>2856.898144509485</v>
       </c>
       <c r="O12">
-        <v>631.3856289018969</v>
+        <v>628.5175917920866</v>
       </c>
       <c r="P12">
-        <v>2238.549047924907</v>
+        <v>2228.380552717398</v>
       </c>
       <c r="Q12">
-        <v>3264.849047924907</v>
+        <v>3254.680552717398</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1001816354452575</v>
+        <v>0.1006689596754832</v>
       </c>
       <c r="T12">
-        <v>0.7913190577359913</v>
+        <v>0.7984102190722897</v>
       </c>
       <c r="U12">
         <v>0.06915748822216713</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.01455576506313</v>
+        <v>20.92232342278467</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09552908660064195</v>
+        <v>0.09550041721922312</v>
       </c>
       <c r="C13">
-        <v>17024.84944338703</v>
+        <v>16843.77239394985</v>
       </c>
       <c r="D13">
-        <v>15725.00444338703</v>
+        <v>15732.43239394985</v>
       </c>
       <c r="E13">
-        <v>-4478.045</v>
+        <v>-4289.540000000001</v>
       </c>
       <c r="F13">
-        <v>2073.555</v>
+        <v>2262.06</v>
       </c>
       <c r="G13">
         <v>3373.4</v>
@@ -2359,28 +2359,28 @@
         <v>3000.3</v>
       </c>
       <c r="M13">
-        <v>143.4018554905158</v>
+        <v>156.4383878078354</v>
       </c>
       <c r="N13">
-        <v>2856.898144509485</v>
+        <v>2843.861612192165</v>
       </c>
       <c r="O13">
-        <v>628.5175917920866</v>
+        <v>625.6495546822763</v>
       </c>
       <c r="P13">
-        <v>2228.380552717398</v>
+        <v>2218.212057509889</v>
       </c>
       <c r="Q13">
-        <v>3254.680552717398</v>
+        <v>3244.512057509889</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1006689596754832</v>
+        <v>0.1011673594563958</v>
       </c>
       <c r="T13">
-        <v>0.7984102190722897</v>
+        <v>0.8056625431662311</v>
       </c>
       <c r="U13">
         <v>0.06915748822216713</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.92232342278467</v>
+        <v>19.17879647088595</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09550041721922312</v>
+        <v>0.09547174783780425</v>
       </c>
       <c r="C14">
-        <v>16843.77239394985</v>
+        <v>16662.70236524513</v>
       </c>
       <c r="D14">
-        <v>15732.43239394985</v>
+        <v>15739.86736524513</v>
       </c>
       <c r="E14">
-        <v>-4289.540000000001</v>
+        <v>-4101.035</v>
       </c>
       <c r="F14">
-        <v>2262.06</v>
+        <v>2450.565</v>
       </c>
       <c r="G14">
         <v>3373.4</v>
@@ -2441,28 +2441,28 @@
         <v>3000.3</v>
       </c>
       <c r="M14">
-        <v>156.4383878078354</v>
+        <v>169.474920125155</v>
       </c>
       <c r="N14">
-        <v>2843.861612192165</v>
+        <v>2830.825079874845</v>
       </c>
       <c r="O14">
-        <v>625.6495546822763</v>
+        <v>622.7815175724659</v>
       </c>
       <c r="P14">
-        <v>2218.212057509889</v>
+        <v>2208.043562302379</v>
       </c>
       <c r="Q14">
-        <v>3244.512057509889</v>
+        <v>3234.343562302379</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1011673594563958</v>
+        <v>0.1016772167035362</v>
       </c>
       <c r="T14">
-        <v>0.8056625431662311</v>
+        <v>0.813081587354286</v>
       </c>
       <c r="U14">
         <v>0.06915748822216713</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.17879647088595</v>
+        <v>17.70350443466395</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09547174783780425</v>
+        <v>0.09544307845638542</v>
       </c>
       <c r="C15">
-        <v>16662.70236524513</v>
+        <v>16481.6393672313</v>
       </c>
       <c r="D15">
-        <v>15739.86736524513</v>
+        <v>15747.3093672313</v>
       </c>
       <c r="E15">
-        <v>-4101.035</v>
+        <v>-3912.53</v>
       </c>
       <c r="F15">
-        <v>2450.565</v>
+        <v>2639.07</v>
       </c>
       <c r="G15">
         <v>3373.4</v>
@@ -2523,28 +2523,28 @@
         <v>3000.3</v>
       </c>
       <c r="M15">
-        <v>169.474920125155</v>
+        <v>182.5114524424746</v>
       </c>
       <c r="N15">
-        <v>2830.825079874845</v>
+        <v>2817.788547557525</v>
       </c>
       <c r="O15">
-        <v>622.7815175724659</v>
+        <v>619.9134804626556</v>
       </c>
       <c r="P15">
-        <v>2208.043562302379</v>
+        <v>2197.87506709487</v>
       </c>
       <c r="Q15">
-        <v>3234.343562302379</v>
+        <v>3224.17506709487</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1016772167035362</v>
+        <v>0.102198931095959</v>
       </c>
       <c r="T15">
-        <v>0.813081587354286</v>
+        <v>0.8206731674536911</v>
       </c>
       <c r="U15">
         <v>0.06915748822216713</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.70350443466395</v>
+        <v>16.43896840361652</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09544307845638542</v>
+        <v>0.09541440907496657</v>
       </c>
       <c r="C16">
-        <v>16481.6393672313</v>
+        <v>16300.58340988569</v>
       </c>
       <c r="D16">
-        <v>15747.3093672313</v>
+        <v>15754.75840988569</v>
       </c>
       <c r="E16">
-        <v>-3912.53</v>
+        <v>-3724.025</v>
       </c>
       <c r="F16">
-        <v>2639.07</v>
+        <v>2827.575</v>
       </c>
       <c r="G16">
         <v>3373.4</v>
@@ -2605,28 +2605,28 @@
         <v>3000.3</v>
       </c>
       <c r="M16">
-        <v>182.5114524424746</v>
+        <v>195.5479847597942</v>
       </c>
       <c r="N16">
-        <v>2817.788547557525</v>
+        <v>2804.752015240206</v>
       </c>
       <c r="O16">
-        <v>619.9134804626556</v>
+        <v>617.0454433528453</v>
       </c>
       <c r="P16">
-        <v>2197.87506709487</v>
+        <v>2187.70657188736</v>
       </c>
       <c r="Q16">
-        <v>3224.17506709487</v>
+        <v>3214.00657188736</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.102198931095959</v>
+        <v>0.1027329211211447</v>
       </c>
       <c r="T16">
-        <v>0.8206731674536911</v>
+        <v>0.8284433729671999</v>
       </c>
       <c r="U16">
         <v>0.06915748822216713</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.43896840361652</v>
+        <v>15.34303717670875</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09541440907496657</v>
+        <v>0.09538573969354772</v>
       </c>
       <c r="C17">
-        <v>16300.58340988569</v>
+        <v>16119.53450320447</v>
       </c>
       <c r="D17">
-        <v>15754.75840988569</v>
+        <v>15762.21450320447</v>
       </c>
       <c r="E17">
-        <v>-3724.025000000001</v>
+        <v>-3535.52</v>
       </c>
       <c r="F17">
-        <v>2827.575</v>
+        <v>3016.08</v>
       </c>
       <c r="G17">
         <v>3373.4</v>
@@ -2687,28 +2687,28 @@
         <v>3000.3</v>
       </c>
       <c r="M17">
-        <v>195.5479847597942</v>
+        <v>208.5845170771138</v>
       </c>
       <c r="N17">
-        <v>2804.752015240206</v>
+        <v>2791.715482922886</v>
       </c>
       <c r="O17">
-        <v>617.0454433528453</v>
+        <v>614.177406243035</v>
       </c>
       <c r="P17">
-        <v>2187.70657188736</v>
+        <v>2177.538076679851</v>
       </c>
       <c r="Q17">
-        <v>3214.00657188736</v>
+        <v>3203.838076679851</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1027329211211447</v>
+        <v>0.1032796251945491</v>
       </c>
       <c r="T17">
-        <v>0.8284433729671999</v>
+        <v>0.8363985833738874</v>
       </c>
       <c r="U17">
         <v>0.06915748822216713</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.34303717670876</v>
+        <v>14.38409735316446</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09538573969354772</v>
+        <v>0.09535707031212887</v>
       </c>
       <c r="C18">
-        <v>16119.53450320447</v>
+        <v>15938.4926572028</v>
       </c>
       <c r="D18">
-        <v>15762.21450320447</v>
+        <v>15769.6776572028</v>
       </c>
       <c r="E18">
-        <v>-3535.52</v>
+        <v>-3347.015</v>
       </c>
       <c r="F18">
-        <v>3016.08</v>
+        <v>3204.585</v>
       </c>
       <c r="G18">
         <v>3373.4</v>
@@ -2769,28 +2769,28 @@
         <v>3000.3</v>
       </c>
       <c r="M18">
-        <v>208.5845170771138</v>
+        <v>221.6210493944335</v>
       </c>
       <c r="N18">
-        <v>2791.715482922886</v>
+        <v>2778.678950605567</v>
       </c>
       <c r="O18">
-        <v>614.177406243035</v>
+        <v>611.3093691332247</v>
       </c>
       <c r="P18">
-        <v>2177.538076679851</v>
+        <v>2167.369581472342</v>
       </c>
       <c r="Q18">
-        <v>3203.838076679851</v>
+        <v>3193.669581472342</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1032796251945491</v>
+        <v>0.1038395028600838</v>
       </c>
       <c r="T18">
-        <v>0.8363985833738874</v>
+        <v>0.8445454855976037</v>
       </c>
       <c r="U18">
         <v>0.06915748822216713</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.38409735316446</v>
+        <v>13.5379739794489</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09535707031212887</v>
+        <v>0.09532840093071004</v>
       </c>
       <c r="C19">
-        <v>15938.4926572028</v>
+        <v>15757.45788191475</v>
       </c>
       <c r="D19">
-        <v>15769.6776572028</v>
+        <v>15777.14788191475</v>
       </c>
       <c r="E19">
-        <v>-3347.015</v>
+        <v>-3158.51</v>
       </c>
       <c r="F19">
-        <v>3204.585</v>
+        <v>3393.090000000001</v>
       </c>
       <c r="G19">
         <v>3373.4</v>
@@ -2851,28 +2851,28 @@
         <v>3000.3</v>
       </c>
       <c r="M19">
-        <v>221.6210493944335</v>
+        <v>234.6575817117531</v>
       </c>
       <c r="N19">
-        <v>2778.678950605567</v>
+        <v>2765.642418288247</v>
       </c>
       <c r="O19">
-        <v>611.3093691332247</v>
+        <v>608.4413320234144</v>
       </c>
       <c r="P19">
-        <v>2167.369581472342</v>
+        <v>2157.201086264833</v>
       </c>
       <c r="Q19">
-        <v>3193.669581472342</v>
+        <v>3183.501086264832</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1038395028600838</v>
+        <v>0.1044130360784363</v>
       </c>
       <c r="T19">
-        <v>0.8445454855976037</v>
+        <v>0.8528910927536056</v>
       </c>
       <c r="U19">
         <v>0.06915748822216713</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.5379739794489</v>
+        <v>12.78586431392396</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09532840093071004</v>
+        <v>0.09529973154929119</v>
       </c>
       <c r="C20">
-        <v>15757.45788191475</v>
+        <v>15576.43018739347</v>
       </c>
       <c r="D20">
-        <v>15777.14788191475</v>
+        <v>15784.62518739347</v>
       </c>
       <c r="E20">
-        <v>-3158.510000000001</v>
+        <v>-2970.005</v>
       </c>
       <c r="F20">
-        <v>3393.09</v>
+        <v>3581.595</v>
       </c>
       <c r="G20">
         <v>3373.4</v>
@@ -2933,28 +2933,28 @@
         <v>3000.3</v>
       </c>
       <c r="M20">
-        <v>234.6575817117531</v>
+        <v>247.6941140290727</v>
       </c>
       <c r="N20">
-        <v>2765.642418288247</v>
+        <v>2752.605885970927</v>
       </c>
       <c r="O20">
-        <v>608.4413320234144</v>
+        <v>605.5732949136041</v>
       </c>
       <c r="P20">
-        <v>2157.201086264833</v>
+        <v>2147.032591057323</v>
       </c>
       <c r="Q20">
-        <v>3183.501086264832</v>
+        <v>3173.332591057323</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1044130360784363</v>
+        <v>0.1050007306108222</v>
       </c>
       <c r="T20">
-        <v>0.8528910927536054</v>
+        <v>0.8614427642838297</v>
       </c>
       <c r="U20">
         <v>0.06915748822216713</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.78586431392396</v>
+        <v>12.11292408687533</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09529973154929119</v>
+        <v>0.09527106216787237</v>
       </c>
       <c r="C21">
-        <v>15576.43018739347</v>
+        <v>15395.40958371114</v>
       </c>
       <c r="D21">
-        <v>15784.62518739347</v>
+        <v>15792.10958371114</v>
       </c>
       <c r="E21">
-        <v>-2970.005</v>
+        <v>-2781.5</v>
       </c>
       <c r="F21">
-        <v>3581.595</v>
+        <v>3770.1</v>
       </c>
       <c r="G21">
         <v>3373.4</v>
@@ -3015,28 +3015,28 @@
         <v>3000.3</v>
       </c>
       <c r="M21">
-        <v>247.6941140290727</v>
+        <v>260.7306463463923</v>
       </c>
       <c r="N21">
-        <v>2752.605885970927</v>
+        <v>2739.569353653608</v>
       </c>
       <c r="O21">
-        <v>605.5732949136041</v>
+        <v>602.7052578037938</v>
       </c>
       <c r="P21">
-        <v>2147.032591057323</v>
+        <v>2136.864095849814</v>
       </c>
       <c r="Q21">
-        <v>3173.332591057323</v>
+        <v>3163.164095849814</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1050007306108222</v>
+        <v>0.1056031175065179</v>
       </c>
       <c r="T21">
-        <v>0.8614427642838297</v>
+        <v>0.8702082276023095</v>
       </c>
       <c r="U21">
         <v>0.06915748822216713</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.11292408687533</v>
+        <v>11.50727788253156</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09527106216787237</v>
+        <v>0.09524239278645349</v>
       </c>
       <c r="C22">
-        <v>15395.40958371114</v>
+        <v>15214.39608095908</v>
       </c>
       <c r="D22">
-        <v>15792.10958371114</v>
+        <v>15799.60108095908</v>
       </c>
       <c r="E22">
-        <v>-2781.5</v>
+        <v>-2592.995</v>
       </c>
       <c r="F22">
-        <v>3770.1</v>
+        <v>3958.605</v>
       </c>
       <c r="G22">
         <v>3373.4</v>
@@ -3097,28 +3097,28 @@
         <v>3000.3</v>
       </c>
       <c r="M22">
-        <v>260.7306463463923</v>
+        <v>273.7671786637119</v>
       </c>
       <c r="N22">
-        <v>2739.569353653608</v>
+        <v>2726.532821336288</v>
       </c>
       <c r="O22">
-        <v>602.7052578037938</v>
+        <v>599.8372206939835</v>
       </c>
       <c r="P22">
-        <v>2136.864095849814</v>
+        <v>2126.695600642305</v>
       </c>
       <c r="Q22">
-        <v>3163.164095849814</v>
+        <v>3152.995600642304</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1056031175065179</v>
+        <v>0.1062207547033703</v>
       </c>
       <c r="T22">
-        <v>0.8702082276023095</v>
+        <v>0.8791956013845483</v>
       </c>
       <c r="U22">
         <v>0.06915748822216713</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.50727788253156</v>
+        <v>10.95931226907768</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09524239278645349</v>
+        <v>0.09521372340503467</v>
       </c>
       <c r="C23">
-        <v>15214.39608095908</v>
+        <v>15033.38968924774</v>
       </c>
       <c r="D23">
-        <v>15799.60108095908</v>
+        <v>15807.09968924774</v>
       </c>
       <c r="E23">
-        <v>-2592.995</v>
+        <v>-2404.490000000001</v>
       </c>
       <c r="F23">
-        <v>3958.605</v>
+        <v>4147.11</v>
       </c>
       <c r="G23">
         <v>3373.4</v>
@@ -3179,28 +3179,28 @@
         <v>3000.3</v>
       </c>
       <c r="M23">
-        <v>273.7671786637119</v>
+        <v>286.8037109810315</v>
       </c>
       <c r="N23">
-        <v>2726.532821336288</v>
+        <v>2713.496289018969</v>
       </c>
       <c r="O23">
-        <v>599.8372206939835</v>
+        <v>596.969183584173</v>
       </c>
       <c r="P23">
-        <v>2126.695600642305</v>
+        <v>2116.527105434795</v>
       </c>
       <c r="Q23">
-        <v>3152.995600642304</v>
+        <v>3142.827105434795</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1062207547033703</v>
+        <v>0.1068542287514241</v>
       </c>
       <c r="T23">
-        <v>0.8791956013845482</v>
+        <v>0.8884134206483829</v>
       </c>
       <c r="U23">
         <v>0.06915748822216713</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.95931226907768</v>
+        <v>10.46116171139233</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09521372340503467</v>
+        <v>0.09518505402361582</v>
       </c>
       <c r="C24">
-        <v>15033.38968924774</v>
+        <v>14852.39041870679</v>
       </c>
       <c r="D24">
-        <v>15807.09968924774</v>
+        <v>15814.60541870679</v>
       </c>
       <c r="E24">
-        <v>-2404.490000000001</v>
+        <v>-2215.985000000001</v>
       </c>
       <c r="F24">
-        <v>4147.11</v>
+        <v>4335.615</v>
       </c>
       <c r="G24">
         <v>3373.4</v>
@@ -3261,28 +3261,28 @@
         <v>3000.3</v>
       </c>
       <c r="M24">
-        <v>286.8037109810315</v>
+        <v>299.8402432983511</v>
       </c>
       <c r="N24">
-        <v>2713.496289018969</v>
+        <v>2700.459756701649</v>
       </c>
       <c r="O24">
-        <v>596.969183584173</v>
+        <v>594.1011464743627</v>
       </c>
       <c r="P24">
-        <v>2116.527105434795</v>
+        <v>2106.358610227286</v>
       </c>
       <c r="Q24">
-        <v>3142.827105434795</v>
+        <v>3132.658610227286</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1068542287514241</v>
+        <v>0.1075041566708559</v>
       </c>
       <c r="T24">
-        <v>0.8884134206483829</v>
+        <v>0.8978706637892003</v>
       </c>
       <c r="U24">
         <v>0.06915748822216713</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.46116171139233</v>
+        <v>10.00632859350571</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09518505402361582</v>
+        <v>0.09515638464219697</v>
       </c>
       <c r="C25">
-        <v>14852.39041870679</v>
+        <v>14671.39827948515</v>
       </c>
       <c r="D25">
-        <v>15814.60541870679</v>
+        <v>15822.11827948515</v>
       </c>
       <c r="E25">
-        <v>-2215.985000000001</v>
+        <v>-2027.48</v>
       </c>
       <c r="F25">
-        <v>4335.615</v>
+        <v>4524.120000000001</v>
       </c>
       <c r="G25">
         <v>3373.4</v>
@@ -3343,28 +3343,28 @@
         <v>3000.3</v>
       </c>
       <c r="M25">
-        <v>299.8402432983511</v>
+        <v>312.8767756156709</v>
       </c>
       <c r="N25">
-        <v>2700.459756701649</v>
+        <v>2687.423224384329</v>
       </c>
       <c r="O25">
-        <v>594.1011464743627</v>
+        <v>591.2331093645524</v>
       </c>
       <c r="P25">
-        <v>2106.358610227286</v>
+        <v>2096.190115019777</v>
       </c>
       <c r="Q25">
-        <v>3132.658610227286</v>
+        <v>3122.490115019777</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1075041566708559</v>
+        <v>0.1081711879565885</v>
       </c>
       <c r="T25">
-        <v>0.8978706637892003</v>
+        <v>0.9075767817495128</v>
       </c>
       <c r="U25">
         <v>0.06915748822216713</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.00632859350571</v>
+        <v>9.589398235442971</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09515638464219697</v>
+        <v>0.09512771526077812</v>
       </c>
       <c r="C26">
-        <v>14671.39827948515</v>
+        <v>14490.41328175103</v>
       </c>
       <c r="D26">
-        <v>15822.11827948515</v>
+        <v>15829.63828175103</v>
       </c>
       <c r="E26">
-        <v>-2027.48</v>
+        <v>-1838.975</v>
       </c>
       <c r="F26">
-        <v>4524.12</v>
+        <v>4712.625</v>
       </c>
       <c r="G26">
         <v>3373.4</v>
@@ -3425,28 +3425,28 @@
         <v>3000.3</v>
       </c>
       <c r="M26">
-        <v>312.8767756156708</v>
+        <v>325.9133079329904</v>
       </c>
       <c r="N26">
-        <v>2687.423224384329</v>
+        <v>2674.38669206701</v>
       </c>
       <c r="O26">
-        <v>591.2331093645524</v>
+        <v>588.3650722547421</v>
       </c>
       <c r="P26">
-        <v>2096.190115019777</v>
+        <v>2086.021619812268</v>
       </c>
       <c r="Q26">
-        <v>3122.490115019777</v>
+        <v>3112.321619812267</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1081711879565885</v>
+        <v>0.108856006743274</v>
       </c>
       <c r="T26">
-        <v>0.9075767817495128</v>
+        <v>0.9175417295221003</v>
       </c>
       <c r="U26">
         <v>0.06915748822216713</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.589398235442973</v>
+        <v>9.205822306025254</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09512771526077812</v>
+        <v>0.09509904587935927</v>
       </c>
       <c r="C27">
-        <v>14490.41328175103</v>
+        <v>14309.43543569196</v>
       </c>
       <c r="D27">
-        <v>15829.63828175103</v>
+        <v>15837.16543569196</v>
       </c>
       <c r="E27">
-        <v>-1838.975</v>
+        <v>-1650.47</v>
       </c>
       <c r="F27">
-        <v>4712.625</v>
+        <v>4901.13</v>
       </c>
       <c r="G27">
         <v>3373.4</v>
@@ -3507,28 +3507,28 @@
         <v>3000.3</v>
       </c>
       <c r="M27">
-        <v>325.9133079329904</v>
+        <v>338.94984025031</v>
       </c>
       <c r="N27">
-        <v>2674.38669206701</v>
+        <v>2661.35015974969</v>
       </c>
       <c r="O27">
-        <v>588.3650722547421</v>
+        <v>585.4970351449318</v>
       </c>
       <c r="P27">
-        <v>2086.021619812268</v>
+        <v>2075.853124604758</v>
       </c>
       <c r="Q27">
-        <v>3112.321619812267</v>
+        <v>3102.153124604758</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.108856006743274</v>
+        <v>0.1095593341458159</v>
       </c>
       <c r="T27">
-        <v>0.9175417295221003</v>
+        <v>0.9277760002074606</v>
       </c>
       <c r="U27">
         <v>0.06915748822216713</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.205822306025254</v>
+        <v>8.851752217331974</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09509904587935927</v>
+        <v>0.09538627649794043</v>
       </c>
       <c r="C28">
-        <v>14309.43543569196</v>
+        <v>14045.83983076756</v>
       </c>
       <c r="D28">
-        <v>15837.16543569196</v>
+        <v>15762.07483076756</v>
       </c>
       <c r="E28">
-        <v>-1650.47</v>
+        <v>-1461.965</v>
       </c>
       <c r="F28">
-        <v>4901.13</v>
+        <v>5089.635</v>
       </c>
       <c r="G28">
         <v>3373.4</v>
@@ -3589,45 +3589,45 @@
         <v>3000.3</v>
       </c>
       <c r="M28">
-        <v>338.94984025031</v>
+        <v>359.6208250676297</v>
       </c>
       <c r="N28">
-        <v>2661.35015974969</v>
+        <v>2640.679174932371</v>
       </c>
       <c r="O28">
-        <v>585.4970351449318</v>
+        <v>580.9494184851216</v>
       </c>
       <c r="P28">
-        <v>2075.853124604758</v>
+        <v>2059.729756447249</v>
       </c>
       <c r="Q28">
-        <v>3102.153124604758</v>
+        <v>3086.029756447249</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1095593341458159</v>
+        <v>0.1102819307922631</v>
       </c>
       <c r="T28">
-        <v>0.9277760002074606</v>
+        <v>0.9382906618705019</v>
       </c>
       <c r="U28">
-        <v>0.06915748822216713</v>
+        <v>0.07065748822216714</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.05394284081329036</v>
+        <v>0.05511284081329037</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>8.851752217331974</v>
+        <v>8.342953997271346</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09538627649794043</v>
+        <v>0.0953693071165216</v>
       </c>
       <c r="C29">
-        <v>14045.83983076756</v>
+        <v>13861.75133330042</v>
       </c>
       <c r="D29">
-        <v>15762.07483076756</v>
+        <v>15766.49133330042</v>
       </c>
       <c r="E29">
-        <v>-1461.965</v>
+        <v>-1273.46</v>
       </c>
       <c r="F29">
-        <v>5089.635</v>
+        <v>5278.14</v>
       </c>
       <c r="G29">
         <v>3373.4</v>
@@ -3671,28 +3671,28 @@
         <v>3000.3</v>
       </c>
       <c r="M29">
-        <v>359.6208250676297</v>
+        <v>372.9401148849493</v>
       </c>
       <c r="N29">
-        <v>2640.679174932371</v>
+        <v>2627.359885115051</v>
       </c>
       <c r="O29">
-        <v>580.9494184851216</v>
+        <v>578.0191747253112</v>
       </c>
       <c r="P29">
-        <v>2059.729756447249</v>
+        <v>2049.34071038974</v>
       </c>
       <c r="Q29">
-        <v>3086.029756447249</v>
+        <v>3075.64071038974</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1102819307922631</v>
+        <v>0.1110245995677782</v>
       </c>
       <c r="T29">
-        <v>0.9382906618705019</v>
+        <v>0.9490973974686278</v>
       </c>
       <c r="U29">
         <v>0.07065748822216714</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.342953997271346</v>
+        <v>8.044991354511655</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0953693071165216</v>
+        <v>0.09535233773510274</v>
       </c>
       <c r="C30">
-        <v>13861.75133330042</v>
+        <v>13677.6653115177</v>
       </c>
       <c r="D30">
-        <v>15766.49133330042</v>
+        <v>15770.9103115177</v>
       </c>
       <c r="E30">
-        <v>-1273.46</v>
+        <v>-1084.955</v>
       </c>
       <c r="F30">
-        <v>5278.14</v>
+        <v>5466.645</v>
       </c>
       <c r="G30">
         <v>3373.4</v>
@@ -3753,28 +3753,28 @@
         <v>3000.3</v>
       </c>
       <c r="M30">
-        <v>372.9401148849493</v>
+        <v>386.2594047022689</v>
       </c>
       <c r="N30">
-        <v>2627.359885115051</v>
+        <v>2614.040595297731</v>
       </c>
       <c r="O30">
-        <v>578.0191747253112</v>
+        <v>575.0889309655008</v>
       </c>
       <c r="P30">
-        <v>2049.34071038974</v>
+        <v>2038.95166433223</v>
       </c>
       <c r="Q30">
-        <v>3075.64071038974</v>
+        <v>3065.25166433223</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1110245995677782</v>
+        <v>0.1117881885904909</v>
       </c>
       <c r="T30">
-        <v>0.9490973974686278</v>
+        <v>0.9602085481540246</v>
       </c>
       <c r="U30">
         <v>0.07065748822216714</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.044991354511655</v>
+        <v>7.767577859528494</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09535233773510274</v>
+        <v>0.09533536835368389</v>
       </c>
       <c r="C31">
-        <v>13677.6653115177</v>
+        <v>13493.58176750162</v>
       </c>
       <c r="D31">
-        <v>15770.9103115177</v>
+        <v>15775.33176750162</v>
       </c>
       <c r="E31">
-        <v>-1084.955000000001</v>
+        <v>-896.4500000000007</v>
       </c>
       <c r="F31">
-        <v>5466.645</v>
+        <v>5655.15</v>
       </c>
       <c r="G31">
         <v>3373.4</v>
@@ -3835,28 +3835,28 @@
         <v>3000.3</v>
       </c>
       <c r="M31">
-        <v>386.2594047022689</v>
+        <v>399.5786945195885</v>
       </c>
       <c r="N31">
-        <v>2614.040595297731</v>
+        <v>2600.721305480412</v>
       </c>
       <c r="O31">
-        <v>575.0889309655008</v>
+        <v>572.1586872056905</v>
       </c>
       <c r="P31">
-        <v>2038.95166433223</v>
+        <v>2028.562618274721</v>
       </c>
       <c r="Q31">
-        <v>3065.25166433223</v>
+        <v>3054.862618274721</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1117881885904909</v>
+        <v>0.112573594442424</v>
       </c>
       <c r="T31">
-        <v>0.9602085481540246</v>
+        <v>0.9716371602875757</v>
       </c>
       <c r="U31">
         <v>0.07065748822216714</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.767577859528495</v>
+        <v>7.508658597544212</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09533536835368389</v>
+        <v>0.09531839897226504</v>
       </c>
       <c r="C32">
-        <v>13493.58176750162</v>
+        <v>13309.50070333672</v>
       </c>
       <c r="D32">
-        <v>15775.33176750162</v>
+        <v>15779.75570333672</v>
       </c>
       <c r="E32">
-        <v>-896.4500000000007</v>
+        <v>-707.9450000000006</v>
       </c>
       <c r="F32">
-        <v>5655.15</v>
+        <v>5843.655</v>
       </c>
       <c r="G32">
         <v>3373.4</v>
@@ -3917,28 +3917,28 @@
         <v>3000.3</v>
       </c>
       <c r="M32">
-        <v>399.5786945195885</v>
+        <v>412.8979843369081</v>
       </c>
       <c r="N32">
-        <v>2600.721305480412</v>
+        <v>2587.402015663092</v>
       </c>
       <c r="O32">
-        <v>572.1586872056905</v>
+        <v>569.2284434458803</v>
       </c>
       <c r="P32">
-        <v>2028.562618274721</v>
+        <v>2018.173572217212</v>
       </c>
       <c r="Q32">
-        <v>3054.862618274721</v>
+        <v>3044.473572217212</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.112573594442424</v>
+        <v>0.1133817656813696</v>
       </c>
       <c r="T32">
-        <v>0.9716371602875757</v>
+        <v>0.9833970365409399</v>
       </c>
       <c r="U32">
         <v>0.07065748822216714</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.508658597544212</v>
+        <v>7.266443804075045</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09531839897226504</v>
+        <v>0.0953014295908462</v>
       </c>
       <c r="C33">
-        <v>13309.50070333672</v>
+        <v>13125.42212110988</v>
       </c>
       <c r="D33">
-        <v>15779.75570333672</v>
+        <v>15784.18212110988</v>
       </c>
       <c r="E33">
-        <v>-707.9450000000006</v>
+        <v>-519.4400000000005</v>
       </c>
       <c r="F33">
-        <v>5843.655</v>
+        <v>6032.16</v>
       </c>
       <c r="G33">
         <v>3373.4</v>
@@ -3999,28 +3999,28 @@
         <v>3000.3</v>
       </c>
       <c r="M33">
-        <v>412.8979843369081</v>
+        <v>426.2172741542277</v>
       </c>
       <c r="N33">
-        <v>2587.402015663092</v>
+        <v>2574.082725845773</v>
       </c>
       <c r="O33">
-        <v>569.2284434458803</v>
+        <v>566.29819968607</v>
       </c>
       <c r="P33">
-        <v>2018.173572217212</v>
+        <v>2007.784526159703</v>
       </c>
       <c r="Q33">
-        <v>3044.473572217212</v>
+        <v>3034.084526159702</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1133817656813696</v>
+        <v>0.1142137066626372</v>
       </c>
       <c r="T33">
-        <v>0.9833970365409399</v>
+        <v>0.9955027915076384</v>
       </c>
       <c r="U33">
         <v>0.07065748822216714</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.266443804075045</v>
+        <v>7.039367435197699</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0953014295908462</v>
+        <v>0.09528446020942737</v>
       </c>
       <c r="C34">
-        <v>13125.42212110988</v>
+        <v>12941.34602291035</v>
       </c>
       <c r="D34">
-        <v>15784.18212110988</v>
+        <v>15788.61102291035</v>
       </c>
       <c r="E34">
-        <v>-519.4400000000005</v>
+        <v>-330.9350000000004</v>
       </c>
       <c r="F34">
-        <v>6032.16</v>
+        <v>6220.665</v>
       </c>
       <c r="G34">
         <v>3373.4</v>
@@ -4081,28 +4081,28 @@
         <v>3000.3</v>
       </c>
       <c r="M34">
-        <v>426.2172741542277</v>
+        <v>439.5365639715473</v>
       </c>
       <c r="N34">
-        <v>2574.082725845773</v>
+        <v>2560.763436028453</v>
       </c>
       <c r="O34">
-        <v>566.29819968607</v>
+        <v>563.3679559262596</v>
       </c>
       <c r="P34">
-        <v>2007.784526159703</v>
+        <v>1997.395480102193</v>
       </c>
       <c r="Q34">
-        <v>3034.084526159702</v>
+        <v>3023.695480102193</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1142137066626372</v>
+        <v>0.1150704817030471</v>
       </c>
       <c r="T34">
-        <v>0.9955027915076384</v>
+        <v>1.007969912294238</v>
       </c>
       <c r="U34">
         <v>0.07065748822216714</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.039367435197699</v>
+        <v>6.826053270494738</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09528446020942737</v>
+        <v>0.0957183308280085</v>
       </c>
       <c r="C35">
-        <v>12941.34602291035</v>
+        <v>12640.37856573124</v>
       </c>
       <c r="D35">
-        <v>15788.61102291035</v>
+        <v>15676.14856573124</v>
       </c>
       <c r="E35">
-        <v>-330.9350000000004</v>
+        <v>-142.4300000000003</v>
       </c>
       <c r="F35">
-        <v>6220.665</v>
+        <v>6409.17</v>
       </c>
       <c r="G35">
         <v>3373.4</v>
@@ -4163,45 +4163,45 @@
         <v>3000.3</v>
       </c>
       <c r="M35">
-        <v>439.5365639715473</v>
+        <v>463.7514427888669</v>
       </c>
       <c r="N35">
-        <v>2560.763436028453</v>
+        <v>2536.548557211133</v>
       </c>
       <c r="O35">
-        <v>563.3679559262596</v>
+        <v>558.0406825864493</v>
       </c>
       <c r="P35">
-        <v>1997.395480102193</v>
+        <v>1978.507874624684</v>
       </c>
       <c r="Q35">
-        <v>3023.695480102193</v>
+        <v>3004.807874624684</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1150704817030471</v>
+        <v>0.1159532196234694</v>
       </c>
       <c r="T35">
-        <v>1.007969912294238</v>
+        <v>1.020814824619826</v>
       </c>
       <c r="U35">
-        <v>0.07065748822216714</v>
+        <v>0.07235748822216713</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.05511284081329037</v>
+        <v>0.05643884081329036</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.826053270494738</v>
+        <v>6.469629467796509</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0957183308280085</v>
+        <v>0.09571462144658968</v>
       </c>
       <c r="C36">
-        <v>12640.37856573124</v>
+        <v>12452.8282740642</v>
       </c>
       <c r="D36">
-        <v>15676.14856573124</v>
+        <v>15677.1032740642</v>
       </c>
       <c r="E36">
-        <v>-142.4300000000003</v>
+        <v>46.07499999999982</v>
       </c>
       <c r="F36">
-        <v>6409.17</v>
+        <v>6597.675</v>
       </c>
       <c r="G36">
         <v>3373.4</v>
@@ -4245,28 +4245,28 @@
         <v>3000.3</v>
       </c>
       <c r="M36">
-        <v>463.7514427888669</v>
+        <v>477.3911911061865</v>
       </c>
       <c r="N36">
-        <v>2536.548557211133</v>
+        <v>2522.908808893814</v>
       </c>
       <c r="O36">
-        <v>558.0406825864493</v>
+        <v>555.0399379566391</v>
       </c>
       <c r="P36">
-        <v>1978.507874624684</v>
+        <v>1967.868870937175</v>
       </c>
       <c r="Q36">
-        <v>3004.807874624684</v>
+        <v>2994.168870937175</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1159532196234694</v>
+        <v>0.1168631187106739</v>
       </c>
       <c r="T36">
-        <v>1.020814824619826</v>
+        <v>1.03405496501697</v>
       </c>
       <c r="U36">
         <v>0.07235748822216713</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.469629467796509</v>
+        <v>6.284782911573752</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09571462144658968</v>
+        <v>0.09571091206517082</v>
       </c>
       <c r="C37">
-        <v>12452.8282740642</v>
+        <v>12265.2780986915</v>
       </c>
       <c r="D37">
-        <v>15677.1032740642</v>
+        <v>15678.0580986915</v>
       </c>
       <c r="E37">
-        <v>46.07499999999982</v>
+        <v>234.5800000000008</v>
       </c>
       <c r="F37">
-        <v>6597.675</v>
+        <v>6786.180000000001</v>
       </c>
       <c r="G37">
         <v>3373.4</v>
@@ -4327,28 +4327,28 @@
         <v>3000.3</v>
       </c>
       <c r="M37">
-        <v>477.3911911061865</v>
+        <v>491.0309394235062</v>
       </c>
       <c r="N37">
-        <v>2522.908808893814</v>
+        <v>2509.269060576494</v>
       </c>
       <c r="O37">
-        <v>555.0399379566391</v>
+        <v>552.0391933268286</v>
       </c>
       <c r="P37">
-        <v>1967.868870937175</v>
+        <v>1957.229867249665</v>
       </c>
       <c r="Q37">
-        <v>2994.168870937175</v>
+        <v>2983.529867249665</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1168631187106739</v>
+        <v>0.1178014521443536</v>
       </c>
       <c r="T37">
-        <v>1.03405496501697</v>
+        <v>1.047708859801525</v>
       </c>
       <c r="U37">
         <v>0.07235748822216713</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.284782911573752</v>
+        <v>6.110205608474479</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09571091206517082</v>
+        <v>0.09570720268375199</v>
       </c>
       <c r="C38">
-        <v>12265.2780986915</v>
+        <v>12077.72803963436</v>
       </c>
       <c r="D38">
-        <v>15678.0580986915</v>
+        <v>15679.01303963436</v>
       </c>
       <c r="E38">
-        <v>234.579999999999</v>
+        <v>423.0849999999991</v>
       </c>
       <c r="F38">
-        <v>6786.179999999999</v>
+        <v>6974.684999999999</v>
       </c>
       <c r="G38">
         <v>3373.4</v>
@@ -4409,28 +4409,28 @@
         <v>3000.3</v>
       </c>
       <c r="M38">
-        <v>491.0309394235061</v>
+        <v>504.6706877408257</v>
       </c>
       <c r="N38">
-        <v>2509.269060576494</v>
+        <v>2495.629312259175</v>
       </c>
       <c r="O38">
-        <v>552.0391933268287</v>
+        <v>549.0384486970185</v>
       </c>
       <c r="P38">
-        <v>1957.229867249665</v>
+        <v>1946.590863562156</v>
       </c>
       <c r="Q38">
-        <v>2983.529867249665</v>
+        <v>2972.890863562156</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1178014521443536</v>
+        <v>0.1187695739410072</v>
       </c>
       <c r="T38">
-        <v>1.047708859801525</v>
+        <v>1.061796211563368</v>
       </c>
       <c r="U38">
         <v>0.07235748822216713</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.110205608474482</v>
+        <v>5.94506491635355</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09570720268375199</v>
+        <v>0.09570349330233315</v>
       </c>
       <c r="C39">
-        <v>12077.72803963436</v>
+        <v>11890.17809691405</v>
       </c>
       <c r="D39">
-        <v>15679.01303963436</v>
+        <v>15679.96809691405</v>
       </c>
       <c r="E39">
-        <v>423.0849999999991</v>
+        <v>611.5900000000001</v>
       </c>
       <c r="F39">
-        <v>6974.684999999999</v>
+        <v>7163.190000000001</v>
       </c>
       <c r="G39">
         <v>3373.4</v>
@@ -4491,28 +4491,28 @@
         <v>3000.3</v>
       </c>
       <c r="M39">
-        <v>504.6706877408257</v>
+        <v>518.3104360581453</v>
       </c>
       <c r="N39">
-        <v>2495.629312259175</v>
+        <v>2481.989563941855</v>
       </c>
       <c r="O39">
-        <v>549.0384486970185</v>
+        <v>546.037704067208</v>
       </c>
       <c r="P39">
-        <v>1946.590863562156</v>
+        <v>1935.951859874647</v>
       </c>
       <c r="Q39">
-        <v>2972.890863562156</v>
+        <v>2962.251859874646</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1187695739410072</v>
+        <v>0.1197689254730368</v>
       </c>
       <c r="T39">
-        <v>1.061796211563368</v>
+        <v>1.076337994027205</v>
       </c>
       <c r="U39">
         <v>0.07235748822216713</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.94506491635355</v>
+        <v>5.788615839607402</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09570349330233315</v>
+        <v>0.09569978392091429</v>
       </c>
       <c r="C40">
-        <v>11890.17809691405</v>
+        <v>11702.62827055182</v>
       </c>
       <c r="D40">
-        <v>15679.96809691405</v>
+        <v>15680.92327055182</v>
       </c>
       <c r="E40">
-        <v>611.5900000000001</v>
+        <v>800.0950000000003</v>
       </c>
       <c r="F40">
-        <v>7163.190000000001</v>
+        <v>7351.695000000001</v>
       </c>
       <c r="G40">
         <v>3373.4</v>
@@ -4573,28 +4573,28 @@
         <v>3000.3</v>
       </c>
       <c r="M40">
-        <v>518.3104360581453</v>
+        <v>531.950184375465</v>
       </c>
       <c r="N40">
-        <v>2481.989563941855</v>
+        <v>2468.349815624535</v>
       </c>
       <c r="O40">
-        <v>546.037704067208</v>
+        <v>543.0369594373977</v>
       </c>
       <c r="P40">
-        <v>1935.951859874647</v>
+        <v>1925.312856187137</v>
       </c>
       <c r="Q40">
-        <v>2962.251859874646</v>
+        <v>2951.612856187137</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1197689254730368</v>
+        <v>0.1208010426290673</v>
       </c>
       <c r="T40">
-        <v>1.076337994027205</v>
+        <v>1.091356556243956</v>
       </c>
       <c r="U40">
         <v>0.07235748822216713</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.788615839607402</v>
+        <v>5.640189792437981</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09569978392091429</v>
+        <v>0.09594567453949544</v>
       </c>
       <c r="C41">
-        <v>11702.62827055182</v>
+        <v>11451.05672335466</v>
       </c>
       <c r="D41">
-        <v>15680.92327055182</v>
+        <v>15617.85672335466</v>
       </c>
       <c r="E41">
-        <v>800.0950000000003</v>
+        <v>988.6000000000004</v>
       </c>
       <c r="F41">
-        <v>7351.695000000001</v>
+        <v>7540.200000000001</v>
       </c>
       <c r="G41">
         <v>3373.4</v>
@@ -4655,45 +4655,45 @@
         <v>3000.3</v>
       </c>
       <c r="M41">
-        <v>531.950184375465</v>
+        <v>551.6220926927847</v>
       </c>
       <c r="N41">
-        <v>2468.349815624535</v>
+        <v>2448.677907307216</v>
       </c>
       <c r="O41">
-        <v>543.0369594373977</v>
+        <v>538.7091396075874</v>
       </c>
       <c r="P41">
-        <v>1925.312856187137</v>
+        <v>1909.968767699628</v>
       </c>
       <c r="Q41">
-        <v>2951.612856187137</v>
+        <v>2936.268767699628</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1208010426290673</v>
+        <v>0.1218675636902988</v>
       </c>
       <c r="T41">
-        <v>1.091356556243956</v>
+        <v>1.106875737201264</v>
       </c>
       <c r="U41">
-        <v>0.07235748822216713</v>
+        <v>0.07315748822216714</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.05643884081329036</v>
+        <v>0.05706284081329037</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>5.640189792437981</v>
+        <v>5.439049740291964</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09594567453949544</v>
+        <v>0.0959482051580766</v>
       </c>
       <c r="C42">
-        <v>11451.05672335466</v>
+        <v>11261.90530211684</v>
       </c>
       <c r="D42">
-        <v>15617.85672335466</v>
+        <v>15617.21030211685</v>
       </c>
       <c r="E42">
-        <v>988.6000000000004</v>
+        <v>1177.105</v>
       </c>
       <c r="F42">
-        <v>7540.200000000001</v>
+        <v>7728.705000000001</v>
       </c>
       <c r="G42">
         <v>3373.4</v>
@@ -4737,28 +4737,28 @@
         <v>3000.3</v>
       </c>
       <c r="M42">
-        <v>551.6220926927847</v>
+        <v>565.4126450101044</v>
       </c>
       <c r="N42">
-        <v>2448.677907307216</v>
+        <v>2434.887354989896</v>
       </c>
       <c r="O42">
-        <v>538.7091396075874</v>
+        <v>535.6752180977771</v>
       </c>
       <c r="P42">
-        <v>1909.968767699628</v>
+        <v>1899.212136892119</v>
       </c>
       <c r="Q42">
-        <v>2936.268767699628</v>
+        <v>2925.512136892118</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1218675636902988</v>
+        <v>0.1229702380078433</v>
       </c>
       <c r="T42">
-        <v>1.106875737201264</v>
+        <v>1.122920992089329</v>
       </c>
       <c r="U42">
         <v>0.07315748822216714</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.439049740291964</v>
+        <v>5.306389990528745</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0959482051580766</v>
+        <v>0.09595073577665776</v>
       </c>
       <c r="C43">
-        <v>11261.90530211684</v>
+        <v>11072.75393438741</v>
       </c>
       <c r="D43">
-        <v>15617.21030211685</v>
+        <v>15616.56393438741</v>
       </c>
       <c r="E43">
-        <v>1177.105</v>
+        <v>1365.610000000001</v>
       </c>
       <c r="F43">
-        <v>7728.705000000001</v>
+        <v>7917.210000000001</v>
       </c>
       <c r="G43">
         <v>3373.4</v>
@@ -4819,28 +4819,28 @@
         <v>3000.3</v>
       </c>
       <c r="M43">
-        <v>565.4126450101044</v>
+        <v>579.2031973274239</v>
       </c>
       <c r="N43">
-        <v>2434.887354989896</v>
+        <v>2421.096802672576</v>
       </c>
       <c r="O43">
-        <v>535.6752180977771</v>
+        <v>532.6412965879668</v>
       </c>
       <c r="P43">
-        <v>1899.212136892119</v>
+        <v>1888.45550608461</v>
       </c>
       <c r="Q43">
-        <v>2925.512136892118</v>
+        <v>2914.755506084609</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1229702380078433</v>
+        <v>0.1241109355777169</v>
       </c>
       <c r="T43">
-        <v>1.122920992089329</v>
+        <v>1.139519531628706</v>
       </c>
       <c r="U43">
         <v>0.07315748822216714</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.306389990528745</v>
+        <v>5.180047371706633</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09595073577665778</v>
+        <v>0.09595326639523892</v>
       </c>
       <c r="C44">
-        <v>11072.75393438741</v>
+        <v>10883.60262015972</v>
       </c>
       <c r="D44">
-        <v>15616.56393438741</v>
+        <v>15615.91762015971</v>
       </c>
       <c r="E44">
-        <v>1365.61</v>
+        <v>1554.115</v>
       </c>
       <c r="F44">
-        <v>7917.21</v>
+        <v>8105.715</v>
       </c>
       <c r="G44">
         <v>3373.4</v>
@@ -4901,28 +4901,28 @@
         <v>3000.3</v>
       </c>
       <c r="M44">
-        <v>579.2031973274239</v>
+        <v>592.9937496447435</v>
       </c>
       <c r="N44">
-        <v>2421.096802672576</v>
+        <v>2407.306250355256</v>
       </c>
       <c r="O44">
-        <v>532.6412965879668</v>
+        <v>529.6073750781565</v>
       </c>
       <c r="P44">
-        <v>1888.45550608461</v>
+        <v>1877.6988752771</v>
       </c>
       <c r="Q44">
-        <v>2914.755506084609</v>
+        <v>2903.9988752771</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1241109355777169</v>
+        <v>0.1252916576237264</v>
       </c>
       <c r="T44">
-        <v>1.139519531628706</v>
+        <v>1.156700476064202</v>
       </c>
       <c r="U44">
         <v>0.07315748822216714</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.180047371706633</v>
+        <v>5.059581153759966</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09595326639523892</v>
+        <v>0.09595579701382009</v>
       </c>
       <c r="C45">
-        <v>10883.60262015972</v>
+        <v>10694.45135942711</v>
       </c>
       <c r="D45">
-        <v>15615.91762015971</v>
+        <v>15615.27135942711</v>
       </c>
       <c r="E45">
-        <v>1554.115</v>
+        <v>1742.619999999999</v>
       </c>
       <c r="F45">
-        <v>8105.715</v>
+        <v>8294.219999999999</v>
       </c>
       <c r="G45">
         <v>3373.4</v>
@@ -4983,28 +4983,28 @@
         <v>3000.3</v>
       </c>
       <c r="M45">
-        <v>592.9937496447435</v>
+        <v>606.7843019620631</v>
       </c>
       <c r="N45">
-        <v>2407.306250355256</v>
+        <v>2393.515698037937</v>
       </c>
       <c r="O45">
-        <v>529.6073750781565</v>
+        <v>526.5734535683462</v>
       </c>
       <c r="P45">
-        <v>1877.6988752771</v>
+        <v>1866.942244469591</v>
       </c>
       <c r="Q45">
-        <v>2903.9988752771</v>
+        <v>2893.24224446959</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1252916576237264</v>
+        <v>0.1265145483142363</v>
       </c>
       <c r="T45">
-        <v>1.156700476064202</v>
+        <v>1.174495025658108</v>
       </c>
       <c r="U45">
         <v>0.07315748822216714</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.059581153759966</v>
+        <v>4.944590672992695</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09595579701382009</v>
+        <v>0.09595832763240125</v>
       </c>
       <c r="C46">
-        <v>10694.45135942711</v>
+        <v>10505.30015218297</v>
       </c>
       <c r="D46">
-        <v>15615.27135942711</v>
+        <v>15614.62515218297</v>
       </c>
       <c r="E46">
-        <v>1742.619999999999</v>
+        <v>1931.125</v>
       </c>
       <c r="F46">
-        <v>8294.219999999999</v>
+        <v>8482.725</v>
       </c>
       <c r="G46">
         <v>3373.4</v>
@@ -5065,28 +5065,28 @@
         <v>3000.3</v>
       </c>
       <c r="M46">
-        <v>606.7843019620631</v>
+        <v>620.5748542793827</v>
       </c>
       <c r="N46">
-        <v>2393.515698037937</v>
+        <v>2379.725145720618</v>
       </c>
       <c r="O46">
-        <v>526.5734535683462</v>
+        <v>523.5395320585359</v>
       </c>
       <c r="P46">
-        <v>1866.942244469591</v>
+        <v>1856.185613662082</v>
       </c>
       <c r="Q46">
-        <v>2893.24224446959</v>
+        <v>2882.485613662082</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1265145483142363</v>
+        <v>0.1277819077571283</v>
       </c>
       <c r="T46">
-        <v>1.174495025658108</v>
+        <v>1.192936649782702</v>
       </c>
       <c r="U46">
         <v>0.07315748822216714</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.944590672992695</v>
+        <v>4.834710880259523</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09595832763240125</v>
+        <v>0.09596085825098238</v>
       </c>
       <c r="C47">
-        <v>10505.30015218297</v>
+        <v>10316.14899842065</v>
       </c>
       <c r="D47">
-        <v>15614.62515218297</v>
+        <v>15613.97899842065</v>
       </c>
       <c r="E47">
-        <v>1931.125</v>
+        <v>2119.629999999999</v>
       </c>
       <c r="F47">
-        <v>8482.725</v>
+        <v>8671.23</v>
       </c>
       <c r="G47">
         <v>3373.4</v>
@@ -5147,28 +5147,28 @@
         <v>3000.3</v>
       </c>
       <c r="M47">
-        <v>620.5748542793827</v>
+        <v>634.3654065967023</v>
       </c>
       <c r="N47">
-        <v>2379.725145720618</v>
+        <v>2365.934593403298</v>
       </c>
       <c r="O47">
-        <v>523.5395320585359</v>
+        <v>520.5056105487256</v>
       </c>
       <c r="P47">
-        <v>1856.185613662082</v>
+        <v>1845.428982854572</v>
       </c>
       <c r="Q47">
-        <v>2882.485613662082</v>
+        <v>2871.728982854572</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1277819077571283</v>
+        <v>0.1290962064386459</v>
       </c>
       <c r="T47">
-        <v>1.192936649782702</v>
+        <v>1.212061297023021</v>
       </c>
       <c r="U47">
         <v>0.07315748822216714</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.834710880259523</v>
+        <v>4.7296084698191</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09596085825098238</v>
+        <v>0.09596338886956354</v>
       </c>
       <c r="C48">
-        <v>10316.14899842065</v>
+        <v>10126.99789813349</v>
       </c>
       <c r="D48">
-        <v>15613.97899842065</v>
+        <v>15613.33289813349</v>
       </c>
       <c r="E48">
-        <v>2119.629999999999</v>
+        <v>2308.135</v>
       </c>
       <c r="F48">
-        <v>8671.23</v>
+        <v>8859.735000000001</v>
       </c>
       <c r="G48">
         <v>3373.4</v>
@@ -5229,28 +5229,28 @@
         <v>3000.3</v>
       </c>
       <c r="M48">
-        <v>634.3654065967023</v>
+        <v>648.155958914022</v>
       </c>
       <c r="N48">
-        <v>2365.934593403298</v>
+        <v>2352.144041085978</v>
       </c>
       <c r="O48">
-        <v>520.5056105487256</v>
+        <v>517.4716890389152</v>
       </c>
       <c r="P48">
-        <v>1845.428982854572</v>
+        <v>1834.672352047063</v>
       </c>
       <c r="Q48">
-        <v>2871.728982854572</v>
+        <v>2860.972352047062</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1290962064386459</v>
+        <v>0.1304601012968246</v>
       </c>
       <c r="T48">
-        <v>1.212061297023021</v>
+        <v>1.231907629064863</v>
       </c>
       <c r="U48">
         <v>0.07315748822216714</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.7296084698191</v>
+        <v>4.628978502376139</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09596338886956354</v>
+        <v>0.0959659194881447</v>
       </c>
       <c r="C49">
-        <v>10126.99789813349</v>
+        <v>9937.846851314873</v>
       </c>
       <c r="D49">
-        <v>15613.33289813349</v>
+        <v>15612.68685131487</v>
       </c>
       <c r="E49">
-        <v>2308.135</v>
+        <v>2496.640000000001</v>
       </c>
       <c r="F49">
-        <v>8859.735000000001</v>
+        <v>9048.240000000002</v>
       </c>
       <c r="G49">
         <v>3373.4</v>
@@ -5311,28 +5311,28 @@
         <v>3000.3</v>
       </c>
       <c r="M49">
-        <v>648.155958914022</v>
+        <v>661.9465112313417</v>
       </c>
       <c r="N49">
-        <v>2352.144041085978</v>
+        <v>2338.353488768658</v>
       </c>
       <c r="O49">
-        <v>517.4716890389152</v>
+        <v>514.4377675291048</v>
       </c>
       <c r="P49">
-        <v>1834.672352047063</v>
+        <v>1823.915721239553</v>
       </c>
       <c r="Q49">
-        <v>2860.972352047062</v>
+        <v>2850.215721239553</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1304601012968246</v>
+        <v>0.1318764536495487</v>
       </c>
       <c r="T49">
-        <v>1.231907629064863</v>
+        <v>1.252517281569852</v>
       </c>
       <c r="U49">
         <v>0.07315748822216714</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.628978502376139</v>
+        <v>4.532541450243302</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0959659194881447</v>
+        <v>0.09596845010672586</v>
       </c>
       <c r="C50">
-        <v>9937.846851314875</v>
+        <v>9748.695857958159</v>
       </c>
       <c r="D50">
-        <v>15612.68685131487</v>
+        <v>15612.04085795816</v>
       </c>
       <c r="E50">
-        <v>2496.639999999999</v>
+        <v>2685.144999999999</v>
       </c>
       <c r="F50">
-        <v>9048.24</v>
+        <v>9236.744999999999</v>
       </c>
       <c r="G50">
         <v>3373.4</v>
@@ -5393,28 +5393,28 @@
         <v>3000.3</v>
       </c>
       <c r="M50">
-        <v>661.9465112313416</v>
+        <v>675.7370635486611</v>
       </c>
       <c r="N50">
-        <v>2338.353488768659</v>
+        <v>2324.562936451339</v>
       </c>
       <c r="O50">
-        <v>514.4377675291049</v>
+        <v>511.4038460192945</v>
       </c>
       <c r="P50">
-        <v>1823.915721239554</v>
+        <v>1813.159090432044</v>
       </c>
       <c r="Q50">
-        <v>2850.215721239554</v>
+        <v>2839.459090432044</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1318764536495487</v>
+        <v>0.1333483492317913</v>
       </c>
       <c r="T50">
-        <v>1.252517281569851</v>
+        <v>1.273935155741702</v>
       </c>
       <c r="U50">
         <v>0.07315748822216714</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.532541450243304</v>
+        <v>4.440040604319972</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09596845010672586</v>
+        <v>0.09597098072530699</v>
       </c>
       <c r="C51">
-        <v>9748.695857958159</v>
+        <v>9559.544918056708</v>
       </c>
       <c r="D51">
-        <v>15612.04085795816</v>
+        <v>15611.39491805671</v>
       </c>
       <c r="E51">
-        <v>2685.144999999999</v>
+        <v>2873.65</v>
       </c>
       <c r="F51">
-        <v>9236.744999999999</v>
+        <v>9425.25</v>
       </c>
       <c r="G51">
         <v>3373.4</v>
@@ -5475,28 +5475,28 @@
         <v>3000.3</v>
       </c>
       <c r="M51">
-        <v>675.7370635486611</v>
+        <v>689.5276158659808</v>
       </c>
       <c r="N51">
-        <v>2324.562936451339</v>
+        <v>2310.772384134019</v>
       </c>
       <c r="O51">
-        <v>511.4038460192945</v>
+        <v>508.3699245094843</v>
       </c>
       <c r="P51">
-        <v>1813.159090432044</v>
+        <v>1802.402459624535</v>
       </c>
       <c r="Q51">
-        <v>2839.459090432044</v>
+        <v>2828.702459624535</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1333483492317913</v>
+        <v>0.1348791206373236</v>
       </c>
       <c r="T51">
-        <v>1.273935155741702</v>
+        <v>1.296209744880428</v>
       </c>
       <c r="U51">
         <v>0.07315748822216714</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.440040604319972</v>
+        <v>4.351239792233571</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09597098072530699</v>
+        <v>0.09597351134388817</v>
       </c>
       <c r="C52">
-        <v>9559.544918056708</v>
+        <v>9370.394031603882</v>
       </c>
       <c r="D52">
-        <v>15611.39491805671</v>
+        <v>15610.74903160388</v>
       </c>
       <c r="E52">
-        <v>2873.65</v>
+        <v>3062.155000000001</v>
       </c>
       <c r="F52">
-        <v>9425.25</v>
+        <v>9613.755000000001</v>
       </c>
       <c r="G52">
         <v>3373.4</v>
@@ -5557,28 +5557,28 @@
         <v>3000.3</v>
       </c>
       <c r="M52">
-        <v>689.5276158659808</v>
+        <v>703.3181681833005</v>
       </c>
       <c r="N52">
-        <v>2310.772384134019</v>
+        <v>2296.9818318167</v>
       </c>
       <c r="O52">
-        <v>508.3699245094843</v>
+        <v>505.336002999674</v>
       </c>
       <c r="P52">
-        <v>1802.402459624535</v>
+        <v>1791.645828817026</v>
       </c>
       <c r="Q52">
-        <v>2828.702459624535</v>
+        <v>2817.945828817025</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1348791206373236</v>
+        <v>0.1364723725083879</v>
       </c>
       <c r="T52">
-        <v>1.296209744880428</v>
+        <v>1.319393500922774</v>
       </c>
       <c r="U52">
         <v>0.07315748822216714</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.351239792233571</v>
+        <v>4.265921364934874</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09597351134388817</v>
+        <v>0.09638164196246933</v>
       </c>
       <c r="C53">
-        <v>9370.394031603882</v>
+        <v>9078.417113933237</v>
       </c>
       <c r="D53">
-        <v>15610.74903160388</v>
+        <v>15507.27711393324</v>
       </c>
       <c r="E53">
-        <v>3062.155000000001</v>
+        <v>3250.66</v>
       </c>
       <c r="F53">
-        <v>9613.755000000001</v>
+        <v>9802.26</v>
       </c>
       <c r="G53">
         <v>3373.4</v>
@@ -5639,45 +5639,45 @@
         <v>3000.3</v>
       </c>
       <c r="M53">
-        <v>703.3181681833005</v>
+        <v>726.9109805006201</v>
       </c>
       <c r="N53">
-        <v>2296.9818318167</v>
+        <v>2273.38901949938</v>
       </c>
       <c r="O53">
-        <v>505.336002999674</v>
+        <v>500.1455842898636</v>
       </c>
       <c r="P53">
-        <v>1791.645828817026</v>
+        <v>1773.243435209517</v>
       </c>
       <c r="Q53">
-        <v>2817.945828817025</v>
+        <v>2799.543435209516</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1364723725083879</v>
+        <v>0.1381320098740799</v>
       </c>
       <c r="T53">
-        <v>1.319393500922774</v>
+        <v>1.343543246800219</v>
       </c>
       <c r="U53">
-        <v>0.07315748822216714</v>
+        <v>0.07415748822216714</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.05706284081329037</v>
+        <v>0.05784284081329037</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.265921364934874</v>
+        <v>4.1274655088216</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09638164196246933</v>
+        <v>0.09639197258105048</v>
       </c>
       <c r="C54">
-        <v>9078.417113933237</v>
+        <v>8887.310824981812</v>
       </c>
       <c r="D54">
-        <v>15507.27711393324</v>
+        <v>15504.67582498181</v>
       </c>
       <c r="E54">
-        <v>3250.66</v>
+        <v>3439.165000000001</v>
       </c>
       <c r="F54">
-        <v>9802.26</v>
+        <v>9990.765000000001</v>
       </c>
       <c r="G54">
         <v>3373.4</v>
@@ -5721,28 +5721,28 @@
         <v>3000.3</v>
       </c>
       <c r="M54">
-        <v>726.9109805006201</v>
+        <v>740.8900378179397</v>
       </c>
       <c r="N54">
-        <v>2273.38901949938</v>
+        <v>2259.409962182061</v>
       </c>
       <c r="O54">
-        <v>500.1455842898636</v>
+        <v>497.0701916800533</v>
       </c>
       <c r="P54">
-        <v>1773.243435209517</v>
+        <v>1762.339770502007</v>
       </c>
       <c r="Q54">
-        <v>2799.543435209516</v>
+        <v>2788.639770502007</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1381320098740799</v>
+        <v>0.139862270106397</v>
       </c>
       <c r="T54">
-        <v>1.343543246800219</v>
+        <v>1.368720641438405</v>
       </c>
       <c r="U54">
         <v>0.07415748822216714</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.1274655088216</v>
+        <v>4.049588801107985</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09639197258105048</v>
+        <v>0.09640230319963163</v>
       </c>
       <c r="C55">
-        <v>8887.310824981812</v>
+        <v>8696.205408597416</v>
       </c>
       <c r="D55">
-        <v>15504.67582498181</v>
+        <v>15502.07540859741</v>
       </c>
       <c r="E55">
-        <v>3439.165000000001</v>
+        <v>3627.67</v>
       </c>
       <c r="F55">
-        <v>9990.765000000001</v>
+        <v>10179.27</v>
       </c>
       <c r="G55">
         <v>3373.4</v>
@@ -5803,28 +5803,28 @@
         <v>3000.3</v>
       </c>
       <c r="M55">
-        <v>740.8900378179397</v>
+        <v>754.8690951352594</v>
       </c>
       <c r="N55">
-        <v>2259.409962182061</v>
+        <v>2245.430904864741</v>
       </c>
       <c r="O55">
-        <v>497.0701916800533</v>
+        <v>493.994799070243</v>
       </c>
       <c r="P55">
-        <v>1762.339770502007</v>
+        <v>1751.436105794498</v>
       </c>
       <c r="Q55">
-        <v>2788.639770502007</v>
+        <v>2777.736105794498</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.139862270106397</v>
+        <v>0.141667759044467</v>
       </c>
       <c r="T55">
-        <v>1.368720641438405</v>
+        <v>1.394992705408687</v>
       </c>
       <c r="U55">
         <v>0.07415748822216714</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.049588801107985</v>
+        <v>3.974596415902282</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09640230319963163</v>
+        <v>0.09641263381821279</v>
       </c>
       <c r="C56">
-        <v>8696.205408597416</v>
+        <v>8505.100864341075</v>
       </c>
       <c r="D56">
-        <v>15502.07540859741</v>
+        <v>15499.47586434108</v>
       </c>
       <c r="E56">
-        <v>3627.67</v>
+        <v>3816.175000000001</v>
       </c>
       <c r="F56">
-        <v>10179.27</v>
+        <v>10367.775</v>
       </c>
       <c r="G56">
         <v>3373.4</v>
@@ -5885,28 +5885,28 @@
         <v>3000.3</v>
       </c>
       <c r="M56">
-        <v>754.8690951352594</v>
+        <v>768.848152452579</v>
       </c>
       <c r="N56">
-        <v>2245.430904864741</v>
+        <v>2231.451847547421</v>
       </c>
       <c r="O56">
-        <v>493.994799070243</v>
+        <v>490.9194064604326</v>
       </c>
       <c r="P56">
-        <v>1751.436105794498</v>
+        <v>1740.532441086988</v>
       </c>
       <c r="Q56">
-        <v>2777.736105794498</v>
+        <v>2766.832441086988</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.141667759044467</v>
+        <v>0.1435534919353402</v>
       </c>
       <c r="T56">
-        <v>1.394992705408687</v>
+        <v>1.422432416666537</v>
       </c>
       <c r="U56">
         <v>0.07415748822216714</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.974596415902282</v>
+        <v>3.90233102652224</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09641263381821279</v>
+        <v>0.09642296443679393</v>
       </c>
       <c r="C57">
-        <v>8505.100864341075</v>
+        <v>8313.99719177413</v>
       </c>
       <c r="D57">
-        <v>15499.47586434108</v>
+        <v>15496.87719177413</v>
       </c>
       <c r="E57">
-        <v>3816.175000000001</v>
+        <v>4004.68</v>
       </c>
       <c r="F57">
-        <v>10367.775</v>
+        <v>10556.28</v>
       </c>
       <c r="G57">
         <v>3373.4</v>
@@ -5967,28 +5967,28 @@
         <v>3000.3</v>
       </c>
       <c r="M57">
-        <v>768.848152452579</v>
+        <v>782.8272097698986</v>
       </c>
       <c r="N57">
-        <v>2231.451847547421</v>
+        <v>2217.472790230102</v>
       </c>
       <c r="O57">
-        <v>490.9194064604326</v>
+        <v>487.8440138506223</v>
       </c>
       <c r="P57">
-        <v>1740.532441086988</v>
+        <v>1729.628776379479</v>
       </c>
       <c r="Q57">
-        <v>2766.832441086988</v>
+        <v>2755.928776379479</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1435534919353402</v>
+        <v>0.1455249399576167</v>
       </c>
       <c r="T57">
-        <v>1.422432416666537</v>
+        <v>1.451119387527016</v>
       </c>
       <c r="U57">
         <v>0.07415748822216714</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.90233102652224</v>
+        <v>3.832646543905772</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09642296443679393</v>
+        <v>0.0964332950553751</v>
       </c>
       <c r="C58">
-        <v>8313.99719177413</v>
+        <v>8122.894390458192</v>
       </c>
       <c r="D58">
-        <v>15496.87719177413</v>
+        <v>15494.27939045819</v>
       </c>
       <c r="E58">
-        <v>4004.68</v>
+        <v>4193.185000000001</v>
       </c>
       <c r="F58">
-        <v>10556.28</v>
+        <v>10744.785</v>
       </c>
       <c r="G58">
         <v>3373.4</v>
@@ -6049,28 +6049,28 @@
         <v>3000.3</v>
       </c>
       <c r="M58">
-        <v>782.8272097698986</v>
+        <v>796.8062670872183</v>
       </c>
       <c r="N58">
-        <v>2217.472790230102</v>
+        <v>2203.493732912782</v>
       </c>
       <c r="O58">
-        <v>487.8440138506223</v>
+        <v>484.768621240812</v>
       </c>
       <c r="P58">
-        <v>1729.628776379479</v>
+        <v>1718.72511167197</v>
       </c>
       <c r="Q58">
-        <v>2755.928776379479</v>
+        <v>2745.02511167197</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1455249399576167</v>
+        <v>0.1475880832367432</v>
       </c>
       <c r="T58">
-        <v>1.451119387527016</v>
+        <v>1.481140636101936</v>
       </c>
       <c r="U58">
         <v>0.07415748822216714</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.832646543905772</v>
+        <v>3.765407130854793</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0964332950553751</v>
+        <v>0.09644362567395624</v>
       </c>
       <c r="C59">
-        <v>8122.894390458192</v>
+        <v>7931.792459955206</v>
       </c>
       <c r="D59">
-        <v>15494.27939045819</v>
+        <v>15491.68245995521</v>
       </c>
       <c r="E59">
-        <v>4193.185000000001</v>
+        <v>4381.690000000001</v>
       </c>
       <c r="F59">
-        <v>10744.785</v>
+        <v>10933.29</v>
       </c>
       <c r="G59">
         <v>3373.4</v>
@@ -6131,28 +6131,28 @@
         <v>3000.3</v>
       </c>
       <c r="M59">
-        <v>796.8062670872183</v>
+        <v>810.7853244045378</v>
       </c>
       <c r="N59">
-        <v>2203.493732912782</v>
+        <v>2189.514675595462</v>
       </c>
       <c r="O59">
-        <v>484.768621240812</v>
+        <v>481.6932286310017</v>
       </c>
       <c r="P59">
-        <v>1718.72511167197</v>
+        <v>1707.821446964461</v>
       </c>
       <c r="Q59">
-        <v>2745.02511167197</v>
+        <v>2734.121446964461</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1475880832367432</v>
+        <v>0.1497494714339234</v>
       </c>
       <c r="T59">
-        <v>1.481140636101936</v>
+        <v>1.512591467942329</v>
       </c>
       <c r="U59">
         <v>0.07415748822216714</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.765407130854793</v>
+        <v>3.700486318253848</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09644362567395626</v>
+        <v>0.09645395629253742</v>
       </c>
       <c r="C60">
-        <v>7931.792459955204</v>
+        <v>7740.691399827361</v>
       </c>
       <c r="D60">
-        <v>15491.6824599552</v>
+        <v>15489.08639982736</v>
       </c>
       <c r="E60">
-        <v>4381.689999999999</v>
+        <v>4570.195</v>
       </c>
       <c r="F60">
-        <v>10933.29</v>
+        <v>11121.795</v>
       </c>
       <c r="G60">
         <v>3373.4</v>
@@ -6213,28 +6213,28 @@
         <v>3000.3</v>
       </c>
       <c r="M60">
-        <v>810.7853244045377</v>
+        <v>824.7643817218574</v>
       </c>
       <c r="N60">
-        <v>2189.514675595462</v>
+        <v>2175.535618278143</v>
       </c>
       <c r="O60">
-        <v>481.6932286310017</v>
+        <v>478.6178360211915</v>
       </c>
       <c r="P60">
-        <v>1707.821446964461</v>
+        <v>1696.917782256951</v>
       </c>
       <c r="Q60">
-        <v>2734.121446964461</v>
+        <v>2723.217782256951</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1497494714339234</v>
+        <v>0.1520162932016978</v>
       </c>
       <c r="T60">
-        <v>1.512591467942329</v>
+        <v>1.545576486701765</v>
       </c>
       <c r="U60">
         <v>0.07415748822216714</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.700486318253849</v>
+        <v>3.6377662111648</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09645395629253742</v>
+        <v>0.09646428691111855</v>
       </c>
       <c r="C61">
-        <v>7740.691399827361</v>
+        <v>7549.591209637183</v>
       </c>
       <c r="D61">
-        <v>15489.08639982736</v>
+        <v>15486.49120963718</v>
       </c>
       <c r="E61">
-        <v>4570.195</v>
+        <v>4758.699999999999</v>
       </c>
       <c r="F61">
-        <v>11121.795</v>
+        <v>11310.3</v>
       </c>
       <c r="G61">
         <v>3373.4</v>
@@ -6295,28 +6295,28 @@
         <v>3000.3</v>
       </c>
       <c r="M61">
-        <v>824.7643817218574</v>
+        <v>838.7434390391769</v>
       </c>
       <c r="N61">
-        <v>2175.535618278143</v>
+        <v>2161.556560960823</v>
       </c>
       <c r="O61">
-        <v>478.6178360211915</v>
+        <v>475.5424434113812</v>
       </c>
       <c r="P61">
-        <v>1696.917782256951</v>
+        <v>1686.014117549442</v>
       </c>
       <c r="Q61">
-        <v>2723.217782256951</v>
+        <v>2712.314117549442</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1520162932016978</v>
+        <v>0.1543964560578608</v>
       </c>
       <c r="T61">
-        <v>1.545576486701765</v>
+        <v>1.580210756399173</v>
       </c>
       <c r="U61">
         <v>0.07415748822216714</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.6377662111648</v>
+        <v>3.577136774312054</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09646428691111855</v>
+        <v>0.09647461752969971</v>
       </c>
       <c r="C62">
-        <v>7549.591209637183</v>
+        <v>7358.491888947457</v>
       </c>
       <c r="D62">
-        <v>15486.49120963718</v>
+        <v>15483.89688894746</v>
       </c>
       <c r="E62">
-        <v>4758.699999999999</v>
+        <v>4947.205</v>
       </c>
       <c r="F62">
-        <v>11310.3</v>
+        <v>11498.805</v>
       </c>
       <c r="G62">
         <v>3373.4</v>
@@ -6377,28 +6377,28 @@
         <v>3000.3</v>
       </c>
       <c r="M62">
-        <v>838.7434390391769</v>
+        <v>852.7224963564967</v>
       </c>
       <c r="N62">
-        <v>2161.556560960823</v>
+        <v>2147.577503643503</v>
       </c>
       <c r="O62">
-        <v>475.5424434113812</v>
+        <v>472.4670508015707</v>
       </c>
       <c r="P62">
-        <v>1686.014117549442</v>
+        <v>1675.110452841933</v>
       </c>
       <c r="Q62">
-        <v>2712.314117549442</v>
+        <v>2701.410452841933</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1543964560578608</v>
+        <v>0.1568986785476733</v>
       </c>
       <c r="T62">
-        <v>1.580210756399173</v>
+        <v>1.616621142491319</v>
       </c>
       <c r="U62">
         <v>0.07415748822216714</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.577136774312054</v>
+        <v>3.518495187847921</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09647461752969971</v>
+        <v>0.09648494814828087</v>
       </c>
       <c r="C63">
-        <v>7358.491888947457</v>
+        <v>7167.393437321281</v>
       </c>
       <c r="D63">
-        <v>15483.89688894746</v>
+        <v>15481.30343732128</v>
       </c>
       <c r="E63">
-        <v>4947.205</v>
+        <v>5135.709999999999</v>
       </c>
       <c r="F63">
-        <v>11498.805</v>
+        <v>11687.31</v>
       </c>
       <c r="G63">
         <v>3373.4</v>
@@ -6459,28 +6459,28 @@
         <v>3000.3</v>
       </c>
       <c r="M63">
-        <v>852.7224963564967</v>
+        <v>866.7015536738162</v>
       </c>
       <c r="N63">
-        <v>2147.577503643503</v>
+        <v>2133.598446326184</v>
       </c>
       <c r="O63">
-        <v>472.4670508015707</v>
+        <v>469.3916581917604</v>
       </c>
       <c r="P63">
-        <v>1675.110452841933</v>
+        <v>1664.206788134424</v>
       </c>
       <c r="Q63">
-        <v>2701.410452841933</v>
+        <v>2690.506788134423</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1568986785476733</v>
+        <v>0.1595325969580022</v>
       </c>
       <c r="T63">
-        <v>1.616621142491319</v>
+        <v>1.65494786469358</v>
       </c>
       <c r="U63">
         <v>0.07415748822216714</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.518495187847921</v>
+        <v>3.461745265463278</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09648494814828087</v>
+        <v>0.09649527876686202</v>
       </c>
       <c r="C64">
-        <v>7167.393437321281</v>
+        <v>6976.295854322047</v>
       </c>
       <c r="D64">
-        <v>15481.30343732128</v>
+        <v>15478.71085432205</v>
       </c>
       <c r="E64">
-        <v>5135.709999999999</v>
+        <v>5324.215</v>
       </c>
       <c r="F64">
-        <v>11687.31</v>
+        <v>11875.815</v>
       </c>
       <c r="G64">
         <v>3373.4</v>
@@ -6541,28 +6541,28 @@
         <v>3000.3</v>
       </c>
       <c r="M64">
-        <v>866.7015536738162</v>
+        <v>880.6806109911358</v>
       </c>
       <c r="N64">
-        <v>2133.598446326184</v>
+        <v>2119.619389008864</v>
       </c>
       <c r="O64">
-        <v>469.3916581917604</v>
+        <v>466.3162655819502</v>
       </c>
       <c r="P64">
-        <v>1664.206788134424</v>
+        <v>1653.303123426914</v>
       </c>
       <c r="Q64">
-        <v>2690.506788134423</v>
+        <v>2679.603123426914</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1595325969580022</v>
+        <v>0.162308889336457</v>
       </c>
       <c r="T64">
-        <v>1.65494786469358</v>
+        <v>1.695346301609475</v>
       </c>
       <c r="U64">
         <v>0.07415748822216714</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.461745265463278</v>
+        <v>3.406796927916242</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09649527876686202</v>
+        <v>0.09650560938544318</v>
       </c>
       <c r="C65">
-        <v>6976.295854322047</v>
+        <v>6785.199139513428</v>
       </c>
       <c r="D65">
-        <v>15478.71085432205</v>
+        <v>15476.11913951343</v>
       </c>
       <c r="E65">
-        <v>5324.215</v>
+        <v>5512.719999999999</v>
       </c>
       <c r="F65">
-        <v>11875.815</v>
+        <v>12064.32</v>
       </c>
       <c r="G65">
         <v>3373.4</v>
@@ -6623,28 +6623,28 @@
         <v>3000.3</v>
       </c>
       <c r="M65">
-        <v>880.6806109911358</v>
+        <v>894.6596683084555</v>
       </c>
       <c r="N65">
-        <v>2119.619389008864</v>
+        <v>2105.640331691545</v>
       </c>
       <c r="O65">
-        <v>466.3162655819502</v>
+        <v>463.2408729721399</v>
       </c>
       <c r="P65">
-        <v>1653.303123426914</v>
+        <v>1642.399458719405</v>
       </c>
       <c r="Q65">
-        <v>2679.603123426914</v>
+        <v>2668.699458719405</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.162308889336457</v>
+        <v>0.1652394201803815</v>
       </c>
       <c r="T65">
-        <v>1.695346301609475</v>
+        <v>1.737989096131809</v>
       </c>
       <c r="U65">
         <v>0.07415748822216714</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.406796927916242</v>
+        <v>3.35356572591755</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09650560938544318</v>
+        <v>0.09651594000402433</v>
       </c>
       <c r="C66">
-        <v>6785.199139513428</v>
+        <v>6594.103292459396</v>
       </c>
       <c r="D66">
-        <v>15476.11913951343</v>
+        <v>15473.5282924594</v>
       </c>
       <c r="E66">
-        <v>5512.719999999999</v>
+        <v>5701.225</v>
       </c>
       <c r="F66">
-        <v>12064.32</v>
+        <v>12252.825</v>
       </c>
       <c r="G66">
         <v>3373.4</v>
@@ -6705,28 +6705,28 @@
         <v>3000.3</v>
       </c>
       <c r="M66">
-        <v>894.6596683084555</v>
+        <v>908.6387256257751</v>
       </c>
       <c r="N66">
-        <v>2105.640331691545</v>
+        <v>2091.661274374225</v>
       </c>
       <c r="O66">
-        <v>463.2408729721399</v>
+        <v>460.1654803623296</v>
       </c>
       <c r="P66">
-        <v>1642.399458719405</v>
+        <v>1631.495794011896</v>
       </c>
       <c r="Q66">
-        <v>2668.699458719405</v>
+        <v>2657.795794011895</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1652394201803815</v>
+        <v>0.1683374099296731</v>
       </c>
       <c r="T66">
-        <v>1.737989096131809</v>
+        <v>1.783068621769705</v>
       </c>
       <c r="U66">
         <v>0.07415748822216714</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.35356572591755</v>
+        <v>3.30197240705728</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09651594000402433</v>
+        <v>0.09652627062260549</v>
       </c>
       <c r="C67">
-        <v>6594.103292459396</v>
+        <v>6403.008312724209</v>
       </c>
       <c r="D67">
-        <v>15473.5282924594</v>
+        <v>15470.93831272421</v>
       </c>
       <c r="E67">
-        <v>5701.225</v>
+        <v>5889.73</v>
       </c>
       <c r="F67">
-        <v>12252.825</v>
+        <v>12441.33</v>
       </c>
       <c r="G67">
         <v>3373.4</v>
@@ -6787,28 +6787,28 @@
         <v>3000.3</v>
       </c>
       <c r="M67">
-        <v>908.6387256257751</v>
+        <v>922.6177829430947</v>
       </c>
       <c r="N67">
-        <v>2091.661274374225</v>
+        <v>2077.682217056906</v>
       </c>
       <c r="O67">
-        <v>460.1654803623296</v>
+        <v>457.0900877525193</v>
       </c>
       <c r="P67">
-        <v>1631.495794011896</v>
+        <v>1620.592129304387</v>
       </c>
       <c r="Q67">
-        <v>2657.795794011895</v>
+        <v>2646.892129304386</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1683374099296731</v>
+        <v>0.1716176343700996</v>
       </c>
       <c r="T67">
-        <v>1.783068621769705</v>
+        <v>1.830799884209831</v>
       </c>
       <c r="U67">
         <v>0.07415748822216714</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.30197240705728</v>
+        <v>3.251942522101867</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09652627062260549</v>
+        <v>0.09653660124118665</v>
       </c>
       <c r="C68">
-        <v>6403.008312724209</v>
+        <v>6211.914199872424</v>
       </c>
       <c r="D68">
-        <v>15470.93831272421</v>
+        <v>15468.34919987242</v>
       </c>
       <c r="E68">
-        <v>5889.73</v>
+        <v>6078.235000000001</v>
       </c>
       <c r="F68">
-        <v>12441.33</v>
+        <v>12629.835</v>
       </c>
       <c r="G68">
         <v>3373.4</v>
@@ -6869,28 +6869,28 @@
         <v>3000.3</v>
       </c>
       <c r="M68">
-        <v>922.6177829430947</v>
+        <v>936.5968402604144</v>
       </c>
       <c r="N68">
-        <v>2077.682217056906</v>
+        <v>2063.703159739586</v>
       </c>
       <c r="O68">
-        <v>457.0900877525193</v>
+        <v>454.0146951427089</v>
       </c>
       <c r="P68">
-        <v>1620.592129304387</v>
+        <v>1609.688464596877</v>
       </c>
       <c r="Q68">
-        <v>2646.892129304386</v>
+        <v>2635.988464596877</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1716176343700996</v>
+        <v>0.175096660291764</v>
       </c>
       <c r="T68">
-        <v>1.830799884209831</v>
+        <v>1.881423950434206</v>
       </c>
       <c r="U68">
         <v>0.07415748822216714</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.251942522101867</v>
+        <v>3.203406066548107</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09653660124118665</v>
+        <v>0.09654693185976781</v>
       </c>
       <c r="C69">
-        <v>6211.914199872424</v>
+        <v>6020.820953468887</v>
       </c>
       <c r="D69">
-        <v>15468.34919987242</v>
+        <v>15465.76095346889</v>
       </c>
       <c r="E69">
-        <v>6078.235000000001</v>
+        <v>6266.74</v>
       </c>
       <c r="F69">
-        <v>12629.835</v>
+        <v>12818.34</v>
       </c>
       <c r="G69">
         <v>3373.4</v>
@@ -6951,28 +6951,28 @@
         <v>3000.3</v>
       </c>
       <c r="M69">
-        <v>936.5968402604144</v>
+        <v>950.5758975777339</v>
       </c>
       <c r="N69">
-        <v>2063.703159739586</v>
+        <v>2049.724102422266</v>
       </c>
       <c r="O69">
-        <v>454.0146951427089</v>
+        <v>450.9393025328986</v>
       </c>
       <c r="P69">
-        <v>1609.688464596877</v>
+        <v>1598.784799889368</v>
       </c>
       <c r="Q69">
-        <v>2635.988464596877</v>
+        <v>2625.084799889367</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.175096660291764</v>
+        <v>0.1787931253335324</v>
       </c>
       <c r="T69">
-        <v>1.881423950434206</v>
+        <v>1.935212020797605</v>
       </c>
       <c r="U69">
         <v>0.07415748822216714</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.203406066548107</v>
+        <v>3.156297153804753</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09654693185976781</v>
+        <v>0.09655726247834896</v>
       </c>
       <c r="C70">
-        <v>6020.820953468887</v>
+        <v>5829.728573078733</v>
       </c>
       <c r="D70">
-        <v>15465.76095346889</v>
+        <v>15463.17357307873</v>
       </c>
       <c r="E70">
-        <v>6266.74</v>
+        <v>6455.245000000001</v>
       </c>
       <c r="F70">
-        <v>12818.34</v>
+        <v>13006.845</v>
       </c>
       <c r="G70">
         <v>3373.4</v>
@@ -7033,28 +7033,28 @@
         <v>3000.3</v>
       </c>
       <c r="M70">
-        <v>950.5758975777339</v>
+        <v>964.5549548950536</v>
       </c>
       <c r="N70">
-        <v>2049.724102422266</v>
+        <v>2035.745045104947</v>
       </c>
       <c r="O70">
-        <v>450.9393025328986</v>
+        <v>447.8639099230883</v>
       </c>
       <c r="P70">
-        <v>1598.784799889368</v>
+        <v>1587.881135181859</v>
       </c>
       <c r="Q70">
-        <v>2625.084799889367</v>
+        <v>2614.181135181858</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1787931253335324</v>
+        <v>0.1827280719908987</v>
       </c>
       <c r="T70">
-        <v>1.935212020797605</v>
+        <v>1.992470289248965</v>
       </c>
       <c r="U70">
         <v>0.07415748822216714</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.156297153804753</v>
+        <v>3.11055371679309</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09655726247834896</v>
+        <v>0.09656759309693011</v>
       </c>
       <c r="C71">
-        <v>5829.728573078733</v>
+        <v>5638.637058267397</v>
       </c>
       <c r="D71">
-        <v>15463.17357307873</v>
+        <v>15460.5870582674</v>
       </c>
       <c r="E71">
-        <v>6455.245000000001</v>
+        <v>6643.75</v>
       </c>
       <c r="F71">
-        <v>13006.845</v>
+        <v>13195.35</v>
       </c>
       <c r="G71">
         <v>3373.4</v>
@@ -7115,28 +7115,28 @@
         <v>3000.3</v>
       </c>
       <c r="M71">
-        <v>964.5549548950536</v>
+        <v>978.5340122123732</v>
       </c>
       <c r="N71">
-        <v>2035.745045104947</v>
+        <v>2021.765987787627</v>
       </c>
       <c r="O71">
-        <v>447.8639099230883</v>
+        <v>444.7885173132779</v>
       </c>
       <c r="P71">
-        <v>1587.881135181859</v>
+        <v>1576.977470474349</v>
       </c>
       <c r="Q71">
-        <v>2614.181135181858</v>
+        <v>2603.277470474349</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1827280719908987</v>
+        <v>0.1869253484254229</v>
       </c>
       <c r="T71">
-        <v>1.992470289248965</v>
+        <v>2.053545775597082</v>
       </c>
       <c r="U71">
         <v>0.07415748822216714</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.11055371679309</v>
+        <v>3.066117235124617</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09656759309693011</v>
+        <v>0.09657792371551129</v>
       </c>
       <c r="C72">
-        <v>5638.637058267397</v>
+        <v>5447.54640860058</v>
       </c>
       <c r="D72">
-        <v>15460.5870582674</v>
+        <v>15458.00140860058</v>
       </c>
       <c r="E72">
-        <v>6643.75</v>
+        <v>6832.255000000001</v>
       </c>
       <c r="F72">
-        <v>13195.35</v>
+        <v>13383.855</v>
       </c>
       <c r="G72">
         <v>3373.4</v>
@@ -7197,28 +7197,28 @@
         <v>3000.3</v>
       </c>
       <c r="M72">
-        <v>978.5340122123732</v>
+        <v>992.5130695296929</v>
       </c>
       <c r="N72">
-        <v>2021.765987787627</v>
+        <v>2007.786930470307</v>
       </c>
       <c r="O72">
-        <v>444.7885173132779</v>
+        <v>441.7131247034676</v>
       </c>
       <c r="P72">
-        <v>1576.977470474349</v>
+        <v>1566.07380576684</v>
       </c>
       <c r="Q72">
-        <v>2603.277470474349</v>
+        <v>2592.373805766839</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1869253484254229</v>
+        <v>0.1914120922002591</v>
       </c>
       <c r="T72">
-        <v>2.053545775597082</v>
+        <v>2.118833364451967</v>
       </c>
       <c r="U72">
         <v>0.07415748822216714</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.066117235124617</v>
+        <v>3.022932485334129</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09657792371551127</v>
+        <v>0.09799225433409242</v>
       </c>
       <c r="C73">
-        <v>5447.546408600585</v>
+        <v>4913.030345754951</v>
       </c>
       <c r="D73">
-        <v>15458.00140860058</v>
+        <v>15111.99034575495</v>
       </c>
       <c r="E73">
-        <v>6832.254999999999</v>
+        <v>7020.759999999998</v>
       </c>
       <c r="F73">
-        <v>13383.855</v>
+        <v>13572.36</v>
       </c>
       <c r="G73">
         <v>3373.4</v>
@@ -7279,45 +7279,45 @@
         <v>3000.3</v>
       </c>
       <c r="M73">
-        <v>992.5130695296928</v>
+        <v>1040.423026847012</v>
       </c>
       <c r="N73">
-        <v>2007.786930470307</v>
+        <v>1959.876973152988</v>
       </c>
       <c r="O73">
-        <v>441.7131247034677</v>
+        <v>431.1729340936574</v>
       </c>
       <c r="P73">
-        <v>1566.07380576684</v>
+        <v>1528.704039059331</v>
       </c>
       <c r="Q73">
-        <v>2592.37380576684</v>
+        <v>2555.00403905933</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.191412092200259</v>
+        <v>0.1962193176732977</v>
       </c>
       <c r="T73">
-        <v>2.118833364451965</v>
+        <v>2.18878435251077</v>
       </c>
       <c r="U73">
-        <v>0.07415748822216714</v>
+        <v>0.07665748822216713</v>
       </c>
       <c r="V73">
         <v>0.22</v>
       </c>
       <c r="W73">
-        <v>0.05784284081329037</v>
+        <v>0.05979284081329036</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.02293248533413</v>
+        <v>2.883730869637102</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09799225433409242</v>
+        <v>0.09802208495267357</v>
       </c>
       <c r="C74">
-        <v>4913.030345754951</v>
+        <v>4717.39411258924</v>
       </c>
       <c r="D74">
-        <v>15111.99034575495</v>
+        <v>15104.85911258924</v>
       </c>
       <c r="E74">
-        <v>7020.759999999998</v>
+        <v>7209.264999999999</v>
       </c>
       <c r="F74">
-        <v>13572.36</v>
+        <v>13760.865</v>
       </c>
       <c r="G74">
         <v>3373.4</v>
@@ -7361,28 +7361,28 @@
         <v>3000.3</v>
       </c>
       <c r="M74">
-        <v>1040.423026847012</v>
+        <v>1054.873346664332</v>
       </c>
       <c r="N74">
-        <v>1959.876973152988</v>
+        <v>1945.426653335668</v>
       </c>
       <c r="O74">
-        <v>431.1729340936574</v>
+        <v>427.993863733847</v>
       </c>
       <c r="P74">
-        <v>1528.704039059331</v>
+        <v>1517.432789601821</v>
       </c>
       <c r="Q74">
-        <v>2555.00403905933</v>
+        <v>2543.732789601821</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1962193176732977</v>
+        <v>0.2013826339221171</v>
       </c>
       <c r="T74">
-        <v>2.18878435251077</v>
+        <v>2.263916895240597</v>
       </c>
       <c r="U74">
         <v>0.07665748822216713</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.883730869637102</v>
+        <v>2.844227707039333</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09802208495267357</v>
+        <v>0.09805191557125473</v>
       </c>
       <c r="C75">
-        <v>4717.39411258924</v>
+        <v>4521.764606598284</v>
       </c>
       <c r="D75">
-        <v>15104.85911258924</v>
+        <v>15097.73460659828</v>
       </c>
       <c r="E75">
-        <v>7209.264999999999</v>
+        <v>7397.769999999999</v>
       </c>
       <c r="F75">
-        <v>13760.865</v>
+        <v>13949.37</v>
       </c>
       <c r="G75">
         <v>3373.4</v>
@@ -7443,28 +7443,28 @@
         <v>3000.3</v>
       </c>
       <c r="M75">
-        <v>1054.873346664332</v>
+        <v>1069.323666481651</v>
       </c>
       <c r="N75">
-        <v>1945.426653335668</v>
+        <v>1930.976333518349</v>
       </c>
       <c r="O75">
-        <v>427.993863733847</v>
+        <v>424.8147933740368</v>
       </c>
       <c r="P75">
-        <v>1517.432789601821</v>
+        <v>1506.161540144312</v>
       </c>
       <c r="Q75">
-        <v>2543.732789601821</v>
+        <v>2532.461540144312</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2013826339221171</v>
+        <v>0.2069431283439225</v>
       </c>
       <c r="T75">
-        <v>2.263916895240597</v>
+        <v>2.344828864334256</v>
       </c>
       <c r="U75">
         <v>0.07665748822216713</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.844227707039333</v>
+        <v>2.805792197484748</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09805191557125473</v>
+        <v>0.09808174618983588</v>
       </c>
       <c r="C76">
-        <v>4521.764606598284</v>
+        <v>4326.141818267548</v>
       </c>
       <c r="D76">
-        <v>15097.73460659828</v>
+        <v>15090.61681826755</v>
       </c>
       <c r="E76">
-        <v>7397.769999999999</v>
+        <v>7586.275</v>
       </c>
       <c r="F76">
-        <v>13949.37</v>
+        <v>14137.875</v>
       </c>
       <c r="G76">
         <v>3373.4</v>
@@ -7525,28 +7525,28 @@
         <v>3000.3</v>
       </c>
       <c r="M76">
-        <v>1069.323666481651</v>
+        <v>1083.773986298971</v>
       </c>
       <c r="N76">
-        <v>1930.976333518349</v>
+        <v>1916.526013701029</v>
       </c>
       <c r="O76">
-        <v>424.8147933740368</v>
+        <v>421.6357230142264</v>
       </c>
       <c r="P76">
-        <v>1506.161540144312</v>
+        <v>1494.890290686803</v>
       </c>
       <c r="Q76">
-        <v>2532.461540144312</v>
+        <v>2521.190290686803</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2069431283439225</v>
+        <v>0.2129484623194725</v>
       </c>
       <c r="T76">
-        <v>2.344828864334256</v>
+        <v>2.432213790955409</v>
       </c>
       <c r="U76">
         <v>0.07665748822216713</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.805792197484748</v>
+        <v>2.768381634851618</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09808174618983588</v>
+        <v>0.09811157680841703</v>
       </c>
       <c r="C77">
-        <v>4326.141818267548</v>
+        <v>4130.525738100438</v>
       </c>
       <c r="D77">
-        <v>15090.61681826755</v>
+        <v>15083.50573810044</v>
       </c>
       <c r="E77">
-        <v>7586.275</v>
+        <v>7774.780000000001</v>
       </c>
       <c r="F77">
-        <v>14137.875</v>
+        <v>14326.38</v>
       </c>
       <c r="G77">
         <v>3373.4</v>
@@ -7607,28 +7607,28 @@
         <v>3000.3</v>
       </c>
       <c r="M77">
-        <v>1083.773986298971</v>
+        <v>1098.224306116291</v>
       </c>
       <c r="N77">
-        <v>1916.526013701029</v>
+        <v>1902.075693883709</v>
       </c>
       <c r="O77">
-        <v>421.6357230142264</v>
+        <v>418.4566526544161</v>
       </c>
       <c r="P77">
-        <v>1494.890290686803</v>
+        <v>1483.619041229293</v>
       </c>
       <c r="Q77">
-        <v>2521.190290686803</v>
+        <v>2509.919041229293</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2129484623194725</v>
+        <v>0.2194542407929849</v>
       </c>
       <c r="T77">
-        <v>2.432213790955409</v>
+        <v>2.526880794794991</v>
       </c>
       <c r="U77">
         <v>0.07665748822216713</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.768381634851618</v>
+        <v>2.731955560708833</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09811157680841703</v>
+        <v>0.0981414074269982</v>
       </c>
       <c r="C78">
-        <v>4130.525738100438</v>
+        <v>3934.916356618252</v>
       </c>
       <c r="D78">
-        <v>15083.50573810044</v>
+        <v>15076.40135661825</v>
       </c>
       <c r="E78">
-        <v>7774.780000000001</v>
+        <v>7963.285</v>
       </c>
       <c r="F78">
-        <v>14326.38</v>
+        <v>14514.885</v>
       </c>
       <c r="G78">
         <v>3373.4</v>
@@ -7689,28 +7689,28 @@
         <v>3000.3</v>
       </c>
       <c r="M78">
-        <v>1098.224306116291</v>
+        <v>1112.67462593361</v>
       </c>
       <c r="N78">
-        <v>1902.075693883709</v>
+        <v>1887.62537406639</v>
       </c>
       <c r="O78">
-        <v>418.4566526544161</v>
+        <v>415.2775822946058</v>
       </c>
       <c r="P78">
-        <v>1483.619041229293</v>
+        <v>1472.347791771784</v>
       </c>
       <c r="Q78">
-        <v>2509.919041229293</v>
+        <v>2498.647791771784</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2194542407929849</v>
+        <v>0.2265257391337592</v>
       </c>
       <c r="T78">
-        <v>2.526880794794991</v>
+        <v>2.629779712011928</v>
       </c>
       <c r="U78">
         <v>0.07665748822216713</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.731955560708833</v>
+        <v>2.696475618361966</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0981414074269982</v>
+        <v>0.09817123804557935</v>
       </c>
       <c r="C79">
-        <v>3934.916356618252</v>
+        <v>3739.313664360145</v>
       </c>
       <c r="D79">
-        <v>15076.40135661825</v>
+        <v>15069.30366436014</v>
       </c>
       <c r="E79">
-        <v>7963.285</v>
+        <v>8151.790000000001</v>
       </c>
       <c r="F79">
-        <v>14514.885</v>
+        <v>14703.39</v>
       </c>
       <c r="G79">
         <v>3373.4</v>
@@ -7771,28 +7771,28 @@
         <v>3000.3</v>
       </c>
       <c r="M79">
-        <v>1112.67462593361</v>
+        <v>1127.12494575093</v>
       </c>
       <c r="N79">
-        <v>1887.62537406639</v>
+        <v>1873.17505424907</v>
       </c>
       <c r="O79">
-        <v>415.2775822946058</v>
+        <v>412.0985119347955</v>
       </c>
       <c r="P79">
-        <v>1472.347791771784</v>
+        <v>1461.076542314275</v>
       </c>
       <c r="Q79">
-        <v>2498.647791771784</v>
+        <v>2487.376542314275</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2265257391337592</v>
+        <v>0.2342401009600585</v>
       </c>
       <c r="T79">
-        <v>2.629779712011928</v>
+        <v>2.742033076248586</v>
       </c>
       <c r="U79">
         <v>0.07665748822216713</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.696475618361966</v>
+        <v>2.661905418126555</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09817123804557935</v>
+        <v>0.09820106866416051</v>
       </c>
       <c r="C80">
-        <v>3739.313664360145</v>
+        <v>3543.717651883064</v>
       </c>
       <c r="D80">
-        <v>15069.30366436014</v>
+        <v>15062.21265188306</v>
       </c>
       <c r="E80">
-        <v>8151.790000000001</v>
+        <v>8340.295</v>
       </c>
       <c r="F80">
-        <v>14703.39</v>
+        <v>14891.895</v>
       </c>
       <c r="G80">
         <v>3373.4</v>
@@ -7853,28 +7853,28 @@
         <v>3000.3</v>
       </c>
       <c r="M80">
-        <v>1127.12494575093</v>
+        <v>1141.57526556825</v>
       </c>
       <c r="N80">
-        <v>1873.17505424907</v>
+        <v>1858.724734431751</v>
       </c>
       <c r="O80">
-        <v>412.0985119347955</v>
+        <v>408.9194415749852</v>
       </c>
       <c r="P80">
-        <v>1461.076542314275</v>
+        <v>1449.805292856765</v>
       </c>
       <c r="Q80">
-        <v>2487.376542314275</v>
+        <v>2476.105292856765</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2342401009600585</v>
+        <v>0.242689163912672</v>
       </c>
       <c r="T80">
-        <v>2.742033076248586</v>
+        <v>2.864977237079212</v>
       </c>
       <c r="U80">
         <v>0.07665748822216713</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.661905418126555</v>
+        <v>2.628210412833814</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09820106866416051</v>
+        <v>0.09823089928274167</v>
       </c>
       <c r="C81">
-        <v>3543.717651883064</v>
+        <v>3348.128309761727</v>
       </c>
       <c r="D81">
-        <v>15062.21265188306</v>
+        <v>15055.12830976173</v>
       </c>
       <c r="E81">
-        <v>8340.295</v>
+        <v>8528.800000000001</v>
       </c>
       <c r="F81">
-        <v>14891.895</v>
+        <v>15080.4</v>
       </c>
       <c r="G81">
         <v>3373.4</v>
@@ -7935,28 +7935,28 @@
         <v>3000.3</v>
       </c>
       <c r="M81">
-        <v>1141.57526556825</v>
+        <v>1156.025585385569</v>
       </c>
       <c r="N81">
-        <v>1858.724734431751</v>
+        <v>1844.274414614431</v>
       </c>
       <c r="O81">
-        <v>408.9194415749852</v>
+        <v>405.7403712151748</v>
       </c>
       <c r="P81">
-        <v>1449.805292856765</v>
+        <v>1438.534043399256</v>
       </c>
       <c r="Q81">
-        <v>2476.105292856765</v>
+        <v>2464.834043399256</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.242689163912672</v>
+        <v>0.2519831331605469</v>
       </c>
       <c r="T81">
-        <v>2.864977237079212</v>
+        <v>3.0002158139929</v>
       </c>
       <c r="U81">
         <v>0.07665748822216713</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.628210412833814</v>
+        <v>2.595357782673391</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09823089928274167</v>
+        <v>0.09826072990132281</v>
       </c>
       <c r="C82">
-        <v>3348.128309761727</v>
+        <v>3152.54562858859</v>
       </c>
       <c r="D82">
-        <v>15055.12830976173</v>
+        <v>15048.05062858859</v>
       </c>
       <c r="E82">
-        <v>8528.800000000001</v>
+        <v>8717.305</v>
       </c>
       <c r="F82">
-        <v>15080.4</v>
+        <v>15268.905</v>
       </c>
       <c r="G82">
         <v>3373.4</v>
@@ -8017,28 +8017,28 @@
         <v>3000.3</v>
       </c>
       <c r="M82">
-        <v>1156.025585385569</v>
+        <v>1170.475905202889</v>
       </c>
       <c r="N82">
-        <v>1844.274414614431</v>
+        <v>1829.824094797111</v>
       </c>
       <c r="O82">
-        <v>405.7403712151748</v>
+        <v>402.5613008553645</v>
       </c>
       <c r="P82">
-        <v>1438.534043399256</v>
+        <v>1427.262793941747</v>
       </c>
       <c r="Q82">
-        <v>2464.834043399256</v>
+        <v>2453.562793941746</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2519831331605469</v>
+        <v>0.2622554149608297</v>
       </c>
       <c r="T82">
-        <v>3.0002158139929</v>
+        <v>3.149690030581714</v>
       </c>
       <c r="U82">
         <v>0.07665748822216713</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.595357782673391</v>
+        <v>2.563316328566313</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09826072990132281</v>
+        <v>0.09829056051990395</v>
       </c>
       <c r="C83">
-        <v>3152.54562858859</v>
+        <v>2956.969598973772</v>
       </c>
       <c r="D83">
-        <v>15048.05062858859</v>
+        <v>15040.97959897377</v>
       </c>
       <c r="E83">
-        <v>8717.305</v>
+        <v>8905.810000000001</v>
       </c>
       <c r="F83">
-        <v>15268.905</v>
+        <v>15457.41</v>
       </c>
       <c r="G83">
         <v>3373.4</v>
@@ -8099,28 +8099,28 @@
         <v>3000.3</v>
       </c>
       <c r="M83">
-        <v>1170.475905202889</v>
+        <v>1184.926225020208</v>
       </c>
       <c r="N83">
-        <v>1829.824094797111</v>
+        <v>1815.373774979792</v>
       </c>
       <c r="O83">
-        <v>402.5613008553645</v>
+        <v>399.3822304955542</v>
       </c>
       <c r="P83">
-        <v>1427.262793941747</v>
+        <v>1415.991544484237</v>
       </c>
       <c r="Q83">
-        <v>2453.562793941746</v>
+        <v>2442.291544484237</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2622554149608297</v>
+        <v>0.2736690614055882</v>
       </c>
       <c r="T83">
-        <v>3.149690030581714</v>
+        <v>3.315772493458173</v>
       </c>
       <c r="U83">
         <v>0.07665748822216713</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.563316328566313</v>
+        <v>2.532056373339894</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09829056051990395</v>
+        <v>0.09832039113848512</v>
       </c>
       <c r="C84">
-        <v>2956.969598973772</v>
+        <v>2761.400211545042</v>
       </c>
       <c r="D84">
-        <v>15040.97959897377</v>
+        <v>15033.91521154504</v>
       </c>
       <c r="E84">
-        <v>8905.810000000001</v>
+        <v>9094.315000000001</v>
       </c>
       <c r="F84">
-        <v>15457.41</v>
+        <v>15645.915</v>
       </c>
       <c r="G84">
         <v>3373.4</v>
@@ -8181,28 +8181,28 @@
         <v>3000.3</v>
       </c>
       <c r="M84">
-        <v>1184.926225020208</v>
+        <v>1199.376544837528</v>
       </c>
       <c r="N84">
-        <v>1815.373774979792</v>
+        <v>1800.923455162472</v>
       </c>
       <c r="O84">
-        <v>399.3822304955542</v>
+        <v>396.2031601357439</v>
       </c>
       <c r="P84">
-        <v>1415.991544484237</v>
+        <v>1404.720295026728</v>
       </c>
       <c r="Q84">
-        <v>2442.291544484237</v>
+        <v>2431.020295026728</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2736690614055882</v>
+        <v>0.2864254897850244</v>
       </c>
       <c r="T84">
-        <v>3.315772493458173</v>
+        <v>3.501394069614217</v>
       </c>
       <c r="U84">
         <v>0.07665748822216713</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.532056373339894</v>
+        <v>2.501549670046642</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09832039113848512</v>
+        <v>0.1006434217570663</v>
       </c>
       <c r="C85">
-        <v>2761.400211545042</v>
+        <v>2042.423547280505</v>
       </c>
       <c r="D85">
-        <v>15033.91521154504</v>
+        <v>14503.44354728051</v>
       </c>
       <c r="E85">
-        <v>9094.315000000001</v>
+        <v>9282.820000000002</v>
       </c>
       <c r="F85">
-        <v>15645.915</v>
+        <v>15834.42</v>
       </c>
       <c r="G85">
         <v>3373.4</v>
@@ -8263,45 +8263,45 @@
         <v>3000.3</v>
       </c>
       <c r="M85">
-        <v>1199.376544837528</v>
+        <v>1269.247334654848</v>
       </c>
       <c r="N85">
-        <v>1800.923455162472</v>
+        <v>1731.052665345152</v>
       </c>
       <c r="O85">
-        <v>396.2031601357439</v>
+        <v>380.8315863759335</v>
       </c>
       <c r="P85">
-        <v>1404.720295026728</v>
+        <v>1350.221078969219</v>
       </c>
       <c r="Q85">
-        <v>2431.020295026728</v>
+        <v>2376.521078969218</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2864254897850244</v>
+        <v>0.30077647171189</v>
       </c>
       <c r="T85">
-        <v>3.501394069614217</v>
+        <v>3.710218342789765</v>
       </c>
       <c r="U85">
-        <v>0.07665748822216713</v>
+        <v>0.08015748822216713</v>
       </c>
       <c r="V85">
         <v>0.22</v>
       </c>
       <c r="W85">
-        <v>0.05979284081329036</v>
+        <v>0.06252284081329036</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>2.501549670046642</v>
+        <v>2.363841875481176</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1006434217570663</v>
+        <v>0.1007005523756474</v>
       </c>
       <c r="C86">
-        <v>2042.423547280507</v>
+        <v>1841.343821839622</v>
       </c>
       <c r="D86">
-        <v>14503.44354728051</v>
+        <v>14490.86882183962</v>
       </c>
       <c r="E86">
-        <v>9282.82</v>
+        <v>9471.324999999999</v>
       </c>
       <c r="F86">
-        <v>15834.42</v>
+        <v>16022.925</v>
       </c>
       <c r="G86">
         <v>3373.4</v>
@@ -8345,28 +8345,28 @@
         <v>3000.3</v>
       </c>
       <c r="M86">
-        <v>1269.247334654848</v>
+        <v>1284.357421972167</v>
       </c>
       <c r="N86">
-        <v>1731.052665345152</v>
+        <v>1715.942578027833</v>
       </c>
       <c r="O86">
-        <v>380.8315863759336</v>
+        <v>377.5073671661232</v>
       </c>
       <c r="P86">
-        <v>1350.221078969219</v>
+        <v>1338.43521086171</v>
       </c>
       <c r="Q86">
-        <v>2376.521078969219</v>
+        <v>2364.73521086171</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3007764717118899</v>
+        <v>0.3170409178956708</v>
       </c>
       <c r="T86">
-        <v>3.710218342789763</v>
+        <v>3.946885852388717</v>
       </c>
       <c r="U86">
         <v>0.08015748822216713</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.363841875481177</v>
+        <v>2.336031971063751</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1007005523756474</v>
+        <v>0.1007576829942286</v>
       </c>
       <c r="C87">
-        <v>1841.343821839622</v>
+        <v>1640.285882499702</v>
       </c>
       <c r="D87">
-        <v>14490.86882183962</v>
+        <v>14478.3158824997</v>
       </c>
       <c r="E87">
-        <v>9471.324999999999</v>
+        <v>9659.83</v>
       </c>
       <c r="F87">
-        <v>16022.925</v>
+        <v>16211.43</v>
       </c>
       <c r="G87">
         <v>3373.4</v>
@@ -8427,28 +8427,28 @@
         <v>3000.3</v>
       </c>
       <c r="M87">
-        <v>1284.357421972167</v>
+        <v>1299.467509289487</v>
       </c>
       <c r="N87">
-        <v>1715.942578027833</v>
+        <v>1700.832490710513</v>
       </c>
       <c r="O87">
-        <v>377.5073671661232</v>
+        <v>374.1831479563129</v>
       </c>
       <c r="P87">
-        <v>1338.43521086171</v>
+        <v>1326.6493427542</v>
       </c>
       <c r="Q87">
-        <v>2364.73521086171</v>
+        <v>2352.9493427542</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3170409178956708</v>
+        <v>0.3356288563914206</v>
       </c>
       <c r="T87">
-        <v>3.946885852388717</v>
+        <v>4.217363006216094</v>
       </c>
       <c r="U87">
         <v>0.08015748822216713</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.336031971063751</v>
+        <v>2.308868808609521</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1007576829942286</v>
+        <v>0.1008148136128098</v>
       </c>
       <c r="C88">
-        <v>1640.285882499702</v>
+        <v>1439.249672692124</v>
       </c>
       <c r="D88">
-        <v>14478.3158824997</v>
+        <v>14465.78467269212</v>
       </c>
       <c r="E88">
-        <v>9659.83</v>
+        <v>9848.335000000001</v>
       </c>
       <c r="F88">
-        <v>16211.43</v>
+        <v>16399.935</v>
       </c>
       <c r="G88">
         <v>3373.4</v>
@@ -8509,28 +8509,28 @@
         <v>3000.3</v>
       </c>
       <c r="M88">
-        <v>1299.467509289487</v>
+        <v>1314.577596606807</v>
       </c>
       <c r="N88">
-        <v>1700.832490710513</v>
+        <v>1685.722403393194</v>
       </c>
       <c r="O88">
-        <v>374.1831479563129</v>
+        <v>370.8589287465026</v>
       </c>
       <c r="P88">
-        <v>1326.6493427542</v>
+        <v>1314.863474646691</v>
       </c>
       <c r="Q88">
-        <v>2352.9493427542</v>
+        <v>2341.163474646691</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3356288563914206</v>
+        <v>0.3570764777326703</v>
       </c>
       <c r="T88">
-        <v>4.217363006216094</v>
+        <v>4.529452029863067</v>
       </c>
       <c r="U88">
         <v>0.08015748822216713</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.308868808609521</v>
+        <v>2.282330086671481</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1008148136128098</v>
+        <v>0.1008719442313909</v>
       </c>
       <c r="C89">
-        <v>1439.249672692124</v>
+        <v>1238.235136043921</v>
       </c>
       <c r="D89">
-        <v>14465.78467269212</v>
+        <v>14453.27513604392</v>
       </c>
       <c r="E89">
-        <v>9848.335000000001</v>
+        <v>10036.84</v>
       </c>
       <c r="F89">
-        <v>16399.935</v>
+        <v>16588.44</v>
       </c>
       <c r="G89">
         <v>3373.4</v>
@@ -8591,28 +8591,28 @@
         <v>3000.3</v>
       </c>
       <c r="M89">
-        <v>1314.577596606807</v>
+        <v>1329.687683924126</v>
       </c>
       <c r="N89">
-        <v>1685.722403393194</v>
+        <v>1670.612316075874</v>
       </c>
       <c r="O89">
-        <v>370.8589287465026</v>
+        <v>367.5347095366923</v>
       </c>
       <c r="P89">
-        <v>1314.863474646691</v>
+        <v>1303.077606539182</v>
       </c>
       <c r="Q89">
-        <v>2341.163474646691</v>
+        <v>2329.377606539181</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3570764777326703</v>
+        <v>0.3820987026307949</v>
       </c>
       <c r="T89">
-        <v>4.529452029863067</v>
+        <v>4.893555890784536</v>
       </c>
       <c r="U89">
         <v>0.08015748822216713</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.282330086671481</v>
+        <v>2.25639451750476</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1008719442313909</v>
+        <v>0.1028728348499721</v>
       </c>
       <c r="C90">
-        <v>1238.235136043921</v>
+        <v>624.8545507013769</v>
       </c>
       <c r="D90">
-        <v>14453.27513604392</v>
+        <v>14028.39955070138</v>
       </c>
       <c r="E90">
-        <v>10036.84</v>
+        <v>10225.345</v>
       </c>
       <c r="F90">
-        <v>16588.44</v>
+        <v>16776.945</v>
       </c>
       <c r="G90">
         <v>3373.4</v>
@@ -8673,45 +8673,45 @@
         <v>3000.3</v>
       </c>
       <c r="M90">
-        <v>1329.687683924126</v>
+        <v>1391.773217241446</v>
       </c>
       <c r="N90">
-        <v>1670.612316075874</v>
+        <v>1608.526782758554</v>
       </c>
       <c r="O90">
-        <v>367.5347095366923</v>
+        <v>353.8758922068819</v>
       </c>
       <c r="P90">
-        <v>1303.077606539182</v>
+        <v>1254.650890551672</v>
       </c>
       <c r="Q90">
-        <v>2329.377606539181</v>
+        <v>2280.950890551672</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3820987026307949</v>
+        <v>0.4116704229649422</v>
       </c>
       <c r="T90">
-        <v>4.893555890784536</v>
+        <v>5.323860453691726</v>
       </c>
       <c r="U90">
-        <v>0.08015748822216713</v>
+        <v>0.08295748822216714</v>
       </c>
       <c r="V90">
         <v>0.22</v>
       </c>
       <c r="W90">
-        <v>0.06252284081329036</v>
+        <v>0.06470684081329037</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.25639451750476</v>
+        <v>2.155739141141631</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1028728348499721</v>
+        <v>0.1029518054685532</v>
       </c>
       <c r="C91">
-        <v>624.8545507013769</v>
+        <v>420.0924819457105</v>
       </c>
       <c r="D91">
-        <v>14028.39955070138</v>
+        <v>14012.14248194571</v>
       </c>
       <c r="E91">
-        <v>10225.345</v>
+        <v>10413.85</v>
       </c>
       <c r="F91">
-        <v>16776.945</v>
+        <v>16965.45</v>
       </c>
       <c r="G91">
         <v>3373.4</v>
@@ -8755,28 +8755,28 @@
         <v>3000.3</v>
       </c>
       <c r="M91">
-        <v>1391.773217241446</v>
+        <v>1407.411118558766</v>
       </c>
       <c r="N91">
-        <v>1608.526782758554</v>
+        <v>1592.888881441235</v>
       </c>
       <c r="O91">
-        <v>353.8758922068819</v>
+        <v>350.4355539170716</v>
       </c>
       <c r="P91">
-        <v>1254.650890551672</v>
+        <v>1242.453327524163</v>
       </c>
       <c r="Q91">
-        <v>2280.950890551672</v>
+        <v>2268.753327524163</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4116704229649422</v>
+        <v>0.447156487365919</v>
       </c>
       <c r="T91">
-        <v>5.323860453691726</v>
+        <v>5.840225929180354</v>
       </c>
       <c r="U91">
         <v>0.08295748822216714</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.155739141141631</v>
+        <v>2.131786484017836</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1029518054685532</v>
+        <v>0.1030307760871344</v>
       </c>
       <c r="C92">
-        <v>420.0924819457105</v>
+        <v>215.368049180961</v>
       </c>
       <c r="D92">
-        <v>14012.14248194571</v>
+        <v>13995.92304918096</v>
       </c>
       <c r="E92">
-        <v>10413.85</v>
+        <v>10602.355</v>
       </c>
       <c r="F92">
-        <v>16965.45</v>
+        <v>17153.955</v>
       </c>
       <c r="G92">
         <v>3373.4</v>
@@ -8837,28 +8837,28 @@
         <v>3000.3</v>
       </c>
       <c r="M92">
-        <v>1407.411118558766</v>
+        <v>1423.049019876085</v>
       </c>
       <c r="N92">
-        <v>1592.888881441235</v>
+        <v>1577.250980123915</v>
       </c>
       <c r="O92">
-        <v>350.4355539170716</v>
+        <v>346.9952156272612</v>
       </c>
       <c r="P92">
-        <v>1242.453327524163</v>
+        <v>1230.255764496654</v>
       </c>
       <c r="Q92">
-        <v>2268.753327524163</v>
+        <v>2256.555764496653</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.447156487365919</v>
+        <v>0.4905283438560017</v>
       </c>
       <c r="T92">
-        <v>5.840225929180354</v>
+        <v>6.471339288110901</v>
       </c>
       <c r="U92">
         <v>0.08295748822216714</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.131786484017836</v>
+        <v>2.108360258918738</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1030307760871344</v>
+        <v>0.1031097467057155</v>
       </c>
       <c r="C93">
-        <v>215.368049180961</v>
+        <v>10.68112186422877</v>
       </c>
       <c r="D93">
-        <v>13995.92304918096</v>
+        <v>13979.74112186423</v>
       </c>
       <c r="E93">
-        <v>10602.355</v>
+        <v>10790.86</v>
       </c>
       <c r="F93">
-        <v>17153.955</v>
+        <v>17342.46</v>
       </c>
       <c r="G93">
         <v>3373.4</v>
@@ -8919,28 +8919,28 @@
         <v>3000.3</v>
       </c>
       <c r="M93">
-        <v>1423.049019876085</v>
+        <v>1438.686921193405</v>
       </c>
       <c r="N93">
-        <v>1577.250980123915</v>
+        <v>1561.613078806595</v>
       </c>
       <c r="O93">
-        <v>346.9952156272612</v>
+        <v>343.554877337451</v>
       </c>
       <c r="P93">
-        <v>1230.255764496654</v>
+        <v>1218.058201469144</v>
       </c>
       <c r="Q93">
-        <v>2256.555764496653</v>
+        <v>2244.358201469144</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4905283438560017</v>
+        <v>0.5447431644686052</v>
       </c>
       <c r="T93">
-        <v>6.471339288110901</v>
+        <v>7.260230986774085</v>
       </c>
       <c r="U93">
         <v>0.08295748822216714</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.108360258918738</v>
+        <v>2.085443299582665</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1031097467057155</v>
+        <v>0.1031887173242967</v>
       </c>
       <c r="C94">
-        <v>10.68112186422877</v>
+        <v>-193.968429944387</v>
       </c>
       <c r="D94">
-        <v>13979.74112186423</v>
+        <v>13963.59657005561</v>
       </c>
       <c r="E94">
-        <v>10790.86</v>
+        <v>10979.365</v>
       </c>
       <c r="F94">
-        <v>17342.46</v>
+        <v>17530.965</v>
       </c>
       <c r="G94">
         <v>3373.4</v>
@@ -9001,28 +9001,28 @@
         <v>3000.3</v>
       </c>
       <c r="M94">
-        <v>1438.686921193405</v>
+        <v>1454.324822510724</v>
       </c>
       <c r="N94">
-        <v>1561.613078806595</v>
+        <v>1545.975177489276</v>
       </c>
       <c r="O94">
-        <v>343.554877337451</v>
+        <v>340.1145390476407</v>
       </c>
       <c r="P94">
-        <v>1218.058201469144</v>
+        <v>1205.860638441635</v>
       </c>
       <c r="Q94">
-        <v>2244.358201469144</v>
+        <v>2232.160638441635</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5447431644686052</v>
+        <v>0.6144479338276666</v>
       </c>
       <c r="T94">
-        <v>7.260230986774085</v>
+        <v>8.274520313626747</v>
       </c>
       <c r="U94">
         <v>0.08295748822216714</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.085443299582665</v>
+        <v>2.063019178081777</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1031887173242967</v>
+        <v>0.1032676879428778</v>
       </c>
       <c r="C95">
-        <v>-193.968429944387</v>
+        <v>-398.5807355852085</v>
       </c>
       <c r="D95">
-        <v>13963.59657005561</v>
+        <v>13947.48926441479</v>
       </c>
       <c r="E95">
-        <v>10979.365</v>
+        <v>11167.87</v>
       </c>
       <c r="F95">
-        <v>17530.965</v>
+        <v>17719.47</v>
       </c>
       <c r="G95">
         <v>3373.4</v>
@@ -9083,28 +9083,28 @@
         <v>3000.3</v>
       </c>
       <c r="M95">
-        <v>1454.324822510724</v>
+        <v>1469.962723828044</v>
       </c>
       <c r="N95">
-        <v>1545.975177489276</v>
+        <v>1530.337276171956</v>
       </c>
       <c r="O95">
-        <v>340.1145390476407</v>
+        <v>336.6742007578304</v>
       </c>
       <c r="P95">
-        <v>1205.860638441635</v>
+        <v>1193.663075414126</v>
       </c>
       <c r="Q95">
-        <v>2232.160638441635</v>
+        <v>2219.963075414125</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6144479338276666</v>
+        <v>0.7073876263064155</v>
       </c>
       <c r="T95">
-        <v>8.274520313626747</v>
+        <v>9.626906082763634</v>
       </c>
       <c r="U95">
         <v>0.08295748822216714</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.063019178081777</v>
+        <v>2.041072165548992</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1032676879428778</v>
+        <v>0.103346658561459</v>
       </c>
       <c r="C96">
-        <v>-398.5807355852085</v>
+        <v>-603.1559238024747</v>
       </c>
       <c r="D96">
-        <v>13947.48926441479</v>
+        <v>13931.41907619753</v>
       </c>
       <c r="E96">
-        <v>11167.87</v>
+        <v>11356.375</v>
       </c>
       <c r="F96">
-        <v>17719.47</v>
+        <v>17907.975</v>
       </c>
       <c r="G96">
         <v>3373.4</v>
@@ -9165,28 +9165,28 @@
         <v>3000.3</v>
       </c>
       <c r="M96">
-        <v>1469.962723828044</v>
+        <v>1485.600625145364</v>
       </c>
       <c r="N96">
-        <v>1530.337276171956</v>
+        <v>1514.699374854636</v>
       </c>
       <c r="O96">
-        <v>336.6742007578304</v>
+        <v>333.23386246802</v>
       </c>
       <c r="P96">
-        <v>1193.663075414126</v>
+        <v>1181.465512386616</v>
       </c>
       <c r="Q96">
-        <v>2219.963075414125</v>
+        <v>2207.765512386616</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7073876263064155</v>
+        <v>0.8375031957766641</v>
       </c>
       <c r="T96">
-        <v>9.626906082763634</v>
+        <v>11.52024615955528</v>
       </c>
       <c r="U96">
         <v>0.08295748822216714</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.041072165548992</v>
+        <v>2.019587195385318</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.103346658561459</v>
+        <v>0.1092662691800402</v>
       </c>
       <c r="C97">
-        <v>-603.1559238024747</v>
+        <v>-1899.23031950445</v>
       </c>
       <c r="D97">
-        <v>13931.41907619753</v>
+        <v>12823.84968049555</v>
       </c>
       <c r="E97">
-        <v>11356.375</v>
+        <v>11544.88</v>
       </c>
       <c r="F97">
-        <v>17907.975</v>
+        <v>18096.48</v>
       </c>
       <c r="G97">
         <v>3373.4</v>
@@ -9247,45 +9247,45 @@
         <v>3000.3</v>
       </c>
       <c r="M97">
-        <v>1485.600625145364</v>
+        <v>1642.391070462684</v>
       </c>
       <c r="N97">
-        <v>1514.699374854636</v>
+        <v>1357.908929537317</v>
       </c>
       <c r="O97">
-        <v>333.23386246802</v>
+        <v>298.7399644982096</v>
       </c>
       <c r="P97">
-        <v>1181.465512386616</v>
+        <v>1059.168965039107</v>
       </c>
       <c r="Q97">
-        <v>2207.765512386616</v>
+        <v>2085.468965039106</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8375031957766641</v>
+        <v>1.032676549982037</v>
       </c>
       <c r="T97">
-        <v>11.52024615955528</v>
+        <v>14.36025627474274</v>
       </c>
       <c r="U97">
-        <v>0.08295748822216714</v>
+        <v>0.09075748822216714</v>
       </c>
       <c r="V97">
         <v>0.22</v>
       </c>
       <c r="W97">
-        <v>0.06470684081329037</v>
+        <v>0.07079084081329037</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.019587195385318</v>
+        <v>1.826787818052844</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1092662691800401</v>
+        <v>0.1094060797986213</v>
       </c>
       <c r="C98">
-        <v>-1899.230319504442</v>
+        <v>-2111.769334189537</v>
       </c>
       <c r="D98">
-        <v>12823.84968049556</v>
+        <v>12799.81566581046</v>
       </c>
       <c r="E98">
-        <v>11544.88</v>
+        <v>11733.385</v>
       </c>
       <c r="F98">
-        <v>18096.48</v>
+        <v>18284.985</v>
       </c>
       <c r="G98">
         <v>3373.4</v>
@@ -9329,28 +9329,28 @@
         <v>3000.3</v>
       </c>
       <c r="M98">
-        <v>1642.391070462683</v>
+        <v>1659.499310780003</v>
       </c>
       <c r="N98">
-        <v>1357.908929537317</v>
+        <v>1340.800689219997</v>
       </c>
       <c r="O98">
-        <v>298.7399644982097</v>
+        <v>294.9761516283994</v>
       </c>
       <c r="P98">
-        <v>1059.168965039107</v>
+        <v>1045.824537591598</v>
       </c>
       <c r="Q98">
-        <v>2085.468965039107</v>
+        <v>2072.124537591598</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.032676549982034</v>
+        <v>1.357965473657654</v>
       </c>
       <c r="T98">
-        <v>14.3602562747427</v>
+        <v>19.09360646672179</v>
       </c>
       <c r="U98">
         <v>0.09075748822216714</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.826787818052844</v>
+        <v>1.807954953949206</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1094060797986213</v>
+        <v>0.1095458904172025</v>
       </c>
       <c r="C99">
-        <v>-2111.769334189537</v>
+        <v>-2324.218429962593</v>
       </c>
       <c r="D99">
-        <v>12799.81566581046</v>
+        <v>12775.87157003741</v>
       </c>
       <c r="E99">
-        <v>11733.385</v>
+        <v>11921.89</v>
       </c>
       <c r="F99">
-        <v>18284.985</v>
+        <v>18473.49</v>
       </c>
       <c r="G99">
         <v>3373.4</v>
@@ -9411,28 +9411,28 @@
         <v>3000.3</v>
       </c>
       <c r="M99">
-        <v>1659.499310780003</v>
+        <v>1676.607551097322</v>
       </c>
       <c r="N99">
-        <v>1340.800689219997</v>
+        <v>1323.692448902678</v>
       </c>
       <c r="O99">
-        <v>294.9761516283994</v>
+        <v>291.2123387585891</v>
       </c>
       <c r="P99">
-        <v>1045.824537591598</v>
+        <v>1032.480110144089</v>
       </c>
       <c r="Q99">
-        <v>2072.124537591598</v>
+        <v>2058.780110144088</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.357965473657654</v>
+        <v>2.008543321008894</v>
       </c>
       <c r="T99">
-        <v>19.09360646672179</v>
+        <v>28.56030685067996</v>
       </c>
       <c r="U99">
         <v>0.09075748822216714</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.807954953949206</v>
+        <v>1.78950643401095</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1095458904172025</v>
+        <v>0.1096857010357836</v>
       </c>
       <c r="C100">
-        <v>-2324.218429962593</v>
+        <v>-2536.578110504388</v>
       </c>
       <c r="D100">
-        <v>12775.87157003741</v>
+        <v>12752.01688949561</v>
       </c>
       <c r="E100">
-        <v>11921.89</v>
+        <v>12110.395</v>
       </c>
       <c r="F100">
-        <v>18473.49</v>
+        <v>18661.995</v>
       </c>
       <c r="G100">
         <v>3373.4</v>
@@ -9493,28 +9493,28 @@
         <v>3000.3</v>
       </c>
       <c r="M100">
-        <v>1676.607551097322</v>
+        <v>1693.715791414642</v>
       </c>
       <c r="N100">
-        <v>1323.692448902678</v>
+        <v>1306.584208585358</v>
       </c>
       <c r="O100">
-        <v>291.2123387585891</v>
+        <v>287.4485258887788</v>
       </c>
       <c r="P100">
-        <v>1032.480110144089</v>
+        <v>1019.135682696579</v>
       </c>
       <c r="Q100">
-        <v>2058.780110144088</v>
+        <v>2045.435682696579</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.008543321008894</v>
+        <v>3.960276863062612</v>
       </c>
       <c r="T100">
-        <v>28.56030685067996</v>
+        <v>56.96040800255447</v>
       </c>
       <c r="U100">
         <v>0.09075748822216714</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.78950643401095</v>
+        <v>1.771430611445182</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1096857010357836</v>
-      </c>
-      <c r="C101">
-        <v>-2536.578110504388</v>
-      </c>
-      <c r="D101">
-        <v>12752.01688949561</v>
-      </c>
-      <c r="E101">
-        <v>12110.395</v>
-      </c>
-      <c r="F101">
-        <v>18661.995</v>
-      </c>
-      <c r="G101">
-        <v>3373.4</v>
-      </c>
-      <c r="H101">
-        <v>12298.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4026.6</v>
-      </c>
-      <c r="K101">
-        <v>1026.3</v>
-      </c>
-      <c r="L101">
-        <v>3000.3</v>
-      </c>
-      <c r="M101">
-        <v>1693.715791414642</v>
-      </c>
-      <c r="N101">
-        <v>1306.584208585358</v>
-      </c>
-      <c r="O101">
-        <v>287.4485258887788</v>
-      </c>
-      <c r="P101">
-        <v>1019.135682696579</v>
-      </c>
-      <c r="Q101">
-        <v>2045.435682696579</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.960276863062612</v>
-      </c>
-      <c r="T101">
-        <v>56.96040800255447</v>
-      </c>
-      <c r="U101">
-        <v>0.09075748822216714</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.07079084081329037</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.771430611445182</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
